--- a/public/monitor_latest.xlsx
+++ b/public/monitor_latest.xlsx
@@ -9430,12 +9430,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>李德生</t>
+          <t>罗云照</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>1016030307</t>
+          <t>297822572</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -9450,7 +9450,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>午高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -9471,7 +9471,7 @@
         <v>20</v>
       </c>
       <c r="K172" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L172" t="n">
         <v>0</v>
@@ -9485,12 +9485,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>罗云照</t>
+          <t>杨城鑫</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>297822572</t>
+          <t>1159670127</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -9505,7 +9505,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -9526,7 +9526,7 @@
         <v>20</v>
       </c>
       <c r="K173" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L173" t="n">
         <v>0</v>
@@ -9540,12 +9540,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>杨城鑫</t>
+          <t>王兵</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>1159670127</t>
+          <t>330361220</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -9560,7 +9560,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵2、夜宵1</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -9581,7 +9581,7 @@
         <v>20</v>
       </c>
       <c r="K174" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L174" t="n">
         <v>0</v>
@@ -9595,12 +9595,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>王兵</t>
+          <t>李正国</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>330361220</t>
+          <t>261808524</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -9615,7 +9615,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵2、夜宵1</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -9636,7 +9636,7 @@
         <v>20</v>
       </c>
       <c r="K175" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L175" t="n">
         <v>0</v>
@@ -9650,12 +9650,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>李正国</t>
+          <t>张云强</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>261808524</t>
+          <t>1016211018</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -9670,7 +9670,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -9691,7 +9691,7 @@
         <v>20</v>
       </c>
       <c r="K176" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L176" t="n">
         <v>0</v>
@@ -9705,12 +9705,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>张云强</t>
+          <t>王政元</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>1016211018</t>
+          <t>1034685238</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -9746,7 +9746,7 @@
         <v>20</v>
       </c>
       <c r="K177" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L177" t="n">
         <v>0</v>
@@ -9760,12 +9760,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>王政元</t>
+          <t>罗师航</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>1034685238</t>
+          <t>1092599780</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -9801,7 +9801,7 @@
         <v>20</v>
       </c>
       <c r="K178" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L178" t="n">
         <v>0</v>
@@ -9815,12 +9815,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>罗师航</t>
+          <t>石福</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>1092599780</t>
+          <t>282612804</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -9870,12 +9870,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>石福</t>
+          <t>张仲阳</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>282612804</t>
+          <t>273841420</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -9911,7 +9911,7 @@
         <v>20</v>
       </c>
       <c r="K180" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L180" t="n">
         <v>0</v>
@@ -9925,12 +9925,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>张仲阳</t>
+          <t>王世奎</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>273841420</t>
+          <t>320004748</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -9945,7 +9945,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -9966,7 +9966,7 @@
         <v>20</v>
       </c>
       <c r="K181" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L181" t="n">
         <v>0</v>
@@ -9980,12 +9980,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>王世奎</t>
+          <t>李德生</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>320004748</t>
+          <t>1016030307</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -10000,16 +10000,16 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G182" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H182" t="n">
         <v>480</v>
@@ -10021,10 +10021,10 @@
         <v>20</v>
       </c>
       <c r="K182" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M182" t="inlineStr">
         <is>

--- a/public/monitor_latest.xlsx
+++ b/public/monitor_latest.xlsx
@@ -10009,7 +10009,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="H182" t="n">
         <v>480</v>

--- a/public/monitor_latest.xlsx
+++ b/public/monitor_latest.xlsx
@@ -10009,7 +10009,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H182" t="n">
         <v>480</v>

--- a/public/monitor_latest.xlsx
+++ b/public/monitor_latest.xlsx
@@ -10009,13 +10009,13 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H182" t="n">
         <v>480</v>
       </c>
       <c r="I182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J182" t="n">
         <v>20</v>
@@ -10024,7 +10024,7 @@
         <v>15</v>
       </c>
       <c r="L182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M182" t="inlineStr">
         <is>

--- a/public/monitor_latest.xlsx
+++ b/public/monitor_latest.xlsx
@@ -8000,12 +8000,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>周杰宽</t>
+          <t>雷仕华</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>241046795</t>
+          <t>277513820</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -8041,7 +8041,7 @@
         <v>20</v>
       </c>
       <c r="K146" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L146" t="n">
         <v>0</v>
@@ -8055,12 +8055,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>雷仕华</t>
+          <t>罗锦馥</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>277513820</t>
+          <t>1056121129</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -8096,7 +8096,7 @@
         <v>20</v>
       </c>
       <c r="K147" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="L147" t="n">
         <v>0</v>
@@ -8110,12 +8110,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>罗锦馥</t>
+          <t>杨忠林</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>1056121129</t>
+          <t>1016132235</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -8151,7 +8151,7 @@
         <v>20</v>
       </c>
       <c r="K148" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="L148" t="n">
         <v>0</v>
@@ -8165,12 +8165,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>杨忠林</t>
+          <t>魏启东</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>1016132235</t>
+          <t>291727548</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -8206,7 +8206,7 @@
         <v>20</v>
       </c>
       <c r="K149" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="L149" t="n">
         <v>0</v>
@@ -8220,12 +8220,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>魏启东</t>
+          <t>邱龙涛</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>291727548</t>
+          <t>328769468</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -8249,19 +8249,19 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="H150" t="n">
         <v>480</v>
       </c>
       <c r="I150" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J150" t="n">
         <v>20</v>
       </c>
       <c r="K150" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
@@ -8275,12 +8275,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>邱龙涛</t>
+          <t>刀志鸿</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>328769468</t>
+          <t>308511236</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -8304,19 +8304,19 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="H151" t="n">
         <v>480</v>
       </c>
       <c r="I151" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J151" t="n">
         <v>20</v>
       </c>
       <c r="K151" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L151" t="n">
         <v>0</v>
@@ -8330,12 +8330,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>刀志鸿</t>
+          <t>罗庆福</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>308511236</t>
+          <t>265204452</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -8371,7 +8371,7 @@
         <v>20</v>
       </c>
       <c r="K152" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -8385,12 +8385,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>罗庆福</t>
+          <t>李童焘</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>265204452</t>
+          <t>1040564072</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>凌晨1、晚高峰</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -8414,19 +8414,19 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="H153" t="n">
         <v>480</v>
       </c>
       <c r="I153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J153" t="n">
         <v>20</v>
       </c>
       <c r="K153" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L153" t="n">
         <v>0</v>
@@ -8440,12 +8440,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>李童焘</t>
+          <t>沈正阳</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>1040564072</t>
+          <t>1020850421</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -8460,7 +8460,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>凌晨1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -8469,19 +8469,19 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="H154" t="n">
         <v>480</v>
       </c>
       <c r="I154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J154" t="n">
         <v>20</v>
       </c>
       <c r="K154" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L154" t="n">
         <v>0</v>
@@ -8495,12 +8495,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>沈正阳</t>
+          <t>祁杨</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>1020850421</t>
+          <t>277527332</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -8536,7 +8536,7 @@
         <v>20</v>
       </c>
       <c r="K155" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L155" t="n">
         <v>0</v>
@@ -8550,12 +8550,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>祁杨</t>
+          <t>陈会岭</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>277527332</t>
+          <t>202706747</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -8591,7 +8591,7 @@
         <v>20</v>
       </c>
       <c r="K156" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L156" t="n">
         <v>0</v>
@@ -8605,12 +8605,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>陈会岭</t>
+          <t>李祖顺</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>202706747</t>
+          <t>300606788</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -8646,7 +8646,7 @@
         <v>20</v>
       </c>
       <c r="K157" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L157" t="n">
         <v>0</v>
@@ -8660,12 +8660,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>李祖顺</t>
+          <t>吴发春</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>300606788</t>
+          <t>1125257340</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -8715,12 +8715,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>吴发春</t>
+          <t>李永福</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>1125257340</t>
+          <t>313354908</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -8756,7 +8756,7 @@
         <v>20</v>
       </c>
       <c r="K159" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L159" t="n">
         <v>0</v>
@@ -8770,12 +8770,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>李永福</t>
+          <t>黄显龙</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>313354908</t>
+          <t>270399468</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -8811,7 +8811,7 @@
         <v>20</v>
       </c>
       <c r="K160" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L160" t="n">
         <v>0</v>
@@ -8825,12 +8825,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>黄显龙</t>
+          <t>朱原庆</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>270399468</t>
+          <t>1090480333</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -8866,7 +8866,7 @@
         <v>20</v>
       </c>
       <c r="K161" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L161" t="n">
         <v>0</v>
@@ -8880,12 +8880,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>朱原庆</t>
+          <t>罗杰</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>1090480333</t>
+          <t>291486188</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -8921,7 +8921,7 @@
         <v>20</v>
       </c>
       <c r="K162" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="L162" t="n">
         <v>0</v>
@@ -8935,12 +8935,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>罗杰</t>
+          <t>佟露</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>291486188</t>
+          <t>1016169126</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -8976,7 +8976,7 @@
         <v>20</v>
       </c>
       <c r="K163" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L163" t="n">
         <v>0</v>
@@ -8990,12 +8990,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>佟露</t>
+          <t>刀太勇</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>1016169126</t>
+          <t>1051720597</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -9031,7 +9031,7 @@
         <v>20</v>
       </c>
       <c r="K164" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L164" t="n">
         <v>0</v>
@@ -9045,12 +9045,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>刀太勇</t>
+          <t>吴海斌</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>1051720597</t>
+          <t>1052004810</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -9086,7 +9086,7 @@
         <v>20</v>
       </c>
       <c r="K165" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L165" t="n">
         <v>0</v>
@@ -9100,12 +9100,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>吴海斌</t>
+          <t>周铅超</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>1052004810</t>
+          <t>157611867</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -9141,7 +9141,7 @@
         <v>20</v>
       </c>
       <c r="K166" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L166" t="n">
         <v>0</v>
@@ -9155,12 +9155,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>周铅超</t>
+          <t>周杰宽</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>157611867</t>
+          <t>241046795</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -9175,16 +9175,16 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰、夜宵2</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H167" t="n">
         <v>480</v>
@@ -10009,7 +10009,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H182" t="n">
         <v>480</v>

--- a/public/monitor_latest.xlsx
+++ b/public/monitor_latest.xlsx
@@ -9184,7 +9184,7 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H167" t="n">
         <v>480</v>
@@ -9199,7 +9199,7 @@
         <v>15</v>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M167" t="inlineStr">
         <is>
@@ -10009,13 +10009,13 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H182" t="n">
         <v>480</v>
       </c>
       <c r="I182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J182" t="n">
         <v>20</v>
@@ -10024,7 +10024,7 @@
         <v>15</v>
       </c>
       <c r="L182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M182" t="inlineStr">
         <is>

--- a/public/monitor_latest.xlsx
+++ b/public/monitor_latest.xlsx
@@ -9184,7 +9184,7 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H167" t="n">
         <v>480</v>
@@ -10009,7 +10009,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H182" t="n">
         <v>480</v>

--- a/public/monitor_latest.xlsx
+++ b/public/monitor_latest.xlsx
@@ -9184,7 +9184,7 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H167" t="n">
         <v>480</v>
@@ -9199,7 +9199,7 @@
         <v>15</v>
       </c>
       <c r="L167" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M167" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H182" t="n">
         <v>480</v>

--- a/public/monitor_latest.xlsx
+++ b/public/monitor_latest.xlsx
@@ -121,7 +121,7 @@
         <v>20</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -231,7 +231,7 @@
         <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -245,12 +245,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>杨海轮</t>
+          <t>李翠伟</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>290558268</t>
+          <t>1049933839</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -286,7 +286,7 @@
         <v>20</v>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -300,12 +300,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>胡关浚</t>
+          <t>杨海轮</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>261536156</t>
+          <t>290558268</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -320,7 +320,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>凌晨1、凌晨2、凌晨3、夜宵1</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -329,19 +329,19 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>338</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>480</v>
       </c>
       <c r="I6" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -439,7 +439,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H8" t="n">
         <v>480</v>
@@ -465,12 +465,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>陈维富</t>
+          <t>刀荣程</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>270698852</t>
+          <t>1044820977</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -485,7 +485,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>下午茶1</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -506,7 +506,7 @@
         <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -520,12 +520,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>刀荣程</t>
+          <t>沈红心</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1044820977</t>
+          <t>1151687559</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -575,12 +575,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>沈红心</t>
+          <t>胡关浚</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1151687559</t>
+          <t>261536156</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -595,31 +595,31 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>凌晨1、凌晨2、凌晨3、夜宵1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="H11" t="n">
         <v>480</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
         <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -630,12 +630,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>朱健明</t>
+          <t>陈维富</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1013523131</t>
+          <t>270698852</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -650,31 +650,31 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>凌晨1、凌晨2、凌晨3、夜宵1</t>
+          <t>凌晨1、凌晨2</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>331</v>
+        <v>105</v>
       </c>
       <c r="H12" t="n">
         <v>480</v>
       </c>
       <c r="I12" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>20</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>早餐2</t>
+          <t>夜宵2</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -740,12 +740,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>汤亚东</t>
+          <t>张文平</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>313288188</t>
+          <t>316521756</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -795,12 +795,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>张文平</t>
+          <t>李世坚</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>316521756</t>
+          <t>1124817963</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -836,7 +836,7 @@
         <v>20</v>
       </c>
       <c r="K15" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>480</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>20</v>
@@ -1001,7 +1001,7 @@
         <v>20</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1180,12 +1180,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>鲁炫</t>
+          <t>尹江涛</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>90000339224588</t>
+          <t>1051146884</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>下午茶1、下午茶2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1221,7 +1221,7 @@
         <v>20</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -1235,12 +1235,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>尹江涛</t>
+          <t>李国斌</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1051146884</t>
+          <t>286239588</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>下午茶1、下午茶2、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1276,7 +1276,7 @@
         <v>20</v>
       </c>
       <c r="K23" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -1290,12 +1290,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>李国斌</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>286239588</t>
+          <t>1042321509</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1331,7 +1331,7 @@
         <v>20</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -1345,12 +1345,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>杨福云</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1042321509</t>
+          <t>1156896791</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1400,12 +1400,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>杨福云</t>
+          <t>杨绍元</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1156896791</t>
+          <t>264801124</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1455,12 +1455,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>杨绍元</t>
+          <t>汪宗兵</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>264801124</t>
+          <t>1037848475</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1496,7 +1496,7 @@
         <v>20</v>
       </c>
       <c r="K27" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -1510,12 +1510,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>汪宗兵</t>
+          <t>王朝顺</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1037848475</t>
+          <t>287127412</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1551,7 +1551,7 @@
         <v>20</v>
       </c>
       <c r="K28" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -1565,12 +1565,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>王朝顺</t>
+          <t>鲍德斌</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>287127412</t>
+          <t>317794948</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1620,12 +1620,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>鲍国明</t>
+          <t>王武斌</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1087319378</t>
+          <t>300824396</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>凌晨1、凌晨2、凌晨3、夜宵1</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1649,13 +1649,13 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>480</v>
       </c>
       <c r="I30" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>20</v>
@@ -1675,12 +1675,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>鲍德斌</t>
+          <t>施发龙</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>317794948</t>
+          <t>1060067605</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、晚高峰、夜宵2、夜宵1</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1730,12 +1730,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>王武斌</t>
+          <t>鲍国明</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>300824396</t>
+          <t>1087319378</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1750,22 +1750,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>凌晨1、凌晨2、凌晨3、夜宵1</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="H32" t="n">
         <v>480</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J32" t="n">
         <v>20</v>
@@ -1774,7 +1774,7 @@
         <v>15</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -1785,17 +1785,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>施发龙</t>
+          <t>王钱</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1060067605</t>
+          <t>289243292</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>思茅优选二队</t>
+          <t>思茅优选三队</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵2、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1826,7 +1826,7 @@
         <v>20</v>
       </c>
       <c r="K33" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -1840,12 +1840,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>鲍家伟</t>
+          <t>普李叶</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1069055452</t>
+          <t>1019684446</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>凌晨1、凌晨2、凌晨3、夜宵1</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1869,19 +1869,19 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
         <v>480</v>
       </c>
       <c r="I34" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
         <v>20</v>
       </c>
       <c r="K34" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -1895,12 +1895,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>杨建国</t>
+          <t>佟奇</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1138840186</t>
+          <t>90000336291956</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>凌晨1、凌晨2、凌晨3、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1924,19 +1924,19 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>370</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>480</v>
       </c>
       <c r="I35" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>20</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -1950,12 +1950,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>李海斌</t>
+          <t>李健伟</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>90000335390900</t>
+          <t>264431676</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>下午茶1</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1991,7 +1991,7 @@
         <v>20</v>
       </c>
       <c r="K36" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -2005,12 +2005,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>胡锦波</t>
+          <t>农光应</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>316835700</t>
+          <t>1142610772</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>凌晨1、凌晨2、凌晨3、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2034,19 +2034,19 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>480</v>
       </c>
       <c r="I37" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>20</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -2060,12 +2060,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>普李叶</t>
+          <t>龙峰</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1019684446</t>
+          <t>1087320804</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2101,7 +2101,7 @@
         <v>20</v>
       </c>
       <c r="K38" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -2115,12 +2115,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>佟奇</t>
+          <t>赵兴跃</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>90000336291956</t>
+          <t>1045086221</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2156,7 +2156,7 @@
         <v>20</v>
       </c>
       <c r="K39" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -2170,12 +2170,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>李健伟</t>
+          <t>鲍家伟</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>264431676</t>
+          <t>1069055452</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2190,31 +2190,31 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>下午茶1</t>
+          <t>凌晨1、凌晨2、凌晨3、夜宵1</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="H40" t="n">
         <v>480</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J40" t="n">
         <v>20</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>农光应</t>
+          <t>杨建国</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1142610772</t>
+          <t>1138840186</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2245,31 +2245,31 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>凌晨1、凌晨2、凌晨3、夜宵1</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="H41" t="n">
         <v>480</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J41" t="n">
         <v>20</v>
       </c>
       <c r="K41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -2280,12 +2280,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>龙峰</t>
+          <t>胡锦波</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1087320804</t>
+          <t>316835700</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2300,31 +2300,31 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰、夜宵2</t>
+          <t>凌晨1、凌晨2、凌晨3、夜宵1</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="H42" t="n">
         <v>480</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J42" t="n">
         <v>20</v>
       </c>
       <c r="K42" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -2335,27 +2335,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>赵兴跃</t>
+          <t>罗佳杨</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1045086221</t>
+          <t>289157644</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>思茅优选三队</t>
+          <t>思茅蜂跑一队</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>优选</t>
+          <t>蜂跑</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>午高峰</t>
+          <t>午高峰、下午茶1、夜宵2</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2376,7 +2376,7 @@
         <v>20</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -2390,12 +2390,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>罗佳杨</t>
+          <t>李新田</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>289157644</t>
+          <t>320683868</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2445,12 +2445,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>李新田</t>
+          <t>赵文俊</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>320683868</t>
+          <t>1019362134</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>下午茶1、下午茶2、晚高峰、夜宵2</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2486,7 +2486,7 @@
         <v>20</v>
       </c>
       <c r="K45" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -2500,12 +2500,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>赵文俊</t>
+          <t>郑荣建</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1019362134</t>
+          <t>307784220</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2541,7 +2541,7 @@
         <v>20</v>
       </c>
       <c r="K46" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -2555,12 +2555,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>郑荣建</t>
+          <t>袁洲</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>307784220</t>
+          <t>332120988</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2596,7 +2596,7 @@
         <v>20</v>
       </c>
       <c r="K47" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -2610,12 +2610,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>袁洲</t>
+          <t>王浩</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>332120988</t>
+          <t>1046180007</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2651,7 +2651,7 @@
         <v>20</v>
       </c>
       <c r="K48" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -2665,12 +2665,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>车俊超</t>
+          <t>李志义</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>291997260</t>
+          <t>1112358704</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>下午茶1、下午茶2、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2706,7 +2706,7 @@
         <v>20</v>
       </c>
       <c r="K49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -2720,12 +2720,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>张忠海</t>
+          <t>者少军</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1003950027</t>
+          <t>261859444</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>早餐2、午高峰</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2761,7 +2761,7 @@
         <v>20</v>
       </c>
       <c r="K50" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -2775,17 +2775,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>王浩</t>
+          <t>罗晨龙</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1046180007</t>
+          <t>293959380</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>思茅蜂跑一队</t>
+          <t>思茅蜂跑三队</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>下午茶2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2816,7 +2816,7 @@
         <v>20</v>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -2830,17 +2830,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>李志义</t>
+          <t>朱加林</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1112358704</t>
+          <t>186839747</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>思茅蜂跑一队</t>
+          <t>思茅蜂跑三队</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2871,7 +2871,7 @@
         <v>20</v>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -2885,17 +2885,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>王金林</t>
+          <t>张小华</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1125678007</t>
+          <t>317756532</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>思茅蜂跑一队</t>
+          <t>思茅蜂跑三队</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2926,7 +2926,7 @@
         <v>20</v>
       </c>
       <c r="K53" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -2940,12 +2940,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>罗晨龙</t>
+          <t>蓝琨</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>293959380</t>
+          <t>1070814423</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>下午茶2、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2981,7 +2981,7 @@
         <v>20</v>
       </c>
       <c r="K54" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -2995,12 +2995,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>朱加林</t>
+          <t>王东奎</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>186839747</t>
+          <t>1042700176</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>下午茶2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3036,7 +3036,7 @@
         <v>20</v>
       </c>
       <c r="K55" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -3050,12 +3050,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>张小华</t>
+          <t>金富勤</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>317756532</t>
+          <t>615466374</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3091,7 +3091,7 @@
         <v>20</v>
       </c>
       <c r="K56" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -3105,12 +3105,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>蓝琨</t>
+          <t>陈少平</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1070814423</t>
+          <t>1015826982</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3146,7 +3146,7 @@
         <v>20</v>
       </c>
       <c r="K57" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -3160,12 +3160,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>王东奎</t>
+          <t>李旺坤</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1042700176</t>
+          <t>1052121306</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>下午茶2、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3201,7 +3201,7 @@
         <v>20</v>
       </c>
       <c r="K58" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -3215,12 +3215,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>钱思安</t>
+          <t>白凯勇</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>289601204</t>
+          <t>1092736925</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>下午茶2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3256,7 +3256,7 @@
         <v>20</v>
       </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -3270,12 +3270,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>陈少平</t>
+          <t>金锐</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1015826982</t>
+          <t>292657164</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>下午茶2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3311,7 +3311,7 @@
         <v>20</v>
       </c>
       <c r="K60" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -3325,12 +3325,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>李旺坤</t>
+          <t>刘钦臣</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1052121306</t>
+          <t>332133620</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、夜宵2</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3366,7 +3366,7 @@
         <v>20</v>
       </c>
       <c r="K61" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -3380,17 +3380,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>白凯勇</t>
+          <t>何彪</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1092736925</t>
+          <t>511001013</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>思茅蜂跑三队</t>
+          <t>思茅蜂跑四队</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>下午茶2、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3421,7 +3421,7 @@
         <v>20</v>
       </c>
       <c r="K62" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -3435,17 +3435,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>金锐</t>
+          <t>毕航</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>292657164</t>
+          <t>325067300</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>思茅蜂跑三队</t>
+          <t>思茅蜂跑四队</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>下午茶2、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3476,7 +3476,7 @@
         <v>20</v>
       </c>
       <c r="K63" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -3490,17 +3490,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>刘钦臣</t>
+          <t>苏志国</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>332133620</t>
+          <t>1011062500</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>思茅蜂跑三队</t>
+          <t>思茅蜂跑四队</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、夜宵2</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3531,7 +3531,7 @@
         <v>20</v>
       </c>
       <c r="K64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -3545,12 +3545,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>何彪</t>
+          <t>李院辉</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>511001013</t>
+          <t>1140485075</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3586,7 +3586,7 @@
         <v>20</v>
       </c>
       <c r="K65" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -3600,12 +3600,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>毕航</t>
+          <t>陶改荣</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>325067300</t>
+          <t>1102455067</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3641,7 +3641,7 @@
         <v>20</v>
       </c>
       <c r="K66" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -3655,12 +3655,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>苏志国</t>
+          <t>毕朝军</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1011062500</t>
+          <t>90000334561228</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3696,7 +3696,7 @@
         <v>20</v>
       </c>
       <c r="K67" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -3710,12 +3710,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>毕朝军</t>
+          <t>段文斌</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>90000334561228</t>
+          <t>280124636</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>午高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3751,7 +3751,7 @@
         <v>20</v>
       </c>
       <c r="K68" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -3765,12 +3765,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>段文斌</t>
+          <t>施圆章</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>280124636</t>
+          <t>261823124</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3806,7 +3806,7 @@
         <v>20</v>
       </c>
       <c r="K69" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -3820,12 +3820,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>施圆章</t>
+          <t>毛勇</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>261823124</t>
+          <t>1044060042</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3861,7 +3861,7 @@
         <v>20</v>
       </c>
       <c r="K70" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -3875,12 +3875,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>李晓春</t>
+          <t>罗晓余</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>286141340</t>
+          <t>1150777253</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3916,7 +3916,7 @@
         <v>20</v>
       </c>
       <c r="K71" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -3930,12 +3930,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>罗梦宇</t>
+          <t>李晓春</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1075569997</t>
+          <t>286141340</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3971,7 +3971,7 @@
         <v>20</v>
       </c>
       <c r="K72" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -3985,12 +3985,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>姚天杰</t>
+          <t>罗梦宇</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1003026879</t>
+          <t>1075569997</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4026,7 +4026,7 @@
         <v>20</v>
       </c>
       <c r="K73" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -4040,12 +4040,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>白永斌</t>
+          <t>姚天杰</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>256160060</t>
+          <t>1003026879</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵2</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4081,7 +4081,7 @@
         <v>20</v>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -4095,12 +4095,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>白启鹏</t>
+          <t>白永斌</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>284683276</t>
+          <t>256160060</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4136,7 +4136,7 @@
         <v>20</v>
       </c>
       <c r="K75" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -4150,12 +4150,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>谭欣海</t>
+          <t>白启鹏</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>287795932</t>
+          <t>284683276</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4191,7 +4191,7 @@
         <v>20</v>
       </c>
       <c r="K76" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -4205,12 +4205,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>张永生</t>
+          <t>谭欣海</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>308807828</t>
+          <t>287795932</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4246,7 +4246,7 @@
         <v>20</v>
       </c>
       <c r="K77" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -4301,7 +4301,7 @@
         <v>20</v>
       </c>
       <c r="K78" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -4535,12 +4535,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>郭栩</t>
+          <t>郭熙</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>265884340</t>
+          <t>1079452442</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4576,7 +4576,7 @@
         <v>20</v>
       </c>
       <c r="K83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -4590,12 +4590,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>殷啟成</t>
+          <t>郭栩</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1110070085</t>
+          <t>265884340</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4631,7 +4631,7 @@
         <v>20</v>
       </c>
       <c r="K84" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -4645,12 +4645,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>罗江元</t>
+          <t>殷啟成</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1049953338</t>
+          <t>1110070085</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4686,7 +4686,7 @@
         <v>20</v>
       </c>
       <c r="K85" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -4700,12 +4700,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>周春亮</t>
+          <t>罗江元</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1028562970</t>
+          <t>1049953338</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4741,7 +4741,7 @@
         <v>20</v>
       </c>
       <c r="K86" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -4755,12 +4755,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>李新龙</t>
+          <t>周春亮</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1097517309</t>
+          <t>1028562970</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4796,7 +4796,7 @@
         <v>20</v>
       </c>
       <c r="K87" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -4810,12 +4810,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>蒋丛华</t>
+          <t>徐俊杰</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>276619204</t>
+          <t>1019518033</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4851,7 +4851,7 @@
         <v>20</v>
       </c>
       <c r="K88" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -4865,12 +4865,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>郑云天</t>
+          <t>蒋丛华</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>309340812</t>
+          <t>276619204</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4906,7 +4906,7 @@
         <v>20</v>
       </c>
       <c r="K89" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -4920,12 +4920,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>李西</t>
+          <t>刀建华</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1127440078</t>
+          <t>330888580</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4961,7 +4961,7 @@
         <v>20</v>
       </c>
       <c r="K90" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -4975,12 +4975,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>刀思孟</t>
+          <t>郑云天</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1059874387</t>
+          <t>309340812</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5030,17 +5030,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>石改新</t>
+          <t>李西</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1035136982</t>
+          <t>1127440078</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>思茅蜂跑六队</t>
+          <t>思茅蜂跑五队</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5071,7 +5071,7 @@
         <v>20</v>
       </c>
       <c r="K92" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -5085,17 +5085,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>杨雄</t>
+          <t>刀思孟</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>303350396</t>
+          <t>1059874387</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>思茅蜂跑六队</t>
+          <t>思茅蜂跑五队</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5126,7 +5126,7 @@
         <v>20</v>
       </c>
       <c r="K93" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -5140,12 +5140,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>罗晓秋</t>
+          <t>王龙飞</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>277087084</t>
+          <t>330359444</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5195,12 +5195,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>李光泽</t>
+          <t>杨雄</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1069710126</t>
+          <t>303350396</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5236,7 +5236,7 @@
         <v>20</v>
       </c>
       <c r="K95" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
@@ -5305,12 +5305,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>刀悦</t>
+          <t>郑恩琦</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1137910044</t>
+          <t>1076905054</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>晚高峰、夜宵2、夜宵1</t>
+          <t>下午茶1、下午茶2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5346,7 +5346,7 @@
         <v>20</v>
       </c>
       <c r="K97" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
@@ -5360,12 +5360,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>紫龙标</t>
+          <t>刀悦</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1083595205</t>
+          <t>1137910044</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>晚高峰、夜宵2、夜宵1</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H98" t="n">
         <v>480</v>
@@ -5401,7 +5401,7 @@
         <v>20</v>
       </c>
       <c r="K98" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -5415,12 +5415,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>彭奇伟</t>
+          <t>陈旺</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1119321475</t>
+          <t>1148705026</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>凌晨1、午高峰、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5444,13 +5444,13 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
         <v>480</v>
       </c>
       <c r="I99" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
         <v>20</v>
@@ -5470,12 +5470,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>陈旺</t>
+          <t>王志明</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1148705026</t>
+          <t>1042930930</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>晚高峰、夜宵2、夜宵1</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5525,12 +5525,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>李进明</t>
+          <t>兰龙</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1123870054</t>
+          <t>1150771562</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>午高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5566,7 +5566,7 @@
         <v>20</v>
       </c>
       <c r="K101" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
@@ -5580,12 +5580,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>王志明</t>
+          <t>董俊才</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1042930930</t>
+          <t>1083956676</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>晚高峰、夜宵2、夜宵1</t>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5621,7 +5621,7 @@
         <v>20</v>
       </c>
       <c r="K102" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
@@ -5635,17 +5635,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>董俊才</t>
+          <t>刘智颖</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1083956676</t>
+          <t>298652316</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>思茅蜂跑六队</t>
+          <t>思茅蜂跑七队</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -5676,7 +5676,7 @@
         <v>20</v>
       </c>
       <c r="K103" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -5690,12 +5690,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>刘智颖</t>
+          <t>李建强</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>298652316</t>
+          <t>1108985115</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -5731,7 +5731,7 @@
         <v>20</v>
       </c>
       <c r="K104" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
@@ -5745,12 +5745,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>靳熙</t>
+          <t>罗成飞</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1090161529</t>
+          <t>217491379</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5786,7 +5786,7 @@
         <v>20</v>
       </c>
       <c r="K105" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L105" t="n">
         <v>0</v>
@@ -5800,12 +5800,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>罗成飞</t>
+          <t>罗庭坤</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>217491379</t>
+          <t>1019361639</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5841,7 +5841,7 @@
         <v>20</v>
       </c>
       <c r="K106" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -5855,12 +5855,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>罗庭坤</t>
+          <t>李勇康</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1019361639</t>
+          <t>1055750155</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5896,7 +5896,7 @@
         <v>20</v>
       </c>
       <c r="K107" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
@@ -5910,12 +5910,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>李勇康</t>
+          <t>郭皓嘉</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1055750155</t>
+          <t>1087266441</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5939,19 +5939,19 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="H108" t="n">
         <v>480</v>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J108" t="n">
         <v>20</v>
       </c>
       <c r="K108" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -5965,12 +5965,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>郭皓嘉</t>
+          <t>李二</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1087266441</t>
+          <t>90000334955228</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -5985,7 +5985,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -6006,7 +6006,7 @@
         <v>20</v>
       </c>
       <c r="K109" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -6020,12 +6020,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>李二</t>
+          <t>林光涛</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>90000334955228</t>
+          <t>1125257369</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -6061,7 +6061,7 @@
         <v>20</v>
       </c>
       <c r="K110" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
@@ -6075,17 +6075,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>付美依</t>
+          <t>胡飞</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1117870153</t>
+          <t>1154325068</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>思茅蜂跑七队</t>
+          <t>思茅蜂跑十队</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6116,7 +6116,7 @@
         <v>20</v>
       </c>
       <c r="K111" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
@@ -6130,17 +6130,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>林光涛</t>
+          <t>彭跃超</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1125257369</t>
+          <t>147529594</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>思茅蜂跑七队</t>
+          <t>思茅蜂跑十队</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵2</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -6171,7 +6171,7 @@
         <v>20</v>
       </c>
       <c r="K112" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -6185,12 +6185,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>李开平</t>
+          <t>陈柏宏</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1042226798</t>
+          <t>1121020019</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -6226,7 +6226,7 @@
         <v>20</v>
       </c>
       <c r="K113" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -6240,12 +6240,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>彭跃超</t>
+          <t>陈强</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>147529594</t>
+          <t>1059893263</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -6281,7 +6281,7 @@
         <v>20</v>
       </c>
       <c r="K114" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -6295,12 +6295,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>陈柏宏</t>
+          <t>白云春</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1121020019</t>
+          <t>1040532465</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -6336,7 +6336,7 @@
         <v>20</v>
       </c>
       <c r="K115" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
@@ -6350,12 +6350,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>陈强</t>
+          <t>李荣祝</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1059893263</t>
+          <t>293180284</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -6405,12 +6405,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>白云春</t>
+          <t>李嘎亮</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1040532465</t>
+          <t>1147310101</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -6446,7 +6446,7 @@
         <v>20</v>
       </c>
       <c r="K117" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -6460,12 +6460,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>李嘎亮</t>
+          <t>田宗平</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1147310101</t>
+          <t>1050830056</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -6501,7 +6501,7 @@
         <v>20</v>
       </c>
       <c r="K118" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -6515,12 +6515,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>田宗平</t>
+          <t>高梓菘</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>1050830056</t>
+          <t>1065535017</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -6556,7 +6556,7 @@
         <v>20</v>
       </c>
       <c r="K119" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -6570,12 +6570,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>高梓菘</t>
+          <t>周忠宽</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>1065535017</t>
+          <t>1154175029</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>早餐2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -6611,7 +6611,7 @@
         <v>20</v>
       </c>
       <c r="K120" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="L120" t="n">
         <v>0</v>
@@ -6625,12 +6625,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>周忠宽</t>
+          <t>凤玉兴</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>1154175029</t>
+          <t>1037531500</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -6645,22 +6645,22 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>早餐2、晚高峰、夜宵2</t>
+          <t>下午茶2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H121" t="n">
         <v>480</v>
       </c>
       <c r="I121" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J121" t="n">
         <v>20</v>
@@ -6669,7 +6669,7 @@
         <v>1</v>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M121" t="inlineStr">
         <is>
@@ -6680,12 +6680,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>罗诗洪</t>
+          <t>刀俊平</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>1091335309</t>
+          <t>1019636183</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -6721,7 +6721,7 @@
         <v>20</v>
       </c>
       <c r="K122" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
@@ -6776,7 +6776,7 @@
         <v>20</v>
       </c>
       <c r="K123" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
@@ -6831,7 +6831,7 @@
         <v>20</v>
       </c>
       <c r="K124" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
@@ -6845,12 +6845,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>罗开鑫</t>
+          <t>李真</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1149640115</t>
+          <t>1059999192</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6886,7 +6886,7 @@
         <v>20</v>
       </c>
       <c r="K125" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L125" t="n">
         <v>0</v>
@@ -6900,12 +6900,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>雷国松</t>
+          <t>王涛</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>214339123</t>
+          <t>1052831727</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6955,17 +6955,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>何忠文</t>
+          <t>马恩杰</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>1015977046</t>
+          <t>290446620</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>思茅蜂跑十一队</t>
+          <t>思茅蜂跑十三队</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6996,7 +6996,7 @@
         <v>20</v>
       </c>
       <c r="K127" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="L127" t="n">
         <v>0</v>
@@ -7010,17 +7010,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>岩仁</t>
+          <t>魏魁</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1156480048</t>
+          <t>1153735120</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>思茅蜂跑十一队</t>
+          <t>思茅蜂跑十三队</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -7051,7 +7051,7 @@
         <v>20</v>
       </c>
       <c r="K128" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L128" t="n">
         <v>0</v>
@@ -7065,17 +7065,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>王涛</t>
+          <t>徐红</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1052831727</t>
+          <t>1067685015</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>思茅蜂跑十一队</t>
+          <t>思茅蜂跑十三队</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -7106,7 +7106,7 @@
         <v>20</v>
       </c>
       <c r="K129" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="L129" t="n">
         <v>0</v>
@@ -7120,12 +7120,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>魏魁</t>
+          <t>罗金伟</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1153735120</t>
+          <t>1019360308</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -7161,7 +7161,7 @@
         <v>20</v>
       </c>
       <c r="K130" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L130" t="n">
         <v>0</v>
@@ -7175,12 +7175,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>徐红</t>
+          <t>李杰</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>1067685015</t>
+          <t>1035094629</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -7216,7 +7216,7 @@
         <v>20</v>
       </c>
       <c r="K131" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L131" t="n">
         <v>0</v>
@@ -7230,12 +7230,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>罗金伟</t>
+          <t>许英宝</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1019360308</t>
+          <t>1153845086</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -7271,7 +7271,7 @@
         <v>20</v>
       </c>
       <c r="K132" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="L132" t="n">
         <v>0</v>
@@ -7285,12 +7285,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>李杰</t>
+          <t>贺定军</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1035094629</t>
+          <t>1051380786</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -7326,7 +7326,7 @@
         <v>20</v>
       </c>
       <c r="K133" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L133" t="n">
         <v>0</v>
@@ -7340,12 +7340,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>许英宝</t>
+          <t>李续相</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1153845086</t>
+          <t>310243844</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -7381,7 +7381,7 @@
         <v>20</v>
       </c>
       <c r="K134" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L134" t="n">
         <v>0</v>
@@ -7395,12 +7395,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>贺定军</t>
+          <t>祝涛</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>1051380786</t>
+          <t>1019304138</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -7450,12 +7450,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>祝涛</t>
+          <t>阿开园</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>1019304138</t>
+          <t>1035449050</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -7505,12 +7505,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>阿开园</t>
+          <t>王俊</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>1035449050</t>
+          <t>303146764</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -7546,7 +7546,7 @@
         <v>20</v>
       </c>
       <c r="K137" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
@@ -7560,12 +7560,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>王俊</t>
+          <t>黄聪</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>303146764</t>
+          <t>1130305617</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>午高峰</t>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -7601,7 +7601,7 @@
         <v>20</v>
       </c>
       <c r="K138" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
@@ -7615,27 +7615,27 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>黄聪</t>
+          <t>杨晓强</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>1130305617</t>
+          <t>279931948</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>思茅蜂跑十三队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>蜂跑</t>
+          <t>优远</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -7656,7 +7656,7 @@
         <v>20</v>
       </c>
       <c r="K139" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
@@ -7670,12 +7670,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>杨晓强</t>
+          <t>白文斌</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>279931948</t>
+          <t>277601740</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -7711,7 +7711,7 @@
         <v>20</v>
       </c>
       <c r="K140" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -7725,12 +7725,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>鲁明春</t>
+          <t>彭思宸</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>1033936996</t>
+          <t>316377628</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -7766,7 +7766,7 @@
         <v>20</v>
       </c>
       <c r="K141" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -7780,12 +7780,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>白文斌</t>
+          <t>李光升</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>277601740</t>
+          <t>1112515464</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -7800,7 +7800,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -7821,7 +7821,7 @@
         <v>20</v>
       </c>
       <c r="K142" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
@@ -7835,12 +7835,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>彭思宸</t>
+          <t>杨云海</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>316377628</t>
+          <t>265785436</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -7890,12 +7890,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>李光升</t>
+          <t>李晓东</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>1112515464</t>
+          <t>312936500</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -7931,7 +7931,7 @@
         <v>20</v>
       </c>
       <c r="K144" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -8151,7 +8151,7 @@
         <v>20</v>
       </c>
       <c r="K148" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="L148" t="n">
         <v>0</v>
@@ -8165,12 +8165,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>魏启东</t>
+          <t>周正余</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>291727548</t>
+          <t>331435036</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -8206,7 +8206,7 @@
         <v>20</v>
       </c>
       <c r="K149" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L149" t="n">
         <v>0</v>
@@ -8220,12 +8220,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>邱龙涛</t>
+          <t>魏启东</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>328769468</t>
+          <t>291727548</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -8249,19 +8249,19 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="H150" t="n">
         <v>480</v>
       </c>
       <c r="I150" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J150" t="n">
         <v>20</v>
       </c>
       <c r="K150" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
@@ -8275,12 +8275,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>刀志鸿</t>
+          <t>兰情芳</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>308511236</t>
+          <t>90000338970244</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -8330,12 +8330,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>罗庆福</t>
+          <t>李童焘</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>265204452</t>
+          <t>1040564072</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>晚高峰</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -8371,7 +8371,7 @@
         <v>20</v>
       </c>
       <c r="K152" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -8385,12 +8385,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>李童焘</t>
+          <t>沈正阳</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>1040564072</t>
+          <t>1020850421</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>凌晨1、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -8414,19 +8414,19 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="H153" t="n">
         <v>480</v>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J153" t="n">
         <v>20</v>
       </c>
       <c r="K153" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L153" t="n">
         <v>0</v>
@@ -8440,12 +8440,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>沈正阳</t>
+          <t>祁杨</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>1020850421</t>
+          <t>277527332</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -8460,7 +8460,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -8481,7 +8481,7 @@
         <v>20</v>
       </c>
       <c r="K154" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L154" t="n">
         <v>0</v>
@@ -8495,12 +8495,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>祁杨</t>
+          <t>吴发春</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>277527332</t>
+          <t>1125257340</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -8536,7 +8536,7 @@
         <v>20</v>
       </c>
       <c r="K155" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L155" t="n">
         <v>0</v>
@@ -8550,12 +8550,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>陈会岭</t>
+          <t>李永福</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>202706747</t>
+          <t>313354908</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -8591,7 +8591,7 @@
         <v>20</v>
       </c>
       <c r="K156" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L156" t="n">
         <v>0</v>
@@ -8605,12 +8605,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>李祖顺</t>
+          <t>黄显龙</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>300606788</t>
+          <t>270399468</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -8634,19 +8634,19 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H157" t="n">
         <v>480</v>
       </c>
       <c r="I157" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J157" t="n">
         <v>20</v>
       </c>
       <c r="K157" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L157" t="n">
         <v>0</v>
@@ -8660,12 +8660,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>吴发春</t>
+          <t>朱原庆</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>1125257340</t>
+          <t>1090480333</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -8701,7 +8701,7 @@
         <v>20</v>
       </c>
       <c r="K158" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L158" t="n">
         <v>0</v>
@@ -8715,12 +8715,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>李永福</t>
+          <t>罗杰</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>313354908</t>
+          <t>291486188</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -8756,7 +8756,7 @@
         <v>20</v>
       </c>
       <c r="K159" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L159" t="n">
         <v>0</v>
@@ -8770,12 +8770,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>黄显龙</t>
+          <t>刀太勇</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>270399468</t>
+          <t>1051720597</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -8811,7 +8811,7 @@
         <v>20</v>
       </c>
       <c r="K160" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L160" t="n">
         <v>0</v>
@@ -8825,12 +8825,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>朱原庆</t>
+          <t>李健海</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>1090480333</t>
+          <t>330770764</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -8866,7 +8866,7 @@
         <v>20</v>
       </c>
       <c r="K161" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L161" t="n">
         <v>0</v>
@@ -8880,12 +8880,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>罗杰</t>
+          <t>吴海斌</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>291486188</t>
+          <t>1052004810</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -8935,17 +8935,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>佟露</t>
+          <t>匡伊雕</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>1016169126</t>
+          <t>324847356</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>思茅优远一队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -8990,17 +8990,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>刀太勇</t>
+          <t>李宏</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>1051720597</t>
+          <t>293086524</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>思茅优远一队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -9031,7 +9031,7 @@
         <v>20</v>
       </c>
       <c r="K164" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L164" t="n">
         <v>0</v>
@@ -9045,17 +9045,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>吴海斌</t>
+          <t>赵学初</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>1052004810</t>
+          <t>290252548</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>思茅优远一队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -9100,17 +9100,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>周铅超</t>
+          <t>李德生</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>157611867</t>
+          <t>1016030307</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>思茅优远一队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰、夜宵2</t>
+          <t>午高峰</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -9155,17 +9155,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>周杰宽</t>
+          <t>罗云照</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>241046795</t>
+          <t>297822572</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>思茅优远一队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -9180,11 +9180,11 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>在线</t>
+          <t>离线</t>
         </is>
       </c>
       <c r="G167" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H167" t="n">
         <v>480</v>
@@ -9196,10 +9196,10 @@
         <v>20</v>
       </c>
       <c r="K167" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L167" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M167" t="inlineStr">
         <is>
@@ -9210,12 +9210,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>匡伊雕</t>
+          <t>杨城鑫</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>324847356</t>
+          <t>1159670127</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -9251,7 +9251,7 @@
         <v>20</v>
       </c>
       <c r="K168" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L168" t="n">
         <v>0</v>
@@ -9265,12 +9265,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>李宏</t>
+          <t>王俊</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>293086524</t>
+          <t>317570748</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -9320,12 +9320,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>赵学初</t>
+          <t>王兵</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>290252548</t>
+          <t>330361220</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵2、夜宵1</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -9349,19 +9349,19 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H170" t="n">
         <v>480</v>
       </c>
       <c r="I170" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J170" t="n">
         <v>20</v>
       </c>
       <c r="K170" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L170" t="n">
         <v>0</v>
@@ -9375,12 +9375,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>李笙福</t>
+          <t>李正国</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>1115214416</t>
+          <t>261808524</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -9416,7 +9416,7 @@
         <v>20</v>
       </c>
       <c r="K171" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L171" t="n">
         <v>0</v>
@@ -9430,12 +9430,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>罗云照</t>
+          <t>张云强</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>297822572</t>
+          <t>1016211018</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -9450,7 +9450,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -9471,7 +9471,7 @@
         <v>20</v>
       </c>
       <c r="K172" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L172" t="n">
         <v>0</v>
@@ -9485,12 +9485,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>杨城鑫</t>
+          <t>王政元</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>1159670127</t>
+          <t>1034685238</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -9505,7 +9505,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -9526,7 +9526,7 @@
         <v>20</v>
       </c>
       <c r="K173" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L173" t="n">
         <v>0</v>
@@ -9540,12 +9540,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>王兵</t>
+          <t>罗师航</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>330361220</t>
+          <t>1092599780</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -9560,7 +9560,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵2、夜宵1</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -9581,7 +9581,7 @@
         <v>20</v>
       </c>
       <c r="K174" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L174" t="n">
         <v>0</v>
@@ -9595,12 +9595,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>李正国</t>
+          <t>张仲阳</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>261808524</t>
+          <t>273841420</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -9615,7 +9615,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -9636,7 +9636,7 @@
         <v>20</v>
       </c>
       <c r="K175" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L175" t="n">
         <v>0</v>
@@ -9650,12 +9650,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>张云强</t>
+          <t>王世奎</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>1016211018</t>
+          <t>320004748</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -9670,7 +9670,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -9705,17 +9705,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>王政元</t>
+          <t>罗坤</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>1034685238</t>
+          <t>1142045554</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -9746,7 +9746,7 @@
         <v>20</v>
       </c>
       <c r="K177" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L177" t="n">
         <v>0</v>
@@ -9760,17 +9760,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>罗师航</t>
+          <t>查懿原</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>1092599780</t>
+          <t>276165364</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、晚高峰、夜宵2、夜宵1</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -9801,7 +9801,7 @@
         <v>20</v>
       </c>
       <c r="K178" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L178" t="n">
         <v>0</v>
@@ -9815,17 +9815,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>石福</t>
+          <t>李星龙</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>282612804</t>
+          <t>1090430076</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>晚高峰</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -9856,7 +9856,7 @@
         <v>20</v>
       </c>
       <c r="K179" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L179" t="n">
         <v>0</v>
@@ -9870,17 +9870,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>张仲阳</t>
+          <t>唐涛</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>273841420</t>
+          <t>277946036</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -9925,17 +9925,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>王世奎</t>
+          <t>李海瑞</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>320004748</t>
+          <t>1129764787</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -9945,7 +9945,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -9966,7 +9966,7 @@
         <v>20</v>
       </c>
       <c r="K181" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L181" t="n">
         <v>0</v>
@@ -9980,17 +9980,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>李德生</t>
+          <t>钱学林</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>1016030307</t>
+          <t>1130041012</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -10000,28 +10000,28 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>午高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>在线</t>
+          <t>离线</t>
         </is>
       </c>
       <c r="G182" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H182" t="n">
         <v>480</v>
       </c>
       <c r="I182" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J182" t="n">
         <v>20</v>
       </c>
       <c r="K182" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L182" t="n">
         <v>0</v>
@@ -10035,12 +10035,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>罗坤</t>
+          <t>白顺荣</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>1142045554</t>
+          <t>1045718631</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -10076,7 +10076,7 @@
         <v>20</v>
       </c>
       <c r="K183" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L183" t="n">
         <v>0</v>
@@ -10090,12 +10090,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>查懿原</t>
+          <t>周明权</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>276165364</t>
+          <t>1158625019</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵2、夜宵1</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -10145,12 +10145,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>李星龙</t>
+          <t>曾平</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>1090430076</t>
+          <t>1143782010</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -10186,7 +10186,7 @@
         <v>20</v>
       </c>
       <c r="K185" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L185" t="n">
         <v>0</v>
@@ -10200,12 +10200,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>唐涛</t>
+          <t>梁祖恩</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>277946036</t>
+          <t>1069696308</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -10241,7 +10241,7 @@
         <v>20</v>
       </c>
       <c r="K186" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L186" t="n">
         <v>0</v>
@@ -10255,12 +10255,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>李海瑞</t>
+          <t>罗杰</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>1129764787</t>
+          <t>1142566401</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -10275,7 +10275,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -10296,7 +10296,7 @@
         <v>20</v>
       </c>
       <c r="K187" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L187" t="n">
         <v>0</v>
@@ -10310,12 +10310,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>钱学林</t>
+          <t>罗文婷</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>1130041012</t>
+          <t>280481452</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -10330,7 +10330,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -10351,7 +10351,7 @@
         <v>20</v>
       </c>
       <c r="K188" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L188" t="n">
         <v>0</v>
@@ -10365,12 +10365,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>白顺荣</t>
+          <t>袁翊博</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>1045718631</t>
+          <t>1145707189</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -10406,7 +10406,7 @@
         <v>20</v>
       </c>
       <c r="K189" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L189" t="n">
         <v>0</v>
@@ -10420,17 +10420,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>周明权</t>
+          <t>邓迪社</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>1158625019</t>
+          <t>221905563</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远五队</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、晚高峰、夜宵2、夜宵1</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -10449,7 +10449,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H190" t="n">
         <v>480</v>
@@ -10475,17 +10475,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>曾平</t>
+          <t>熊远发</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>1143782010</t>
+          <t>266314300</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远五队</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -10495,7 +10495,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -10516,7 +10516,7 @@
         <v>20</v>
       </c>
       <c r="K191" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L191" t="n">
         <v>0</v>
@@ -10530,17 +10530,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>梁祖恩</t>
+          <t>黄健翔</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>1069696308</t>
+          <t>1071071679</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远五队</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -10550,7 +10550,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -10571,7 +10571,7 @@
         <v>20</v>
       </c>
       <c r="K192" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L192" t="n">
         <v>0</v>
@@ -10585,17 +10585,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>付林臣</t>
+          <t>张鹏</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>1024206523</t>
+          <t>1028523558</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远五队</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -10626,7 +10626,7 @@
         <v>20</v>
       </c>
       <c r="K193" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="L193" t="n">
         <v>0</v>
@@ -10640,17 +10640,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>罗杰</t>
+          <t>杨双辉</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>1142566401</t>
+          <t>264798596</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远五队</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -10660,7 +10660,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -10681,7 +10681,7 @@
         <v>20</v>
       </c>
       <c r="K194" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L194" t="n">
         <v>0</v>
@@ -10695,17 +10695,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>罗文婷</t>
+          <t>肖滔滔</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>280481452</t>
+          <t>270093300</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远五队</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -10715,7 +10715,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -10736,7 +10736,7 @@
         <v>20</v>
       </c>
       <c r="K195" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L195" t="n">
         <v>0</v>
@@ -10750,17 +10750,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>袁翊博</t>
+          <t>普红兵</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>1145707189</t>
+          <t>277529860</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远五队</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -10791,7 +10791,7 @@
         <v>20</v>
       </c>
       <c r="K196" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L196" t="n">
         <v>0</v>
@@ -10805,12 +10805,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>邓迪社</t>
+          <t>罗俊杰</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>221905563</t>
+          <t>1096790672</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵2、夜宵1</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -10860,12 +10860,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>熊远发</t>
+          <t>匡一鸣</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>266314300</t>
+          <t>90000340722076</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -10901,7 +10901,7 @@
         <v>20</v>
       </c>
       <c r="K198" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L198" t="n">
         <v>0</v>
@@ -10915,12 +10915,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>黄健翔</t>
+          <t>彭毅勇</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>1071071679</t>
+          <t>175204387</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -10956,7 +10956,7 @@
         <v>20</v>
       </c>
       <c r="K199" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L199" t="n">
         <v>0</v>
@@ -10970,12 +10970,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>张鹏</t>
+          <t>陈明源</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>1028523558</t>
+          <t>277124636</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -10990,7 +10990,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -11011,7 +11011,7 @@
         <v>20</v>
       </c>
       <c r="K200" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L200" t="n">
         <v>0</v>
@@ -11025,12 +11025,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>杨双辉</t>
+          <t>李清林</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>264798596</t>
+          <t>266695804</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -11066,7 +11066,7 @@
         <v>20</v>
       </c>
       <c r="K201" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="L201" t="n">
         <v>0</v>
@@ -11080,12 +11080,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>陈晓林</t>
+          <t>杨静修</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>278941292</t>
+          <t>281365980</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -11121,7 +11121,7 @@
         <v>20</v>
       </c>
       <c r="K202" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="L202" t="n">
         <v>0</v>
@@ -11135,12 +11135,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>肖滔滔</t>
+          <t>陈新文</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>270093300</t>
+          <t>266350460</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵2、夜宵1</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -11176,7 +11176,7 @@
         <v>20</v>
       </c>
       <c r="K203" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L203" t="n">
         <v>0</v>
@@ -11190,12 +11190,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>普红兵</t>
+          <t>罗文龙</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>277529860</t>
+          <t>173435307</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -11210,7 +11210,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -11231,7 +11231,7 @@
         <v>20</v>
       </c>
       <c r="K204" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L204" t="n">
         <v>0</v>
@@ -11245,12 +11245,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>罗俊杰</t>
+          <t>王仕臣</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>1096790672</t>
+          <t>1043620937</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -11265,7 +11265,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -11286,7 +11286,7 @@
         <v>20</v>
       </c>
       <c r="K205" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L205" t="n">
         <v>0</v>
@@ -11300,12 +11300,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>匡一鸣</t>
+          <t>李杰彪</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>90000340722076</t>
+          <t>279705460</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -11329,19 +11329,19 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H206" t="n">
         <v>480</v>
       </c>
       <c r="I206" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J206" t="n">
         <v>20</v>
       </c>
       <c r="K206" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L206" t="n">
         <v>0</v>
@@ -11355,12 +11355,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>彭毅勇</t>
+          <t>陶树良</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>175204387</t>
+          <t>278115308</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -11375,7 +11375,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -11396,507 +11396,12 @@
         <v>20</v>
       </c>
       <c r="K207" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L207" t="n">
         <v>0</v>
       </c>
       <c r="M207" t="inlineStr">
-        <is>
-          <t>预计达标</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>夏彪</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>278430252</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>思茅优远五队</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>优远</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>离线</t>
-        </is>
-      </c>
-      <c r="G208" t="n">
-        <v>0</v>
-      </c>
-      <c r="H208" t="n">
-        <v>480</v>
-      </c>
-      <c r="I208" t="n">
-        <v>0</v>
-      </c>
-      <c r="J208" t="n">
-        <v>20</v>
-      </c>
-      <c r="K208" t="n">
-        <v>12</v>
-      </c>
-      <c r="L208" t="n">
-        <v>0</v>
-      </c>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>预计达标</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>孙帅</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>227759883</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>思茅优远五队</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>优远</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>离线</t>
-        </is>
-      </c>
-      <c r="G209" t="n">
-        <v>0</v>
-      </c>
-      <c r="H209" t="n">
-        <v>480</v>
-      </c>
-      <c r="I209" t="n">
-        <v>0</v>
-      </c>
-      <c r="J209" t="n">
-        <v>20</v>
-      </c>
-      <c r="K209" t="n">
-        <v>5</v>
-      </c>
-      <c r="L209" t="n">
-        <v>0</v>
-      </c>
-      <c r="M209" t="inlineStr">
-        <is>
-          <t>预计达标</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>自银号</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>1086868625</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>思茅优远五队</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>优远</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>午高峰、晚高峰、夜宵2、夜宵1</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>离线</t>
-        </is>
-      </c>
-      <c r="G210" t="n">
-        <v>0</v>
-      </c>
-      <c r="H210" t="n">
-        <v>480</v>
-      </c>
-      <c r="I210" t="n">
-        <v>0</v>
-      </c>
-      <c r="J210" t="n">
-        <v>20</v>
-      </c>
-      <c r="K210" t="n">
-        <v>1</v>
-      </c>
-      <c r="L210" t="n">
-        <v>0</v>
-      </c>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>预计达标</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>杨静修</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>281365980</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>思茅优远五队</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>优远</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>离线</t>
-        </is>
-      </c>
-      <c r="G211" t="n">
-        <v>0</v>
-      </c>
-      <c r="H211" t="n">
-        <v>480</v>
-      </c>
-      <c r="I211" t="n">
-        <v>0</v>
-      </c>
-      <c r="J211" t="n">
-        <v>20</v>
-      </c>
-      <c r="K211" t="n">
-        <v>13</v>
-      </c>
-      <c r="L211" t="n">
-        <v>0</v>
-      </c>
-      <c r="M211" t="inlineStr">
-        <is>
-          <t>预计达标</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>郭莉萍</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>276709156</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>思茅优远五队</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>优远</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>离线</t>
-        </is>
-      </c>
-      <c r="G212" t="n">
-        <v>0</v>
-      </c>
-      <c r="H212" t="n">
-        <v>480</v>
-      </c>
-      <c r="I212" t="n">
-        <v>0</v>
-      </c>
-      <c r="J212" t="n">
-        <v>20</v>
-      </c>
-      <c r="K212" t="n">
-        <v>8</v>
-      </c>
-      <c r="L212" t="n">
-        <v>0</v>
-      </c>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>预计达标</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>罗文龙</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>173435307</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>思茅优远五队</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>优远</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>午高峰、下午茶2、晚高峰</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>离线</t>
-        </is>
-      </c>
-      <c r="G213" t="n">
-        <v>0</v>
-      </c>
-      <c r="H213" t="n">
-        <v>480</v>
-      </c>
-      <c r="I213" t="n">
-        <v>0</v>
-      </c>
-      <c r="J213" t="n">
-        <v>20</v>
-      </c>
-      <c r="K213" t="n">
-        <v>15</v>
-      </c>
-      <c r="L213" t="n">
-        <v>0</v>
-      </c>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t>预计达标</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>王仕臣</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>1043620937</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>思茅优远五队</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>优远</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>离线</t>
-        </is>
-      </c>
-      <c r="G214" t="n">
-        <v>0</v>
-      </c>
-      <c r="H214" t="n">
-        <v>480</v>
-      </c>
-      <c r="I214" t="n">
-        <v>0</v>
-      </c>
-      <c r="J214" t="n">
-        <v>20</v>
-      </c>
-      <c r="K214" t="n">
-        <v>1</v>
-      </c>
-      <c r="L214" t="n">
-        <v>0</v>
-      </c>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>预计达标</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>李杰彪</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>279705460</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>思茅优远五队</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>优远</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>午高峰</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>离线</t>
-        </is>
-      </c>
-      <c r="G215" t="n">
-        <v>0</v>
-      </c>
-      <c r="H215" t="n">
-        <v>480</v>
-      </c>
-      <c r="I215" t="n">
-        <v>0</v>
-      </c>
-      <c r="J215" t="n">
-        <v>20</v>
-      </c>
-      <c r="K215" t="n">
-        <v>8</v>
-      </c>
-      <c r="L215" t="n">
-        <v>0</v>
-      </c>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>预计达标</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>陶树良</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>278115308</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>思茅优远五队</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>优远</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>离线</t>
-        </is>
-      </c>
-      <c r="G216" t="n">
-        <v>0</v>
-      </c>
-      <c r="H216" t="n">
-        <v>480</v>
-      </c>
-      <c r="I216" t="n">
-        <v>0</v>
-      </c>
-      <c r="J216" t="n">
-        <v>20</v>
-      </c>
-      <c r="K216" t="n">
-        <v>8</v>
-      </c>
-      <c r="L216" t="n">
-        <v>0</v>
-      </c>
-      <c r="M216" t="inlineStr">
         <is>
           <t>预计达标</t>
         </is>

--- a/public/monitor_latest.xlsx
+++ b/public/monitor_latest.xlsx
@@ -121,7 +121,7 @@
         <v>20</v>
       </c>
       <c r="K2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -135,12 +135,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>邓成毅</t>
+          <t>苏亚春</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1043170062</t>
+          <t>283451844</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -176,7 +176,7 @@
         <v>20</v>
       </c>
       <c r="K3" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -190,12 +190,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>苏亚春</t>
+          <t>李翠伟</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>283451844</t>
+          <t>1049933839</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -210,7 +210,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -231,7 +231,7 @@
         <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -245,12 +245,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>李翠伟</t>
+          <t>杨海轮</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1049933839</t>
+          <t>290558268</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -300,12 +300,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>杨海轮</t>
+          <t>田新宾</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>290558268</t>
+          <t>279429852</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -320,7 +320,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -341,7 +341,7 @@
         <v>20</v>
       </c>
       <c r="K6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -355,12 +355,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>田新宾</t>
+          <t>杨思杰</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>279429852</t>
+          <t>1082260013</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -375,7 +375,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -396,7 +396,7 @@
         <v>20</v>
       </c>
       <c r="K7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -410,12 +410,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>杨思杰</t>
+          <t>陈维富</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1082260013</t>
+          <t>270698852</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -430,7 +430,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>凌晨1、凌晨2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -439,7 +439,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>480</v>
@@ -451,7 +451,7 @@
         <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -506,7 +506,7 @@
         <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -561,7 +561,7 @@
         <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -575,12 +575,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>胡关浚</t>
+          <t>朱健明</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>261536156</t>
+          <t>1013523131</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -600,26 +600,26 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>在线</t>
+          <t>离线</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>480</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -630,12 +630,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>陈维富</t>
+          <t>胡关浚</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>270698852</t>
+          <t>261536156</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>凌晨1、凌晨2</t>
+          <t>午高峰、晚高峰、夜宵2、夜宵1</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>480</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>20</v>
@@ -674,7 +674,7 @@
         <v>15</v>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>夜宵2</t>
+          <t>早餐2</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -740,12 +740,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>张文平</t>
+          <t>汤亚东</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>316521756</t>
+          <t>313288188</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -795,12 +795,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>李世坚</t>
+          <t>张文平</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1124817963</t>
+          <t>316521756</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -836,7 +836,7 @@
         <v>20</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -850,12 +850,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>李金威</t>
+          <t>李世坚</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>281910660</t>
+          <t>1124817963</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵2、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -891,7 +891,7 @@
         <v>20</v>
       </c>
       <c r="K16" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -905,12 +905,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>熊正存</t>
+          <t>马豪</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1070938748</t>
+          <t>1086929921</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -946,7 +946,7 @@
         <v>20</v>
       </c>
       <c r="K17" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>马豪</t>
+          <t>罗宗辉</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1086929921</t>
+          <t>90000338986940</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1001,7 +1001,7 @@
         <v>20</v>
       </c>
       <c r="K18" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1015,12 +1015,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>罗宗辉</t>
+          <t>董宇</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>90000338986940</t>
+          <t>1040981176</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>董宇</t>
+          <t>陶伊翔</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1040981176</t>
+          <t>1110435691</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1111,7 +1111,7 @@
         <v>20</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1125,12 +1125,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>陶伊翔</t>
+          <t>鲁炫</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1110435691</t>
+          <t>90000339224588</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1166,7 +1166,7 @@
         <v>20</v>
       </c>
       <c r="K21" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>下午茶1、下午茶2、晚高峰、夜宵2</t>
+          <t>下午茶2</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1290,12 +1290,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>杨绍元</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1042321509</t>
+          <t>264801124</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1331,7 +1331,7 @@
         <v>20</v>
       </c>
       <c r="K24" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -1345,12 +1345,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>杨福云</t>
+          <t>汪宗兵</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1156896791</t>
+          <t>1037848475</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1386,7 +1386,7 @@
         <v>20</v>
       </c>
       <c r="K25" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -1400,12 +1400,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>杨绍元</t>
+          <t>王朝顺</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>264801124</t>
+          <t>287127412</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1455,12 +1455,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>汪宗兵</t>
+          <t>鲍国明</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1037848475</t>
+          <t>1087319378</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>凌晨1、凌晨2、凌晨3、夜宵1</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1496,7 +1496,7 @@
         <v>20</v>
       </c>
       <c r="K27" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -1510,12 +1510,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>王朝顺</t>
+          <t>王武斌</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>287127412</t>
+          <t>300824396</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1551,7 +1551,7 @@
         <v>20</v>
       </c>
       <c r="K28" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -1565,12 +1565,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>鲍德斌</t>
+          <t>施发龙</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>317794948</t>
+          <t>1060067605</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、晚高峰、夜宵2、夜宵1</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1620,12 +1620,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>王武斌</t>
+          <t>李金威</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>300824396</t>
+          <t>281910660</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、晚高峰、夜宵2、夜宵1</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1661,7 +1661,7 @@
         <v>20</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -1675,17 +1675,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>施发龙</t>
+          <t>杨建国</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1060067605</t>
+          <t>1138840186</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>思茅优选二队</t>
+          <t>思茅优选三队</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵2、夜宵1</t>
+          <t>凌晨1、凌晨2、凌晨3、夜宵1</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1730,17 +1730,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>鲍国明</t>
+          <t>李海斌</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1087319378</t>
+          <t>90000335390900</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>思茅优选二队</t>
+          <t>思茅优选三队</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1750,22 +1750,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>凌晨1、凌晨2、凌晨3、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>在线</t>
+          <t>离线</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>480</v>
       </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>20</v>
@@ -1774,7 +1774,7 @@
         <v>15</v>
       </c>
       <c r="L32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -1840,12 +1840,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>普李叶</t>
+          <t>胡锦波</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1019684446</t>
+          <t>316835700</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>凌晨1、凌晨2、凌晨3、夜宵1</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1881,7 +1881,7 @@
         <v>20</v>
       </c>
       <c r="K34" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -1895,12 +1895,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>佟奇</t>
+          <t>普李叶</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>90000336291956</t>
+          <t>1019684446</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1936,7 +1936,7 @@
         <v>20</v>
       </c>
       <c r="K35" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -1950,12 +1950,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>李健伟</t>
+          <t>佟奇</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>264431676</t>
+          <t>90000336291956</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>下午茶1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1991,7 +1991,7 @@
         <v>20</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -2005,12 +2005,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>农光应</t>
+          <t>李健伟</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1142610772</t>
+          <t>264431676</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>下午茶1</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2046,7 +2046,7 @@
         <v>20</v>
       </c>
       <c r="K37" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -2060,12 +2060,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>龙峰</t>
+          <t>农光应</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1087320804</t>
+          <t>1142610772</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2101,7 +2101,7 @@
         <v>20</v>
       </c>
       <c r="K38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -2115,12 +2115,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>赵兴跃</t>
+          <t>龙峰</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1045086221</t>
+          <t>1087320804</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>午高峰</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2156,7 +2156,7 @@
         <v>20</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -2170,12 +2170,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>鲍家伟</t>
+          <t>赵兴跃</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1069055452</t>
+          <t>1045086221</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2190,31 +2190,31 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>凌晨1、凌晨2、凌晨3、夜宵1</t>
+          <t>午高峰</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>在线</t>
+          <t>离线</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>480</v>
       </c>
       <c r="I40" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
         <v>20</v>
       </c>
       <c r="K40" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>杨建国</t>
+          <t>鲍家伟</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1138840186</t>
+          <t>1069055452</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2254,22 +2254,22 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>480</v>
       </c>
       <c r="I41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>20</v>
       </c>
       <c r="K41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -2280,51 +2280,51 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>胡锦波</t>
+          <t>罗佳杨</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>316835700</t>
+          <t>289157644</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>思茅优选三队</t>
+          <t>思茅蜂跑一队</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>优选</t>
+          <t>蜂跑</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>凌晨1、凌晨2、凌晨3、夜宵1</t>
+          <t>午高峰、下午茶1、夜宵2</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>在线</t>
+          <t>离线</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>480</v>
       </c>
       <c r="I42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>20</v>
       </c>
       <c r="K42" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -2335,12 +2335,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>罗佳杨</t>
+          <t>李新田</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>289157644</t>
+          <t>320683868</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2390,12 +2390,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>李新田</t>
+          <t>赵文俊</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>320683868</t>
+          <t>1019362134</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰、夜宵2</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2431,7 +2431,7 @@
         <v>20</v>
       </c>
       <c r="K44" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -2445,12 +2445,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>赵文俊</t>
+          <t>郑荣建</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1019362134</t>
+          <t>307784220</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2486,7 +2486,7 @@
         <v>20</v>
       </c>
       <c r="K45" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -2500,12 +2500,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>郑荣建</t>
+          <t>车俊超</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>307784220</t>
+          <t>291997260</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>下午茶1、下午茶2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2541,7 +2541,7 @@
         <v>20</v>
       </c>
       <c r="K46" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -2555,12 +2555,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>袁洲</t>
+          <t>张忠海</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>332120988</t>
+          <t>1003950027</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰、夜宵2</t>
+          <t>早餐2、午高峰</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2596,7 +2596,7 @@
         <v>20</v>
       </c>
       <c r="K47" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -2706,7 +2706,7 @@
         <v>20</v>
       </c>
       <c r="K49" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -2720,12 +2720,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>者少军</t>
+          <t>王金林</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>261859444</t>
+          <t>1125678007</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2775,17 +2775,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>罗晨龙</t>
+          <t>者少军</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>293959380</t>
+          <t>261859444</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>思茅蜂跑三队</t>
+          <t>思茅蜂跑一队</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>下午茶2、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -2816,7 +2816,7 @@
         <v>20</v>
       </c>
       <c r="K51" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -2830,12 +2830,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>朱加林</t>
+          <t>罗晨龙</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>186839747</t>
+          <t>293959380</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>下午茶2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2871,7 +2871,7 @@
         <v>20</v>
       </c>
       <c r="K52" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -2885,12 +2885,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>张小华</t>
+          <t>朱加林</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>317756532</t>
+          <t>186839747</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2926,7 +2926,7 @@
         <v>20</v>
       </c>
       <c r="K53" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -2940,12 +2940,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>蓝琨</t>
+          <t>张小华</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1070814423</t>
+          <t>317756532</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2981,7 +2981,7 @@
         <v>20</v>
       </c>
       <c r="K54" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -2995,12 +2995,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>王东奎</t>
+          <t>蓝琨</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1042700176</t>
+          <t>1070814423</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>下午茶2、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3036,7 +3036,7 @@
         <v>20</v>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -3050,12 +3050,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>金富勤</t>
+          <t>王东奎</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>615466374</t>
+          <t>1042700176</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>下午茶2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3091,7 +3091,7 @@
         <v>20</v>
       </c>
       <c r="K56" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -3105,12 +3105,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>陈少平</t>
+          <t>钱思安</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1015826982</t>
+          <t>289601204</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3146,7 +3146,7 @@
         <v>20</v>
       </c>
       <c r="K57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -3160,12 +3160,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>李旺坤</t>
+          <t>金富勤</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1052121306</t>
+          <t>615466374</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3201,7 +3201,7 @@
         <v>20</v>
       </c>
       <c r="K58" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -3215,12 +3215,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>白凯勇</t>
+          <t>陈少平</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1092736925</t>
+          <t>1015826982</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>下午茶2、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3256,7 +3256,7 @@
         <v>20</v>
       </c>
       <c r="K59" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -3270,12 +3270,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>金锐</t>
+          <t>李旺坤</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>292657164</t>
+          <t>1052121306</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>下午茶2、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3311,7 +3311,7 @@
         <v>20</v>
       </c>
       <c r="K60" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -3325,12 +3325,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>刘钦臣</t>
+          <t>金锐</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>332133620</t>
+          <t>292657164</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、夜宵2</t>
+          <t>下午茶2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3366,7 +3366,7 @@
         <v>20</v>
       </c>
       <c r="K61" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -3380,17 +3380,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>何彪</t>
+          <t>刘钦臣</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>511001013</t>
+          <t>332133620</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>思茅蜂跑四队</t>
+          <t>思茅蜂跑三队</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶2、夜宵2</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3421,7 +3421,7 @@
         <v>20</v>
       </c>
       <c r="K62" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -3435,17 +3435,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>毕航</t>
+          <t>白凯勇</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>325067300</t>
+          <t>1092736925</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>思茅蜂跑四队</t>
+          <t>思茅蜂跑三队</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>下午茶2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -3476,7 +3476,7 @@
         <v>20</v>
       </c>
       <c r="K63" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -3490,12 +3490,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>苏志国</t>
+          <t>何彪</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1011062500</t>
+          <t>511001013</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3531,7 +3531,7 @@
         <v>20</v>
       </c>
       <c r="K64" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -3545,12 +3545,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>李院辉</t>
+          <t>毕航</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1140485075</t>
+          <t>325067300</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3586,7 +3586,7 @@
         <v>20</v>
       </c>
       <c r="K65" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -3600,12 +3600,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>陶改荣</t>
+          <t>苏志国</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1102455067</t>
+          <t>1011062500</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3641,7 +3641,7 @@
         <v>20</v>
       </c>
       <c r="K66" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -3655,12 +3655,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>毕朝军</t>
+          <t>李院辉</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>90000334561228</t>
+          <t>1140485075</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>午高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3696,7 +3696,7 @@
         <v>20</v>
       </c>
       <c r="K67" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -3710,12 +3710,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>段文斌</t>
+          <t>陶改荣</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>280124636</t>
+          <t>1102455067</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3751,7 +3751,7 @@
         <v>20</v>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -3765,12 +3765,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>施圆章</t>
+          <t>毕朝军</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>261823124</t>
+          <t>90000334561228</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3806,7 +3806,7 @@
         <v>20</v>
       </c>
       <c r="K69" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -3820,12 +3820,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>毛勇</t>
+          <t>段文斌</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1044060042</t>
+          <t>280124636</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3861,7 +3861,7 @@
         <v>20</v>
       </c>
       <c r="K70" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -3875,12 +3875,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>罗晓余</t>
+          <t>毛勇</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1150777253</t>
+          <t>1044060042</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3916,7 +3916,7 @@
         <v>20</v>
       </c>
       <c r="K71" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -3930,12 +3930,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>李晓春</t>
+          <t>罗晓余</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>286141340</t>
+          <t>1150777253</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3971,7 +3971,7 @@
         <v>20</v>
       </c>
       <c r="K72" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -3985,12 +3985,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>罗梦宇</t>
+          <t>李晓春</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1075569997</t>
+          <t>286141340</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4026,7 +4026,7 @@
         <v>20</v>
       </c>
       <c r="K73" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>20</v>
       </c>
       <c r="K74" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -4136,7 +4136,7 @@
         <v>20</v>
       </c>
       <c r="K75" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -4260,12 +4260,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>郭成红</t>
+          <t>张永生</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>277421812</t>
+          <t>308807828</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4301,7 +4301,7 @@
         <v>20</v>
       </c>
       <c r="K78" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -4315,12 +4315,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>李冬杰</t>
+          <t>郭成红</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>328840900</t>
+          <t>277421812</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4356,7 +4356,7 @@
         <v>20</v>
       </c>
       <c r="K79" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -4370,17 +4370,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>郭朝坤</t>
+          <t>李冬杰</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>187384715</t>
+          <t>328840900</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>思茅蜂跑五队</t>
+          <t>思茅蜂跑四队</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4411,7 +4411,7 @@
         <v>20</v>
       </c>
       <c r="K80" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -4425,12 +4425,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>李子平</t>
+          <t>郭朝坤</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>285715108</t>
+          <t>187384715</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4466,7 +4466,7 @@
         <v>20</v>
       </c>
       <c r="K81" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -4480,12 +4480,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>曾宏飞</t>
+          <t>李子平</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1045088102</t>
+          <t>285715108</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4521,7 +4521,7 @@
         <v>20</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -4535,12 +4535,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>郭熙</t>
+          <t>曾宏飞</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1079452442</t>
+          <t>1045088102</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4576,7 +4576,7 @@
         <v>20</v>
       </c>
       <c r="K83" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -4590,12 +4590,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>郭栩</t>
+          <t>郭熙</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>265884340</t>
+          <t>1079452442</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4631,7 +4631,7 @@
         <v>20</v>
       </c>
       <c r="K84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -4645,12 +4645,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>殷啟成</t>
+          <t>郭栩</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1110070085</t>
+          <t>265884340</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4686,7 +4686,7 @@
         <v>20</v>
       </c>
       <c r="K85" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -4700,12 +4700,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>罗江元</t>
+          <t>殷啟成</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1049953338</t>
+          <t>1110070085</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4741,7 +4741,7 @@
         <v>20</v>
       </c>
       <c r="K86" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -4755,12 +4755,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>周春亮</t>
+          <t>罗江元</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1028562970</t>
+          <t>1049953338</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4796,7 +4796,7 @@
         <v>20</v>
       </c>
       <c r="K87" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -4810,12 +4810,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>徐俊杰</t>
+          <t>周春亮</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1019518033</t>
+          <t>1028562970</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4851,7 +4851,7 @@
         <v>20</v>
       </c>
       <c r="K88" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -4865,12 +4865,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>蒋丛华</t>
+          <t>徐俊杰</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>276619204</t>
+          <t>1019518033</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4906,7 +4906,7 @@
         <v>20</v>
       </c>
       <c r="K89" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -4920,12 +4920,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>刀建华</t>
+          <t>李新龙</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>330888580</t>
+          <t>1097517309</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4961,7 +4961,7 @@
         <v>20</v>
       </c>
       <c r="K90" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -4975,12 +4975,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>郑云天</t>
+          <t>蒋丛华</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>309340812</t>
+          <t>276619204</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5016,7 +5016,7 @@
         <v>20</v>
       </c>
       <c r="K91" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -5030,12 +5030,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>李西</t>
+          <t>刀建华</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1127440078</t>
+          <t>330888580</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5071,7 +5071,7 @@
         <v>20</v>
       </c>
       <c r="K92" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -5085,12 +5085,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>刀思孟</t>
+          <t>郑云天</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1059874387</t>
+          <t>309340812</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5140,17 +5140,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>王龙飞</t>
+          <t>李西</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>330359444</t>
+          <t>1127440078</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>思茅蜂跑六队</t>
+          <t>思茅蜂跑五队</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5181,7 +5181,7 @@
         <v>20</v>
       </c>
       <c r="K94" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
@@ -5195,17 +5195,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>杨雄</t>
+          <t>刀思孟</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>303350396</t>
+          <t>1059874387</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>思茅蜂跑六队</t>
+          <t>思茅蜂跑五队</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5236,7 +5236,7 @@
         <v>20</v>
       </c>
       <c r="K95" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
@@ -5250,12 +5250,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>张韩斌</t>
+          <t>王龙飞</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1123350074</t>
+          <t>330359444</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5305,12 +5305,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>郑恩琦</t>
+          <t>石改新</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1076905054</t>
+          <t>1035136982</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>下午茶1、下午茶2、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5346,7 +5346,7 @@
         <v>20</v>
       </c>
       <c r="K97" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
@@ -5360,12 +5360,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>刀悦</t>
+          <t>杨雄</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1137910044</t>
+          <t>303350396</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>晚高峰、夜宵2、夜宵1</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H98" t="n">
         <v>480</v>
@@ -5401,7 +5401,7 @@
         <v>20</v>
       </c>
       <c r="K98" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -5415,12 +5415,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>陈旺</t>
+          <t>罗晓秋</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1148705026</t>
+          <t>277087084</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5470,12 +5470,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>王志明</t>
+          <t>李光泽</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1042930930</t>
+          <t>1069710126</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>晚高峰、夜宵2、夜宵1</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5511,7 +5511,7 @@
         <v>20</v>
       </c>
       <c r="K100" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -5525,12 +5525,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>兰龙</t>
+          <t>张韩斌</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1150771562</t>
+          <t>1123350074</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5566,7 +5566,7 @@
         <v>20</v>
       </c>
       <c r="K101" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
@@ -5580,12 +5580,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>董俊才</t>
+          <t>郑恩琦</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1083956676</t>
+          <t>1076905054</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>下午茶1、下午茶2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5621,7 +5621,7 @@
         <v>20</v>
       </c>
       <c r="K102" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
@@ -5635,17 +5635,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>刘智颖</t>
+          <t>刀悦</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>298652316</t>
+          <t>1137910044</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>思茅蜂跑七队</t>
+          <t>思茅蜂跑六队</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>晚高峰、夜宵2、夜宵1</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -5676,7 +5676,7 @@
         <v>20</v>
       </c>
       <c r="K103" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -5690,17 +5690,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>李建强</t>
+          <t>紫龙标</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1108985115</t>
+          <t>1083595205</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>思茅蜂跑七队</t>
+          <t>思茅蜂跑六队</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -5731,7 +5731,7 @@
         <v>20</v>
       </c>
       <c r="K104" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
@@ -5745,17 +5745,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>罗成飞</t>
+          <t>彭奇伟</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>217491379</t>
+          <t>1119321475</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>思茅蜂跑七队</t>
+          <t>思茅蜂跑六队</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>凌晨1、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5800,17 +5800,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>罗庭坤</t>
+          <t>陈旺</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1019361639</t>
+          <t>1148705026</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>思茅蜂跑七队</t>
+          <t>思茅蜂跑六队</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5855,17 +5855,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>李勇康</t>
+          <t>李进明</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1055750155</t>
+          <t>1123870054</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>思茅蜂跑七队</t>
+          <t>思茅蜂跑六队</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2</t>
+          <t>午高峰</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5896,7 +5896,7 @@
         <v>20</v>
       </c>
       <c r="K107" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
@@ -5910,17 +5910,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>郭皓嘉</t>
+          <t>王志明</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1087266441</t>
+          <t>1042930930</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>思茅蜂跑七队</t>
+          <t>思茅蜂跑六队</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>晚高峰、夜宵2、夜宵1</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5939,13 +5939,13 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="H108" t="n">
         <v>480</v>
       </c>
       <c r="I108" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J108" t="n">
         <v>20</v>
@@ -5965,17 +5965,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>李二</t>
+          <t>兰龙</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>90000334955228</t>
+          <t>1150771562</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>思茅蜂跑七队</t>
+          <t>思茅蜂跑六队</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5985,7 +5985,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -6006,7 +6006,7 @@
         <v>20</v>
       </c>
       <c r="K109" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -6020,17 +6020,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>林光涛</t>
+          <t>董俊才</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1125257369</t>
+          <t>1083956676</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>思茅蜂跑七队</t>
+          <t>思茅蜂跑六队</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵2</t>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -6061,7 +6061,7 @@
         <v>20</v>
       </c>
       <c r="K110" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
@@ -6075,17 +6075,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>胡飞</t>
+          <t>刘智颖</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1154325068</t>
+          <t>298652316</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>思茅蜂跑十队</t>
+          <t>思茅蜂跑七队</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -6116,7 +6116,7 @@
         <v>20</v>
       </c>
       <c r="K111" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
@@ -6130,17 +6130,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>彭跃超</t>
+          <t>李建强</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>147529594</t>
+          <t>1108985115</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>思茅蜂跑十队</t>
+          <t>思茅蜂跑七队</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -6171,7 +6171,7 @@
         <v>20</v>
       </c>
       <c r="K112" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -6185,17 +6185,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>陈柏宏</t>
+          <t>靳熙</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1121020019</t>
+          <t>1090161529</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>思茅蜂跑十队</t>
+          <t>思茅蜂跑七队</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -6226,7 +6226,7 @@
         <v>20</v>
       </c>
       <c r="K113" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -6240,17 +6240,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>陈强</t>
+          <t>罗成飞</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1059893263</t>
+          <t>217491379</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>思茅蜂跑十队</t>
+          <t>思茅蜂跑七队</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -6281,7 +6281,7 @@
         <v>20</v>
       </c>
       <c r="K114" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -6295,17 +6295,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>白云春</t>
+          <t>罗庭坤</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1040532465</t>
+          <t>1019361639</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>思茅蜂跑十队</t>
+          <t>思茅蜂跑七队</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -6336,7 +6336,7 @@
         <v>20</v>
       </c>
       <c r="K115" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
@@ -6350,17 +6350,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>李荣祝</t>
+          <t>李勇康</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>293180284</t>
+          <t>1055750155</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>思茅蜂跑十队</t>
+          <t>思茅蜂跑七队</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -6391,7 +6391,7 @@
         <v>20</v>
       </c>
       <c r="K116" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -6405,17 +6405,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>李嘎亮</t>
+          <t>郭皓嘉</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1147310101</t>
+          <t>1087266441</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>思茅蜂跑十队</t>
+          <t>思茅蜂跑七队</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6446,7 +6446,7 @@
         <v>20</v>
       </c>
       <c r="K117" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -6460,17 +6460,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>田宗平</t>
+          <t>李二</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1050830056</t>
+          <t>90000334955228</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>思茅蜂跑十队</t>
+          <t>思茅蜂跑七队</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6501,7 +6501,7 @@
         <v>20</v>
       </c>
       <c r="K118" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -6515,17 +6515,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>高梓菘</t>
+          <t>付美依</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>1065535017</t>
+          <t>1117870153</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>思茅蜂跑十队</t>
+          <t>思茅蜂跑七队</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -6556,7 +6556,7 @@
         <v>20</v>
       </c>
       <c r="K119" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -6570,17 +6570,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>周忠宽</t>
+          <t>林光涛</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>1154175029</t>
+          <t>1125257369</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>思茅蜂跑十队</t>
+          <t>思茅蜂跑七队</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>早餐2、晚高峰、夜宵2</t>
+          <t>午高峰、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -6611,7 +6611,7 @@
         <v>20</v>
       </c>
       <c r="K120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L120" t="n">
         <v>0</v>
@@ -6625,12 +6625,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>凤玉兴</t>
+          <t>胡飞</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>1037531500</t>
+          <t>1154325068</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -6645,31 +6645,31 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>下午茶2、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>在线</t>
+          <t>离线</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H121" t="n">
         <v>480</v>
       </c>
       <c r="I121" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J121" t="n">
         <v>20</v>
       </c>
       <c r="K121" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="L121" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M121" t="inlineStr">
         <is>
@@ -6680,17 +6680,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>刀俊平</t>
+          <t>李开平</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>1019636183</t>
+          <t>1042226798</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>思茅蜂跑十一队</t>
+          <t>思茅蜂跑十队</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6721,7 +6721,7 @@
         <v>20</v>
       </c>
       <c r="K122" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
@@ -6735,17 +6735,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>胡明发</t>
+          <t>彭跃超</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>328151452</t>
+          <t>147529594</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>思茅蜂跑十一队</t>
+          <t>思茅蜂跑十队</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>午高峰</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -6790,17 +6790,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>宗祖江</t>
+          <t>陈柏宏</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>1093490392</t>
+          <t>1121020019</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>思茅蜂跑十一队</t>
+          <t>思茅蜂跑十队</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -6831,7 +6831,7 @@
         <v>20</v>
       </c>
       <c r="K124" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
@@ -6845,17 +6845,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>李真</t>
+          <t>白云春</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1059999192</t>
+          <t>1040532465</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>思茅蜂跑十一队</t>
+          <t>思茅蜂跑十队</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6886,7 +6886,7 @@
         <v>20</v>
       </c>
       <c r="K125" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L125" t="n">
         <v>0</v>
@@ -6900,17 +6900,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>王涛</t>
+          <t>李荣祝</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1052831727</t>
+          <t>293180284</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>思茅蜂跑十一队</t>
+          <t>思茅蜂跑十队</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6955,17 +6955,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>马恩杰</t>
+          <t>李嘎亮</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>290446620</t>
+          <t>1147310101</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>思茅蜂跑十三队</t>
+          <t>思茅蜂跑十队</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6996,7 +6996,7 @@
         <v>20</v>
       </c>
       <c r="K127" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="L127" t="n">
         <v>0</v>
@@ -7010,17 +7010,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>魏魁</t>
+          <t>田宗平</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1153735120</t>
+          <t>1050830056</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>思茅蜂跑十三队</t>
+          <t>思茅蜂跑十队</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -7065,17 +7065,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>徐红</t>
+          <t>高梓菘</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1067685015</t>
+          <t>1065535017</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>思茅蜂跑十三队</t>
+          <t>思茅蜂跑十队</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -7106,7 +7106,7 @@
         <v>20</v>
       </c>
       <c r="K129" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="L129" t="n">
         <v>0</v>
@@ -7120,17 +7120,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>罗金伟</t>
+          <t>凤玉兴</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1019360308</t>
+          <t>1037531500</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>思茅蜂跑十三队</t>
+          <t>思茅蜂跑十队</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>下午茶2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -7161,7 +7161,7 @@
         <v>20</v>
       </c>
       <c r="K130" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L130" t="n">
         <v>0</v>
@@ -7175,17 +7175,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>李杰</t>
+          <t>周忠宽</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>1035094629</t>
+          <t>1154175029</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>思茅蜂跑十三队</t>
+          <t>思茅蜂跑十队</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>午高峰</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -7216,7 +7216,7 @@
         <v>20</v>
       </c>
       <c r="K131" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L131" t="n">
         <v>0</v>
@@ -7230,17 +7230,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>许英宝</t>
+          <t>刀俊平</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1153845086</t>
+          <t>1019636183</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>思茅蜂跑十三队</t>
+          <t>思茅蜂跑十一队</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -7271,7 +7271,7 @@
         <v>20</v>
       </c>
       <c r="K132" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L132" t="n">
         <v>0</v>
@@ -7285,17 +7285,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>贺定军</t>
+          <t>罗诗洪</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1051380786</t>
+          <t>1091335309</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>思茅蜂跑十三队</t>
+          <t>思茅蜂跑十一队</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -7326,7 +7326,7 @@
         <v>20</v>
       </c>
       <c r="K133" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L133" t="n">
         <v>0</v>
@@ -7340,17 +7340,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>李续相</t>
+          <t>胡明发</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>310243844</t>
+          <t>328151452</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>思茅蜂跑十三队</t>
+          <t>思茅蜂跑十一队</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -7381,7 +7381,7 @@
         <v>20</v>
       </c>
       <c r="K134" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L134" t="n">
         <v>0</v>
@@ -7395,17 +7395,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>祝涛</t>
+          <t>宗祖江</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>1019304138</t>
+          <t>1093490392</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>思茅蜂跑十三队</t>
+          <t>思茅蜂跑十一队</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -7450,17 +7450,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>阿开园</t>
+          <t>罗开鑫</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>1035449050</t>
+          <t>1149640115</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>思茅蜂跑十三队</t>
+          <t>思茅蜂跑十一队</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7491,7 +7491,7 @@
         <v>20</v>
       </c>
       <c r="K136" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
@@ -7505,17 +7505,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>王俊</t>
+          <t>雷国松</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>303146764</t>
+          <t>214339123</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>思茅蜂跑十三队</t>
+          <t>思茅蜂跑十一队</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -7546,7 +7546,7 @@
         <v>20</v>
       </c>
       <c r="K137" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
@@ -7560,17 +7560,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>黄聪</t>
+          <t>李真</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>1130305617</t>
+          <t>1059999192</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>思茅蜂跑十三队</t>
+          <t>思茅蜂跑十一队</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -7615,27 +7615,27 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>杨晓强</t>
+          <t>何忠文</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>279931948</t>
+          <t>1015977046</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>思茅优远一队</t>
+          <t>思茅蜂跑十一队</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>优远</t>
+          <t>蜂跑</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -7656,7 +7656,7 @@
         <v>20</v>
       </c>
       <c r="K139" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
@@ -7670,27 +7670,27 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>白文斌</t>
+          <t>岩仁</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>277601740</t>
+          <t>1156480048</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>思茅优远一队</t>
+          <t>思茅蜂跑十一队</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>优远</t>
+          <t>蜂跑</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -7711,7 +7711,7 @@
         <v>20</v>
       </c>
       <c r="K140" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -7725,27 +7725,27 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>彭思宸</t>
+          <t>王涛</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>316377628</t>
+          <t>1052831727</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>思茅优远一队</t>
+          <t>思茅蜂跑十一队</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>优远</t>
+          <t>蜂跑</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -7766,7 +7766,7 @@
         <v>20</v>
       </c>
       <c r="K141" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -7780,22 +7780,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>李光升</t>
+          <t>马恩杰</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>1112515464</t>
+          <t>290446620</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>思茅优远一队</t>
+          <t>思茅蜂跑十三队</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>优远</t>
+          <t>蜂跑</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -7821,7 +7821,7 @@
         <v>20</v>
       </c>
       <c r="K142" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
@@ -7835,27 +7835,27 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>杨云海</t>
+          <t>魏魁</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>265785436</t>
+          <t>1153735120</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>思茅优远一队</t>
+          <t>思茅蜂跑十三队</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>优远</t>
+          <t>蜂跑</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -7876,7 +7876,7 @@
         <v>20</v>
       </c>
       <c r="K143" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="L143" t="n">
         <v>0</v>
@@ -7890,27 +7890,27 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>李晓东</t>
+          <t>徐红</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>312936500</t>
+          <t>1067685015</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>思茅优远一队</t>
+          <t>思茅蜂跑十三队</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>优远</t>
+          <t>蜂跑</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -7931,7 +7931,7 @@
         <v>20</v>
       </c>
       <c r="K144" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -7945,27 +7945,27 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>刘癸奇</t>
+          <t>罗金伟</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>294234972</t>
+          <t>1019360308</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>思茅优远一队</t>
+          <t>思茅蜂跑十三队</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>优远</t>
+          <t>蜂跑</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -7986,7 +7986,7 @@
         <v>20</v>
       </c>
       <c r="K145" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -8000,27 +8000,27 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>雷仕华</t>
+          <t>李杰</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>277513820</t>
+          <t>1035094629</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>思茅优远一队</t>
+          <t>思茅蜂跑十三队</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>优远</t>
+          <t>蜂跑</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -8041,7 +8041,7 @@
         <v>20</v>
       </c>
       <c r="K146" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L146" t="n">
         <v>0</v>
@@ -8055,22 +8055,22 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>罗锦馥</t>
+          <t>许英宝</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>1056121129</t>
+          <t>1153845086</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>思茅优远一队</t>
+          <t>思茅蜂跑十三队</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>优远</t>
+          <t>蜂跑</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -8096,7 +8096,7 @@
         <v>20</v>
       </c>
       <c r="K147" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L147" t="n">
         <v>0</v>
@@ -8110,27 +8110,27 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>杨忠林</t>
+          <t>贺定军</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>1016132235</t>
+          <t>1051380786</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>思茅优远一队</t>
+          <t>思茅蜂跑十三队</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>优远</t>
+          <t>蜂跑</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -8151,7 +8151,7 @@
         <v>20</v>
       </c>
       <c r="K148" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L148" t="n">
         <v>0</v>
@@ -8165,27 +8165,27 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>周正余</t>
+          <t>李续相</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>331435036</t>
+          <t>310243844</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>思茅优远一队</t>
+          <t>思茅蜂跑十三队</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>优远</t>
+          <t>蜂跑</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -8206,7 +8206,7 @@
         <v>20</v>
       </c>
       <c r="K149" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="L149" t="n">
         <v>0</v>
@@ -8220,27 +8220,27 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>魏启东</t>
+          <t>祝涛</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>291727548</t>
+          <t>1019304138</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>思茅优远一队</t>
+          <t>思茅蜂跑十三队</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>优远</t>
+          <t>蜂跑</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -8261,7 +8261,7 @@
         <v>20</v>
       </c>
       <c r="K150" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
@@ -8275,22 +8275,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>兰情芳</t>
+          <t>阿开园</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>90000338970244</t>
+          <t>1035449050</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>思茅优远一队</t>
+          <t>思茅蜂跑十三队</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>优远</t>
+          <t>蜂跑</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -8316,7 +8316,7 @@
         <v>20</v>
       </c>
       <c r="K151" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L151" t="n">
         <v>0</v>
@@ -8330,27 +8330,27 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>李童焘</t>
+          <t>王俊</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>1040564072</t>
+          <t>303146764</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>思茅优远一队</t>
+          <t>思茅蜂跑十三队</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>优远</t>
+          <t>蜂跑</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>晚高峰</t>
+          <t>午高峰</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -8371,7 +8371,7 @@
         <v>20</v>
       </c>
       <c r="K152" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -8385,27 +8385,27 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>沈正阳</t>
+          <t>黄聪</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>1020850421</t>
+          <t>1130305617</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>思茅优远一队</t>
+          <t>思茅蜂跑十三队</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>优远</t>
+          <t>蜂跑</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰、夜宵2</t>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -8426,7 +8426,7 @@
         <v>20</v>
       </c>
       <c r="K153" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L153" t="n">
         <v>0</v>
@@ -8440,12 +8440,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>祁杨</t>
+          <t>杨晓强</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>277527332</t>
+          <t>279931948</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -8460,7 +8460,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -8495,12 +8495,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>吴发春</t>
+          <t>鲁明春</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>1125257340</t>
+          <t>1033936996</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -8536,7 +8536,7 @@
         <v>20</v>
       </c>
       <c r="K155" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L155" t="n">
         <v>0</v>
@@ -8550,12 +8550,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>李永福</t>
+          <t>白文斌</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>313354908</t>
+          <t>277601740</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -8591,7 +8591,7 @@
         <v>20</v>
       </c>
       <c r="K156" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L156" t="n">
         <v>0</v>
@@ -8605,12 +8605,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>黄显龙</t>
+          <t>彭思宸</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>270399468</t>
+          <t>316377628</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -8634,19 +8634,19 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H157" t="n">
         <v>480</v>
       </c>
       <c r="I157" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J157" t="n">
         <v>20</v>
       </c>
       <c r="K157" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L157" t="n">
         <v>0</v>
@@ -8660,12 +8660,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>朱原庆</t>
+          <t>李光升</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>1090480333</t>
+          <t>1112515464</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -8715,12 +8715,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>罗杰</t>
+          <t>杨云海</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>291486188</t>
+          <t>265785436</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -8756,7 +8756,7 @@
         <v>20</v>
       </c>
       <c r="K159" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L159" t="n">
         <v>0</v>
@@ -8770,12 +8770,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>刀太勇</t>
+          <t>李晓东</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>1051720597</t>
+          <t>312936500</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -8811,7 +8811,7 @@
         <v>20</v>
       </c>
       <c r="K160" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L160" t="n">
         <v>0</v>
@@ -8825,12 +8825,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>李健海</t>
+          <t>周杰宽</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>330770764</t>
+          <t>241046795</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -8866,7 +8866,7 @@
         <v>20</v>
       </c>
       <c r="K161" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L161" t="n">
         <v>0</v>
@@ -8880,12 +8880,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>吴海斌</t>
+          <t>雷仕华</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>1052004810</t>
+          <t>277513820</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -8921,7 +8921,7 @@
         <v>20</v>
       </c>
       <c r="K162" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L162" t="n">
         <v>0</v>
@@ -8935,17 +8935,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>匡伊雕</t>
+          <t>周正余</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>324847356</t>
+          <t>331435036</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -8976,7 +8976,7 @@
         <v>20</v>
       </c>
       <c r="K163" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L163" t="n">
         <v>0</v>
@@ -8990,17 +8990,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>李宏</t>
+          <t>邱龙涛</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>293086524</t>
+          <t>328769468</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -9031,7 +9031,7 @@
         <v>20</v>
       </c>
       <c r="K164" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L164" t="n">
         <v>0</v>
@@ -9045,17 +9045,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>赵学初</t>
+          <t>兰情芳</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>290252548</t>
+          <t>90000338970244</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -9086,7 +9086,7 @@
         <v>20</v>
       </c>
       <c r="K165" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L165" t="n">
         <v>0</v>
@@ -9100,17 +9100,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>李德生</t>
+          <t>刀志鸿</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>1016030307</t>
+          <t>308511236</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>午高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -9155,17 +9155,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>罗云照</t>
+          <t>罗庆福</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>297822572</t>
+          <t>265204452</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -9175,7 +9175,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -9196,7 +9196,7 @@
         <v>20</v>
       </c>
       <c r="K167" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L167" t="n">
         <v>0</v>
@@ -9210,17 +9210,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>杨城鑫</t>
+          <t>沈正阳</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>1159670127</t>
+          <t>1020850421</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -9251,7 +9251,7 @@
         <v>20</v>
       </c>
       <c r="K168" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L168" t="n">
         <v>0</v>
@@ -9265,17 +9265,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>王俊</t>
+          <t>陈会岭</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>317570748</t>
+          <t>202706747</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -9306,7 +9306,7 @@
         <v>20</v>
       </c>
       <c r="K169" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L169" t="n">
         <v>0</v>
@@ -9320,17 +9320,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>王兵</t>
+          <t>李祖顺</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>330361220</t>
+          <t>300606788</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵2、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -9349,19 +9349,19 @@
         </is>
       </c>
       <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="n">
+        <v>480</v>
+      </c>
+      <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="n">
+        <v>20</v>
+      </c>
+      <c r="K170" t="n">
         <v>12</v>
-      </c>
-      <c r="H170" t="n">
-        <v>480</v>
-      </c>
-      <c r="I170" t="n">
-        <v>3</v>
-      </c>
-      <c r="J170" t="n">
-        <v>20</v>
-      </c>
-      <c r="K170" t="n">
-        <v>8</v>
       </c>
       <c r="L170" t="n">
         <v>0</v>
@@ -9375,17 +9375,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>李正国</t>
+          <t>吴发春</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>261808524</t>
+          <t>1125257340</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -9416,7 +9416,7 @@
         <v>20</v>
       </c>
       <c r="K171" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L171" t="n">
         <v>0</v>
@@ -9430,17 +9430,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>张云强</t>
+          <t>黄显龙</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>1016211018</t>
+          <t>270399468</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -9450,7 +9450,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -9471,7 +9471,7 @@
         <v>20</v>
       </c>
       <c r="K172" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L172" t="n">
         <v>0</v>
@@ -9485,17 +9485,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>王政元</t>
+          <t>朱原庆</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>1034685238</t>
+          <t>1090480333</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -9505,7 +9505,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -9526,7 +9526,7 @@
         <v>20</v>
       </c>
       <c r="K173" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L173" t="n">
         <v>0</v>
@@ -9540,17 +9540,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>罗师航</t>
+          <t>罗杰</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>1092599780</t>
+          <t>291486188</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -9560,7 +9560,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -9581,7 +9581,7 @@
         <v>20</v>
       </c>
       <c r="K174" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L174" t="n">
         <v>0</v>
@@ -9595,17 +9595,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>张仲阳</t>
+          <t>佟露</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>273841420</t>
+          <t>1016169126</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -9615,7 +9615,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -9636,7 +9636,7 @@
         <v>20</v>
       </c>
       <c r="K175" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L175" t="n">
         <v>0</v>
@@ -9650,17 +9650,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>王世奎</t>
+          <t>李健海</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>320004748</t>
+          <t>330770764</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -9670,7 +9670,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -9691,7 +9691,7 @@
         <v>20</v>
       </c>
       <c r="K176" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L176" t="n">
         <v>0</v>
@@ -9705,17 +9705,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>罗坤</t>
+          <t>周铅超</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>1142045554</t>
+          <t>157611867</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -9746,7 +9746,7 @@
         <v>20</v>
       </c>
       <c r="K177" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L177" t="n">
         <v>0</v>
@@ -9760,17 +9760,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>查懿原</t>
+          <t>匡伊雕</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>276165364</t>
+          <t>324847356</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵2、夜宵1</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -9801,7 +9801,7 @@
         <v>20</v>
       </c>
       <c r="K178" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L178" t="n">
         <v>0</v>
@@ -9815,17 +9815,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>李星龙</t>
+          <t>李宏</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>1090430076</t>
+          <t>293086524</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -9856,7 +9856,7 @@
         <v>20</v>
       </c>
       <c r="K179" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L179" t="n">
         <v>0</v>
@@ -9870,17 +9870,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>唐涛</t>
+          <t>赵学初</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>277946036</t>
+          <t>290252548</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -9911,7 +9911,7 @@
         <v>20</v>
       </c>
       <c r="K180" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L180" t="n">
         <v>0</v>
@@ -9925,17 +9925,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>李海瑞</t>
+          <t>李笙福</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>1129764787</t>
+          <t>1115214416</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -9945,7 +9945,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -9966,7 +9966,7 @@
         <v>20</v>
       </c>
       <c r="K181" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L181" t="n">
         <v>0</v>
@@ -9980,17 +9980,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>钱学林</t>
+          <t>罗云照</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>1130041012</t>
+          <t>297822572</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -10021,7 +10021,7 @@
         <v>20</v>
       </c>
       <c r="K182" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L182" t="n">
         <v>0</v>
@@ -10035,17 +10035,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>白顺荣</t>
+          <t>王俊</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>1045718631</t>
+          <t>317570748</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -10076,7 +10076,7 @@
         <v>20</v>
       </c>
       <c r="K183" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L183" t="n">
         <v>0</v>
@@ -10090,17 +10090,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>周明权</t>
+          <t>王兵</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>1158625019</t>
+          <t>330361220</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、晚高峰、夜宵2、夜宵1</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -10131,7 +10131,7 @@
         <v>20</v>
       </c>
       <c r="K184" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L184" t="n">
         <v>0</v>
@@ -10145,17 +10145,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>曾平</t>
+          <t>李正国</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>1143782010</t>
+          <t>261808524</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰、夜宵2</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -10186,7 +10186,7 @@
         <v>20</v>
       </c>
       <c r="K185" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L185" t="n">
         <v>0</v>
@@ -10200,17 +10200,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>梁祖恩</t>
+          <t>张云强</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>1069696308</t>
+          <t>1016211018</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -10220,7 +10220,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -10255,17 +10255,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>罗杰</t>
+          <t>王政元</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>1142566401</t>
+          <t>1034685238</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -10296,7 +10296,7 @@
         <v>20</v>
       </c>
       <c r="K187" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L187" t="n">
         <v>0</v>
@@ -10310,17 +10310,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>罗文婷</t>
+          <t>罗师航</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>280481452</t>
+          <t>1092599780</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -10330,7 +10330,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -10351,7 +10351,7 @@
         <v>20</v>
       </c>
       <c r="K188" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L188" t="n">
         <v>0</v>
@@ -10365,17 +10365,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>袁翊博</t>
+          <t>石福</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>1145707189</t>
+          <t>282612804</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -10406,7 +10406,7 @@
         <v>20</v>
       </c>
       <c r="K189" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L189" t="n">
         <v>0</v>
@@ -10420,17 +10420,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>邓迪社</t>
+          <t>张仲阳</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>221905563</t>
+          <t>273841420</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵2、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -10449,7 +10449,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H190" t="n">
         <v>480</v>
@@ -10461,7 +10461,7 @@
         <v>20</v>
       </c>
       <c r="K190" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L190" t="n">
         <v>0</v>
@@ -10475,17 +10475,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>熊远发</t>
+          <t>王世奎</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>266314300</t>
+          <t>320004748</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -10495,7 +10495,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -10516,7 +10516,7 @@
         <v>20</v>
       </c>
       <c r="K191" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L191" t="n">
         <v>0</v>
@@ -10530,17 +10530,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>黄健翔</t>
+          <t>罗坤</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>1071071679</t>
+          <t>1142045554</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -10571,7 +10571,7 @@
         <v>20</v>
       </c>
       <c r="K192" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L192" t="n">
         <v>0</v>
@@ -10585,17 +10585,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>张鹏</t>
+          <t>查懿原</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>1028523558</t>
+          <t>276165364</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵2、夜宵1</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -10626,7 +10626,7 @@
         <v>20</v>
       </c>
       <c r="K193" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L193" t="n">
         <v>0</v>
@@ -10640,17 +10640,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>杨双辉</t>
+          <t>李星龙</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>264798596</t>
+          <t>1090430076</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -10660,7 +10660,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>晚高峰</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -10681,7 +10681,7 @@
         <v>20</v>
       </c>
       <c r="K194" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L194" t="n">
         <v>0</v>
@@ -10695,17 +10695,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>肖滔滔</t>
+          <t>李海瑞</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>270093300</t>
+          <t>1129764787</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -10715,7 +10715,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -10750,17 +10750,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>普红兵</t>
+          <t>钱学林</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>277529860</t>
+          <t>1130041012</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -10791,7 +10791,7 @@
         <v>20</v>
       </c>
       <c r="K196" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L196" t="n">
         <v>0</v>
@@ -10805,17 +10805,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>罗俊杰</t>
+          <t>白顺荣</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>1096790672</t>
+          <t>1045718631</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -10860,17 +10860,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>匡一鸣</t>
+          <t>周明权</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>90000340722076</t>
+          <t>1158625019</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -10901,7 +10901,7 @@
         <v>20</v>
       </c>
       <c r="K198" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="L198" t="n">
         <v>0</v>
@@ -10915,17 +10915,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>彭毅勇</t>
+          <t>曾平</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>175204387</t>
+          <t>1143782010</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -10956,7 +10956,7 @@
         <v>20</v>
       </c>
       <c r="K199" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L199" t="n">
         <v>0</v>
@@ -10970,17 +10970,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>陈明源</t>
+          <t>梁祖恩</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>277124636</t>
+          <t>1069696308</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -11011,7 +11011,7 @@
         <v>20</v>
       </c>
       <c r="K200" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L200" t="n">
         <v>0</v>
@@ -11025,17 +11025,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>李清林</t>
+          <t>付林臣</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>266695804</t>
+          <t>1024206523</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -11080,17 +11080,17 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>杨静修</t>
+          <t>罗杰</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>281365980</t>
+          <t>1142566401</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -11121,7 +11121,7 @@
         <v>20</v>
       </c>
       <c r="K202" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L202" t="n">
         <v>0</v>
@@ -11135,12 +11135,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>陈新文</t>
+          <t>邓迪社</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>266350460</t>
+          <t>221905563</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -11176,7 +11176,7 @@
         <v>20</v>
       </c>
       <c r="K203" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L203" t="n">
         <v>0</v>
@@ -11190,12 +11190,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>罗文龙</t>
+          <t>熊远发</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>173435307</t>
+          <t>266314300</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -11210,7 +11210,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -11231,7 +11231,7 @@
         <v>20</v>
       </c>
       <c r="K204" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="L204" t="n">
         <v>0</v>
@@ -11245,12 +11245,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>王仕臣</t>
+          <t>黄健翔</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>1043620937</t>
+          <t>1071071679</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -11265,7 +11265,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -11286,7 +11286,7 @@
         <v>20</v>
       </c>
       <c r="K205" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L205" t="n">
         <v>0</v>
@@ -11300,12 +11300,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>李杰彪</t>
+          <t>张鹏</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>279705460</t>
+          <t>1028523558</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>午高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -11329,19 +11329,19 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H206" t="n">
         <v>480</v>
       </c>
       <c r="I206" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J206" t="n">
         <v>20</v>
       </c>
       <c r="K206" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L206" t="n">
         <v>0</v>
@@ -11355,12 +11355,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>陶树良</t>
+          <t>杨双辉</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>278115308</t>
+          <t>264798596</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -11375,33 +11375,748 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
+          <t>午高峰、下午茶1、晚高峰</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" t="n">
+        <v>480</v>
+      </c>
+      <c r="I207" t="n">
+        <v>0</v>
+      </c>
+      <c r="J207" t="n">
+        <v>20</v>
+      </c>
+      <c r="K207" t="n">
+        <v>15</v>
+      </c>
+      <c r="L207" t="n">
+        <v>0</v>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>肖滔滔</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>270093300</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>午高峰、下午茶2、晚高峰</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" t="n">
+        <v>480</v>
+      </c>
+      <c r="I208" t="n">
+        <v>0</v>
+      </c>
+      <c r="J208" t="n">
+        <v>20</v>
+      </c>
+      <c r="K208" t="n">
+        <v>8</v>
+      </c>
+      <c r="L208" t="n">
+        <v>0</v>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>匡一鸣</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>90000340722076</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" t="n">
+        <v>480</v>
+      </c>
+      <c r="I209" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" t="n">
+        <v>20</v>
+      </c>
+      <c r="K209" t="n">
+        <v>15</v>
+      </c>
+      <c r="L209" t="n">
+        <v>0</v>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>彭毅勇</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>175204387</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>午高峰、下午茶1、晚高峰</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G210" t="n">
+        <v>0</v>
+      </c>
+      <c r="H210" t="n">
+        <v>480</v>
+      </c>
+      <c r="I210" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" t="n">
+        <v>20</v>
+      </c>
+      <c r="K210" t="n">
+        <v>15</v>
+      </c>
+      <c r="L210" t="n">
+        <v>0</v>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>夏彪</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>278430252</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" t="n">
+        <v>480</v>
+      </c>
+      <c r="I211" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" t="n">
+        <v>20</v>
+      </c>
+      <c r="K211" t="n">
+        <v>12</v>
+      </c>
+      <c r="L211" t="n">
+        <v>0</v>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>孙帅</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>227759883</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" t="n">
+        <v>480</v>
+      </c>
+      <c r="I212" t="n">
+        <v>0</v>
+      </c>
+      <c r="J212" t="n">
+        <v>20</v>
+      </c>
+      <c r="K212" t="n">
+        <v>3</v>
+      </c>
+      <c r="L212" t="n">
+        <v>0</v>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>陈明源</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>277124636</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G213" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" t="n">
+        <v>480</v>
+      </c>
+      <c r="I213" t="n">
+        <v>0</v>
+      </c>
+      <c r="J213" t="n">
+        <v>20</v>
+      </c>
+      <c r="K213" t="n">
+        <v>4</v>
+      </c>
+      <c r="L213" t="n">
+        <v>0</v>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>李清林</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>266695804</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
           <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>离线</t>
-        </is>
-      </c>
-      <c r="G207" t="n">
-        <v>0</v>
-      </c>
-      <c r="H207" t="n">
-        <v>480</v>
-      </c>
-      <c r="I207" t="n">
-        <v>0</v>
-      </c>
-      <c r="J207" t="n">
-        <v>20</v>
-      </c>
-      <c r="K207" t="n">
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G214" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" t="n">
+        <v>480</v>
+      </c>
+      <c r="I214" t="n">
+        <v>0</v>
+      </c>
+      <c r="J214" t="n">
+        <v>20</v>
+      </c>
+      <c r="K214" t="n">
+        <v>6</v>
+      </c>
+      <c r="L214" t="n">
+        <v>0</v>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>自银号</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>1086868625</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>午高峰、晚高峰、夜宵2、夜宵1</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" t="n">
+        <v>480</v>
+      </c>
+      <c r="I215" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" t="n">
+        <v>20</v>
+      </c>
+      <c r="K215" t="n">
+        <v>1</v>
+      </c>
+      <c r="L215" t="n">
+        <v>0</v>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>杨静修</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>281365980</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" t="n">
+        <v>480</v>
+      </c>
+      <c r="I216" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" t="n">
+        <v>20</v>
+      </c>
+      <c r="K216" t="n">
+        <v>1</v>
+      </c>
+      <c r="L216" t="n">
+        <v>0</v>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>郭莉萍</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>276709156</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>早餐2、午高峰、晚高峰</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" t="n">
+        <v>480</v>
+      </c>
+      <c r="I217" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" t="n">
+        <v>20</v>
+      </c>
+      <c r="K217" t="n">
         <v>8</v>
       </c>
-      <c r="L207" t="n">
-        <v>0</v>
-      </c>
-      <c r="M207" t="inlineStr">
+      <c r="L217" t="n">
+        <v>0</v>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>陈新文</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>266350460</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>午高峰、晚高峰、夜宵2、夜宵1</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" t="n">
+        <v>480</v>
+      </c>
+      <c r="I218" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" t="n">
+        <v>20</v>
+      </c>
+      <c r="K218" t="n">
+        <v>14</v>
+      </c>
+      <c r="L218" t="n">
+        <v>0</v>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>罗文龙</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>173435307</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>午高峰、下午茶2、晚高峰</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="n">
+        <v>480</v>
+      </c>
+      <c r="I219" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" t="n">
+        <v>20</v>
+      </c>
+      <c r="K219" t="n">
+        <v>15</v>
+      </c>
+      <c r="L219" t="n">
+        <v>0</v>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>李杰彪</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>279705460</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>午高峰</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" t="n">
+        <v>480</v>
+      </c>
+      <c r="I220" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" t="n">
+        <v>20</v>
+      </c>
+      <c r="K220" t="n">
+        <v>8</v>
+      </c>
+      <c r="L220" t="n">
+        <v>0</v>
+      </c>
+      <c r="M220" t="inlineStr">
         <is>
           <t>预计达标</t>
         </is>

--- a/public/monitor_latest.xlsx
+++ b/public/monitor_latest.xlsx
@@ -80,12 +80,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>李俊杰</t>
+          <t>陈维富</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>303569484</t>
+          <t>270698852</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -100,7 +100,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>凌晨1、凌晨2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -112,35 +112,35 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>预计达标</t>
+          <t>有风险</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>苏亚春</t>
+          <t>朱健明</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>283451844</t>
+          <t>1013523131</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -155,7 +155,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>凌晨1、凌晨2、凌晨3、夜宵2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -167,40 +167,40 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>预计达标</t>
+          <t>有风险</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>李翠伟</t>
+          <t>鲍国明</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1049933839</t>
+          <t>1087319378</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>思茅优选一队</t>
+          <t>思茅优选二队</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -210,7 +210,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>凌晨1、凌晨2、凌晨3、夜宵2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -222,13 +222,13 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>15</v>
@@ -238,24 +238,24 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>预计达标</t>
+          <t>有风险</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>杨海轮</t>
+          <t>汪宗兵</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>290558268</t>
+          <t>1037848475</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>思茅优选一队</t>
+          <t>思茅优选二队</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -265,52 +265,52 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>凌晨1、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>预计达标</t>
+          <t>有风险</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>田新宾</t>
+          <t>杨建国</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>279429852</t>
+          <t>1138840186</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>思茅优选一队</t>
+          <t>思茅优选三队</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -320,7 +320,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>凌晨1、凌晨2、凌晨3、夜宵2</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -332,40 +332,40 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>预计达标</t>
+          <t>有风险</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>杨思杰</t>
+          <t>胡锦波</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1082260013</t>
+          <t>316835700</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>思茅优选一队</t>
+          <t>思茅优选三队</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -375,7 +375,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>凌晨1、凌晨2、夜宵2</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -387,50 +387,50 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>预计达标</t>
+          <t>有风险</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>陈维富</t>
+          <t>李童焘</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>270698852</t>
+          <t>1040564072</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>思茅优选一队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>优选</t>
+          <t>优远</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>凌晨1、凌晨2</t>
+          <t>凌晨1、晚高峰</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -442,35 +442,35 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>480</v>
+        <v>90</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>预计达标</t>
+          <t>有风险</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>刀荣程</t>
+          <t>李俊杰</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1044820977</t>
+          <t>303569484</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -506,7 +506,7 @@
         <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -520,12 +520,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>沈红心</t>
+          <t>邓成毅</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1151687559</t>
+          <t>1043170062</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -561,7 +561,7 @@
         <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -575,12 +575,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>朱健明</t>
+          <t>苏亚春</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1013523131</t>
+          <t>283451844</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>凌晨1、凌晨2、凌晨3、夜宵1</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -616,7 +616,7 @@
         <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -630,12 +630,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>胡关浚</t>
+          <t>李翠伟</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>261536156</t>
+          <t>1049933839</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -650,12 +650,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵2、夜宵1</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>在线</t>
+          <t>离线</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -685,17 +685,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>刘云</t>
+          <t>杨海轮</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>267345532</t>
+          <t>290558268</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>思茅优选二队</t>
+          <t>思茅优选一队</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>早餐2</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -726,7 +726,7 @@
         <v>20</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -740,17 +740,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>汤亚东</t>
+          <t>田新宾</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>313288188</t>
+          <t>279429852</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>思茅优选二队</t>
+          <t>思茅优选一队</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -781,7 +781,7 @@
         <v>20</v>
       </c>
       <c r="K14" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -795,17 +795,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>张文平</t>
+          <t>杨思杰</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>316521756</t>
+          <t>1082260013</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>思茅优选二队</t>
+          <t>思茅优选一队</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -836,7 +836,7 @@
         <v>20</v>
       </c>
       <c r="K15" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -850,17 +850,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>李世坚</t>
+          <t>陈维富</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1124817963</t>
+          <t>270698852</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>思茅优选二队</t>
+          <t>思茅优选一队</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>凌晨1、凌晨2</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -891,7 +891,7 @@
         <v>20</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -905,17 +905,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>马豪</t>
+          <t>刀荣程</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1086929921</t>
+          <t>1044820977</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>思茅优选二队</t>
+          <t>思茅优选一队</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -960,17 +960,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>罗宗辉</t>
+          <t>沈红心</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90000338986940</t>
+          <t>1151687559</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>思茅优选二队</t>
+          <t>思茅优选一队</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1001,7 +1001,7 @@
         <v>20</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1015,17 +1015,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>董宇</t>
+          <t>朱健明</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1040981176</t>
+          <t>1013523131</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>思茅优选二队</t>
+          <t>思茅优选一队</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>凌晨1、凌晨2、凌晨3、夜宵2</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>陶伊翔</t>
+          <t>刘云</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1110435691</t>
+          <t>267345532</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1111,7 +1111,7 @@
         <v>20</v>
       </c>
       <c r="K20" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1125,12 +1125,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>鲁炫</t>
+          <t>汤亚东</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>90000339224588</t>
+          <t>313288188</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1166,7 +1166,7 @@
         <v>20</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1180,12 +1180,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>尹江涛</t>
+          <t>张文平</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1051146884</t>
+          <t>316521756</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>下午茶2</t>
+          <t>早餐2、午高峰、夜宵1</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1235,12 +1235,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>李国斌</t>
+          <t>李世坚</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>286239588</t>
+          <t>1124817963</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1290,12 +1290,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>杨绍元</t>
+          <t>李金威</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>264801124</t>
+          <t>281910660</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰、夜宵2</t>
+          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1331,7 +1331,7 @@
         <v>20</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -1345,12 +1345,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>汪宗兵</t>
+          <t>熊正存</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1037848475</t>
+          <t>1070938748</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1386,7 +1386,7 @@
         <v>20</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -1400,12 +1400,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>王朝顺</t>
+          <t>马豪</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>287127412</t>
+          <t>1086929921</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1455,12 +1455,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>鲍国明</t>
+          <t>罗宗辉</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1087319378</t>
+          <t>90000338986940</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>凌晨1、凌晨2、凌晨3、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1496,7 +1496,7 @@
         <v>20</v>
       </c>
       <c r="K27" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -1510,12 +1510,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>王武斌</t>
+          <t>陶伊翔</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>300824396</t>
+          <t>1110435691</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1565,12 +1565,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>施发龙</t>
+          <t>鲁炫</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1060067605</t>
+          <t>90000339224588</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵2、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1606,7 +1606,7 @@
         <v>20</v>
       </c>
       <c r="K29" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -1620,12 +1620,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>李金威</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>281910660</t>
+          <t>1042321509</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵2、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>在线</t>
+          <t>离线</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1661,7 +1661,7 @@
         <v>20</v>
       </c>
       <c r="K30" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -1675,17 +1675,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>杨建国</t>
+          <t>杨福云</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1138840186</t>
+          <t>1156896791</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>思茅优选三队</t>
+          <t>思茅优选二队</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>凌晨1、凌晨2、凌晨3、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1730,17 +1730,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>李海斌</t>
+          <t>杨绍元</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>90000335390900</t>
+          <t>264801124</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>思茅优选三队</t>
+          <t>思茅优选二队</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1771,7 +1771,7 @@
         <v>20</v>
       </c>
       <c r="K32" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -1785,17 +1785,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>王钱</t>
+          <t>鲍国明</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>289243292</t>
+          <t>1087319378</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>思茅优选三队</t>
+          <t>思茅优选二队</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>凌晨1、凌晨2、凌晨3、夜宵2</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1826,7 +1826,7 @@
         <v>20</v>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -1840,17 +1840,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>胡锦波</t>
+          <t>鲍德斌</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>316835700</t>
+          <t>317794948</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>思茅优选三队</t>
+          <t>思茅优选二队</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>凌晨1、凌晨2、凌晨3、夜宵1</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1895,17 +1895,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>普李叶</t>
+          <t>王武斌</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1019684446</t>
+          <t>300824396</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>思茅优选三队</t>
+          <t>思茅优选二队</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1936,7 +1936,7 @@
         <v>20</v>
       </c>
       <c r="K35" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -1950,17 +1950,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>佟奇</t>
+          <t>施发龙</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>90000336291956</t>
+          <t>1060067605</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>思茅优选三队</t>
+          <t>思茅优选二队</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2005,17 +2005,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>李健伟</t>
+          <t>尹江涛</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>264431676</t>
+          <t>1051146884</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>思茅优选三队</t>
+          <t>思茅优选二队</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2025,12 +2025,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>下午茶1</t>
+          <t>下午茶1、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2046,7 +2046,7 @@
         <v>20</v>
       </c>
       <c r="K37" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -2060,17 +2060,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>农光应</t>
+          <t>汪宗兵</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1142610772</t>
+          <t>1037848475</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>思茅优选三队</t>
+          <t>思茅优选二队</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2080,12 +2080,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>凌晨1、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2115,17 +2115,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>龙峰</t>
+          <t>王朝顺</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1087320804</t>
+          <t>287127412</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>思茅优选三队</t>
+          <t>思茅优选二队</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -2156,7 +2156,7 @@
         <v>20</v>
       </c>
       <c r="K39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -2170,12 +2170,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>赵兴跃</t>
+          <t>鲍家伟</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1045086221</t>
+          <t>1069055452</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>午高峰</t>
+          <t>夜宵2</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2211,7 +2211,7 @@
         <v>20</v>
       </c>
       <c r="K40" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -2225,12 +2225,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>鲍家伟</t>
+          <t>杨建国</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1069055452</t>
+          <t>1138840186</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>凌晨1、凌晨2、凌晨3、夜宵1</t>
+          <t>凌晨1、凌晨2、凌晨3、夜宵2</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>在线</t>
+          <t>离线</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -2280,27 +2280,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>罗佳杨</t>
+          <t>李海斌</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>289157644</t>
+          <t>90000335390900</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>思茅蜂跑一队</t>
+          <t>思茅优选三队</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>蜂跑</t>
+          <t>优选</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2321,7 +2321,7 @@
         <v>20</v>
       </c>
       <c r="K42" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -2335,27 +2335,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>李新田</t>
+          <t>王钱</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>320683868</t>
+          <t>289243292</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>思茅蜂跑一队</t>
+          <t>思茅优选三队</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>蜂跑</t>
+          <t>优选</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2376,7 +2376,7 @@
         <v>20</v>
       </c>
       <c r="K43" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -2390,27 +2390,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>赵文俊</t>
+          <t>胡锦波</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1019362134</t>
+          <t>316835700</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>思茅蜂跑一队</t>
+          <t>思茅优选三队</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>蜂跑</t>
+          <t>优选</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>凌晨1、凌晨2、夜宵2</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2431,7 +2431,7 @@
         <v>20</v>
       </c>
       <c r="K44" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -2445,27 +2445,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>郑荣建</t>
+          <t>普李叶</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>307784220</t>
+          <t>1019684446</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>思茅蜂跑一队</t>
+          <t>思茅优选三队</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>蜂跑</t>
+          <t>优选</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2486,7 +2486,7 @@
         <v>20</v>
       </c>
       <c r="K45" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -2500,27 +2500,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>车俊超</t>
+          <t>佟奇</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>291997260</t>
+          <t>90000336291956</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>思茅蜂跑一队</t>
+          <t>思茅优选三队</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>蜂跑</t>
+          <t>优选</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>下午茶1、下午茶2、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2541,7 +2541,7 @@
         <v>20</v>
       </c>
       <c r="K46" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -2555,27 +2555,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>张忠海</t>
+          <t>李健伟</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1003950027</t>
+          <t>264431676</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>思茅蜂跑一队</t>
+          <t>思茅优选三队</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>蜂跑</t>
+          <t>优选</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>早餐2、午高峰</t>
+          <t>下午茶1</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2596,7 +2596,7 @@
         <v>20</v>
       </c>
       <c r="K47" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -2610,27 +2610,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>王浩</t>
+          <t>农光应</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1046180007</t>
+          <t>1142610772</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>思茅蜂跑一队</t>
+          <t>思茅优选三队</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>蜂跑</t>
+          <t>优选</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2651,7 +2651,7 @@
         <v>20</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -2665,27 +2665,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>李志义</t>
+          <t>龙峰</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1112358704</t>
+          <t>1087320804</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>思茅蜂跑一队</t>
+          <t>思茅优选三队</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>蜂跑</t>
+          <t>优选</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2706,7 +2706,7 @@
         <v>20</v>
       </c>
       <c r="K49" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -2720,27 +2720,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>王金林</t>
+          <t>赵兴跃</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1125678007</t>
+          <t>1045086221</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>思茅蜂跑一队</t>
+          <t>思茅优选三队</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>蜂跑</t>
+          <t>优选</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰、夜宵2</t>
+          <t>午高峰</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2761,7 +2761,7 @@
         <v>20</v>
       </c>
       <c r="K50" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>者少军</t>
+          <t>罗佳杨</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>261859444</t>
+          <t>289157644</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、夜宵1</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>在线</t>
+          <t>离线</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -2816,7 +2816,7 @@
         <v>20</v>
       </c>
       <c r="K51" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -2830,17 +2830,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>罗晨龙</t>
+          <t>李新田</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>293959380</t>
+          <t>320683868</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>思茅蜂跑三队</t>
+          <t>思茅蜂跑一队</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>下午茶2、晚高峰、夜宵2</t>
+          <t>下午茶1、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2871,7 +2871,7 @@
         <v>20</v>
       </c>
       <c r="K52" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -2885,17 +2885,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>朱加林</t>
+          <t>赵文俊</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>186839747</t>
+          <t>1019362134</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>思茅蜂跑三队</t>
+          <t>思茅蜂跑一队</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2926,7 +2926,7 @@
         <v>20</v>
       </c>
       <c r="K53" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -2940,17 +2940,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>张小华</t>
+          <t>袁洲</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>317756532</t>
+          <t>332120988</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>思茅蜂跑三队</t>
+          <t>思茅蜂跑一队</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2981,7 +2981,7 @@
         <v>20</v>
       </c>
       <c r="K54" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -2995,17 +2995,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>蓝琨</t>
+          <t>车俊超</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1070814423</t>
+          <t>291997260</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>思茅蜂跑三队</t>
+          <t>思茅蜂跑一队</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>下午茶1、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3036,7 +3036,7 @@
         <v>20</v>
       </c>
       <c r="K55" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -3050,17 +3050,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>王东奎</t>
+          <t>张忠海</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1042700176</t>
+          <t>1003950027</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>思茅蜂跑三队</t>
+          <t>思茅蜂跑一队</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>下午茶2、晚高峰、夜宵2</t>
+          <t>早餐2、午高峰</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3091,7 +3091,7 @@
         <v>20</v>
       </c>
       <c r="K56" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -3105,17 +3105,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>钱思安</t>
+          <t>王浩</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>289601204</t>
+          <t>1046180007</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>思茅蜂跑三队</t>
+          <t>思茅蜂跑一队</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3146,7 +3146,7 @@
         <v>20</v>
       </c>
       <c r="K57" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -3160,17 +3160,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>金富勤</t>
+          <t>李志义</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>615466374</t>
+          <t>1112358704</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>思茅蜂跑三队</t>
+          <t>思茅蜂跑一队</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3201,7 +3201,7 @@
         <v>20</v>
       </c>
       <c r="K58" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -3215,17 +3215,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>陈少平</t>
+          <t>王金林</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1015826982</t>
+          <t>1125678007</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>思茅蜂跑三队</t>
+          <t>思茅蜂跑一队</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3256,7 +3256,7 @@
         <v>20</v>
       </c>
       <c r="K59" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -3270,17 +3270,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>李旺坤</t>
+          <t>者少军</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1052121306</t>
+          <t>261859444</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>思茅蜂跑三队</t>
+          <t>思茅蜂跑一队</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3311,7 +3311,7 @@
         <v>20</v>
       </c>
       <c r="K60" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -3325,12 +3325,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>金锐</t>
+          <t>朱加林</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>292657164</t>
+          <t>186839747</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>下午茶2、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3366,7 +3366,7 @@
         <v>20</v>
       </c>
       <c r="K61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -3380,12 +3380,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>刘钦臣</t>
+          <t>张小华</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>332133620</t>
+          <t>317756532</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、夜宵2</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3421,7 +3421,7 @@
         <v>20</v>
       </c>
       <c r="K62" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -3435,12 +3435,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>白凯勇</t>
+          <t>蓝琨</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1092736925</t>
+          <t>1070814423</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>下午茶2、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>在线</t>
+          <t>离线</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -3476,7 +3476,7 @@
         <v>20</v>
       </c>
       <c r="K63" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -3490,17 +3490,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>何彪</t>
+          <t>王东奎</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>511001013</t>
+          <t>1042700176</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>思茅蜂跑四队</t>
+          <t>思茅蜂跑三队</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3531,7 +3531,7 @@
         <v>20</v>
       </c>
       <c r="K64" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -3545,17 +3545,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>毕航</t>
+          <t>钱思安</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>325067300</t>
+          <t>289601204</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>思茅蜂跑四队</t>
+          <t>思茅蜂跑三队</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3586,7 +3586,7 @@
         <v>20</v>
       </c>
       <c r="K65" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -3600,17 +3600,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>苏志国</t>
+          <t>金富勤</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1011062500</t>
+          <t>615466374</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>思茅蜂跑四队</t>
+          <t>思茅蜂跑三队</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3641,7 +3641,7 @@
         <v>20</v>
       </c>
       <c r="K66" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -3655,17 +3655,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>李院辉</t>
+          <t>陈少平</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1140485075</t>
+          <t>1015826982</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>思茅蜂跑四队</t>
+          <t>思茅蜂跑三队</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3696,7 +3696,7 @@
         <v>20</v>
       </c>
       <c r="K67" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -3710,17 +3710,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>陶改荣</t>
+          <t>李旺坤</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1102455067</t>
+          <t>1052121306</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>思茅蜂跑四队</t>
+          <t>思茅蜂跑三队</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、夜宵1</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3751,7 +3751,7 @@
         <v>20</v>
       </c>
       <c r="K68" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -3765,17 +3765,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>毕朝军</t>
+          <t>白凯勇</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>90000334561228</t>
+          <t>1092736925</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>思茅蜂跑四队</t>
+          <t>思茅蜂跑三队</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>午高峰</t>
+          <t>下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3806,7 +3806,7 @@
         <v>20</v>
       </c>
       <c r="K69" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -3820,17 +3820,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>段文斌</t>
+          <t>金锐</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>280124636</t>
+          <t>292657164</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>思茅蜂跑四队</t>
+          <t>思茅蜂跑三队</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3861,7 +3861,7 @@
         <v>20</v>
       </c>
       <c r="K70" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -3875,17 +3875,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>毛勇</t>
+          <t>刘钦臣</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1044060042</t>
+          <t>332133620</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>思茅蜂跑四队</t>
+          <t>思茅蜂跑三队</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶2、夜宵1</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3916,7 +3916,7 @@
         <v>20</v>
       </c>
       <c r="K71" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -3930,17 +3930,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>罗晓余</t>
+          <t>罗晨龙</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1150777253</t>
+          <t>293959380</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>思茅蜂跑四队</t>
+          <t>思茅蜂跑三队</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -3971,7 +3971,7 @@
         <v>20</v>
       </c>
       <c r="K72" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -3985,12 +3985,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>李晓春</t>
+          <t>何彪</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>286141340</t>
+          <t>511001013</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4026,7 +4026,7 @@
         <v>20</v>
       </c>
       <c r="K73" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -4040,12 +4040,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>姚天杰</t>
+          <t>毕航</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1003026879</t>
+          <t>325067300</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4081,7 +4081,7 @@
         <v>20</v>
       </c>
       <c r="K74" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -4095,12 +4095,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>白永斌</t>
+          <t>苏志国</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>256160060</t>
+          <t>1011062500</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵2</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4136,7 +4136,7 @@
         <v>20</v>
       </c>
       <c r="K75" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -4150,12 +4150,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>白启鹏</t>
+          <t>李院辉</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>284683276</t>
+          <t>1140485075</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4191,7 +4191,7 @@
         <v>20</v>
       </c>
       <c r="K76" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -4205,12 +4205,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>谭欣海</t>
+          <t>陶改荣</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>287795932</t>
+          <t>1102455067</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4246,7 +4246,7 @@
         <v>20</v>
       </c>
       <c r="K77" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -4260,12 +4260,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>张永生</t>
+          <t>段文斌</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>308807828</t>
+          <t>280124636</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4301,7 +4301,7 @@
         <v>20</v>
       </c>
       <c r="K78" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -4315,12 +4315,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>郭成红</t>
+          <t>施圆章</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>277421812</t>
+          <t>261823124</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4356,7 +4356,7 @@
         <v>20</v>
       </c>
       <c r="K79" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -4370,12 +4370,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>李冬杰</t>
+          <t>罗晓余</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>328840900</t>
+          <t>1150777253</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4411,7 +4411,7 @@
         <v>20</v>
       </c>
       <c r="K80" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -4425,17 +4425,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>郭朝坤</t>
+          <t>李晓春</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>187384715</t>
+          <t>286141340</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>思茅蜂跑五队</t>
+          <t>思茅蜂跑四队</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4466,7 +4466,7 @@
         <v>20</v>
       </c>
       <c r="K81" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -4480,17 +4480,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>李子平</t>
+          <t>罗梦宇</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>285715108</t>
+          <t>1075569997</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>思茅蜂跑五队</t>
+          <t>思茅蜂跑四队</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4521,7 +4521,7 @@
         <v>20</v>
       </c>
       <c r="K82" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -4535,17 +4535,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>曾宏飞</t>
+          <t>白永斌</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1045088102</t>
+          <t>256160060</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>思茅蜂跑五队</t>
+          <t>思茅蜂跑四队</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4576,7 +4576,7 @@
         <v>20</v>
       </c>
       <c r="K83" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -4590,17 +4590,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>郭熙</t>
+          <t>谭欣海</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1079452442</t>
+          <t>287795932</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>思茅蜂跑五队</t>
+          <t>思茅蜂跑四队</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4631,7 +4631,7 @@
         <v>20</v>
       </c>
       <c r="K84" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -4645,17 +4645,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>郭栩</t>
+          <t>张永生</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>265884340</t>
+          <t>308807828</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>思茅蜂跑五队</t>
+          <t>思茅蜂跑四队</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4686,7 +4686,7 @@
         <v>20</v>
       </c>
       <c r="K85" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -4700,17 +4700,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>殷啟成</t>
+          <t>李冬杰</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1110070085</t>
+          <t>328840900</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>思茅蜂跑五队</t>
+          <t>思茅蜂跑四队</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4741,7 +4741,7 @@
         <v>20</v>
       </c>
       <c r="K86" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -4755,17 +4755,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>罗江元</t>
+          <t>毛勇</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1049953338</t>
+          <t>1044060042</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>思茅蜂跑五队</t>
+          <t>思茅蜂跑四队</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -4796,7 +4796,7 @@
         <v>20</v>
       </c>
       <c r="K87" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -4810,12 +4810,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>周春亮</t>
+          <t>郭朝坤</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1028562970</t>
+          <t>187384715</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4851,7 +4851,7 @@
         <v>20</v>
       </c>
       <c r="K88" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -4865,12 +4865,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>徐俊杰</t>
+          <t>李子平</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1019518033</t>
+          <t>285715108</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4906,7 +4906,7 @@
         <v>20</v>
       </c>
       <c r="K89" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -4920,12 +4920,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>李新龙</t>
+          <t>曾宏飞</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1097517309</t>
+          <t>1045088102</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4961,7 +4961,7 @@
         <v>20</v>
       </c>
       <c r="K90" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -4975,12 +4975,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>蒋丛华</t>
+          <t>郭熙</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>276619204</t>
+          <t>1079452442</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5016,7 +5016,7 @@
         <v>20</v>
       </c>
       <c r="K91" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -5030,12 +5030,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>刀建华</t>
+          <t>郭栩</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>330888580</t>
+          <t>265884340</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5071,7 +5071,7 @@
         <v>20</v>
       </c>
       <c r="K92" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -5085,12 +5085,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>郑云天</t>
+          <t>殷啟成</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>309340812</t>
+          <t>1110070085</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5126,7 +5126,7 @@
         <v>20</v>
       </c>
       <c r="K93" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -5140,12 +5140,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>李西</t>
+          <t>罗江元</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1127440078</t>
+          <t>1049953338</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5181,7 +5181,7 @@
         <v>20</v>
       </c>
       <c r="K94" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
@@ -5195,12 +5195,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>刀思孟</t>
+          <t>周春亮</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1059874387</t>
+          <t>1028562970</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5236,7 +5236,7 @@
         <v>20</v>
       </c>
       <c r="K95" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
@@ -5250,17 +5250,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>王龙飞</t>
+          <t>徐俊杰</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>330359444</t>
+          <t>1019518033</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>思茅蜂跑六队</t>
+          <t>思茅蜂跑五队</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5291,7 +5291,7 @@
         <v>20</v>
       </c>
       <c r="K96" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
@@ -5305,17 +5305,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>石改新</t>
+          <t>李新龙</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1035136982</t>
+          <t>1097517309</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>思茅蜂跑六队</t>
+          <t>思茅蜂跑五队</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5346,7 +5346,7 @@
         <v>20</v>
       </c>
       <c r="K97" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
@@ -5360,17 +5360,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>杨雄</t>
+          <t>蒋丛华</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>303350396</t>
+          <t>276619204</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>思茅蜂跑六队</t>
+          <t>思茅蜂跑五队</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5401,7 +5401,7 @@
         <v>20</v>
       </c>
       <c r="K98" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -5415,17 +5415,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>罗晓秋</t>
+          <t>刀建华</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>277087084</t>
+          <t>330888580</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>思茅蜂跑六队</t>
+          <t>思茅蜂跑五队</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5456,7 +5456,7 @@
         <v>20</v>
       </c>
       <c r="K99" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -5470,17 +5470,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>李光泽</t>
+          <t>郑云天</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1069710126</t>
+          <t>309340812</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>思茅蜂跑六队</t>
+          <t>思茅蜂跑五队</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5511,7 +5511,7 @@
         <v>20</v>
       </c>
       <c r="K100" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -5525,17 +5525,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>张韩斌</t>
+          <t>李西</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1123350074</t>
+          <t>1127440078</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>思茅蜂跑六队</t>
+          <t>思茅蜂跑五队</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5566,7 +5566,7 @@
         <v>20</v>
       </c>
       <c r="K101" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
@@ -5580,12 +5580,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>郑恩琦</t>
+          <t>王龙飞</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1076905054</t>
+          <t>330359444</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>下午茶1、下午茶2、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5621,7 +5621,7 @@
         <v>20</v>
       </c>
       <c r="K102" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
@@ -5635,12 +5635,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>刀悦</t>
+          <t>石改新</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1137910044</t>
+          <t>1035136982</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>晚高峰、夜宵2、夜宵1</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -5676,7 +5676,7 @@
         <v>20</v>
       </c>
       <c r="K103" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -5690,12 +5690,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>紫龙标</t>
+          <t>杨雄</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1083595205</t>
+          <t>303350396</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5731,7 +5731,7 @@
         <v>20</v>
       </c>
       <c r="K104" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
@@ -5745,12 +5745,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>彭奇伟</t>
+          <t>罗晓秋</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1119321475</t>
+          <t>277087084</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>凌晨1、午高峰、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5800,12 +5800,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>陈旺</t>
+          <t>李光泽</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1148705026</t>
+          <t>1069710126</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5841,7 +5841,7 @@
         <v>20</v>
       </c>
       <c r="K106" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -5855,12 +5855,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>李进明</t>
+          <t>张韩斌</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1123870054</t>
+          <t>1123350074</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>午高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5896,7 +5896,7 @@
         <v>20</v>
       </c>
       <c r="K107" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
@@ -5910,12 +5910,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>王志明</t>
+          <t>郑恩琦</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1042930930</t>
+          <t>1076905054</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>晚高峰、夜宵2、夜宵1</t>
+          <t>下午茶1、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5951,7 +5951,7 @@
         <v>20</v>
       </c>
       <c r="K108" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -5965,12 +5965,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>兰龙</t>
+          <t>紫龙标</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1150771562</t>
+          <t>1083595205</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6006,7 +6006,7 @@
         <v>20</v>
       </c>
       <c r="K109" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -6020,12 +6020,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>董俊才</t>
+          <t>彭奇伟</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1083956676</t>
+          <t>1119321475</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -6061,7 +6061,7 @@
         <v>20</v>
       </c>
       <c r="K110" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
@@ -6075,17 +6075,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>刘智颖</t>
+          <t>陈旺</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>298652316</t>
+          <t>1148705026</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>思茅蜂跑七队</t>
+          <t>思茅蜂跑六队</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -6116,7 +6116,7 @@
         <v>20</v>
       </c>
       <c r="K111" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
@@ -6130,17 +6130,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>李建强</t>
+          <t>李进明</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1108985115</t>
+          <t>1123870054</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>思茅蜂跑七队</t>
+          <t>思茅蜂跑六队</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -6171,7 +6171,7 @@
         <v>20</v>
       </c>
       <c r="K112" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -6185,17 +6185,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>靳熙</t>
+          <t>兰龙</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1090161529</t>
+          <t>1150771562</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>思茅蜂跑七队</t>
+          <t>思茅蜂跑六队</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -6226,7 +6226,7 @@
         <v>20</v>
       </c>
       <c r="K113" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -6240,17 +6240,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>罗成飞</t>
+          <t>董俊才</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>217491379</t>
+          <t>1083956676</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>思茅蜂跑七队</t>
+          <t>思茅蜂跑六队</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -6281,7 +6281,7 @@
         <v>20</v>
       </c>
       <c r="K114" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -6295,17 +6295,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>罗庭坤</t>
+          <t>刀悦</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1019361639</t>
+          <t>1137910044</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>思茅蜂跑七队</t>
+          <t>思茅蜂跑六队</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵2</t>
+          <t>晚高峰、夜宵1、夜宵2</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -6336,7 +6336,7 @@
         <v>20</v>
       </c>
       <c r="K115" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
@@ -6350,17 +6350,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>李勇康</t>
+          <t>王志明</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1055750155</t>
+          <t>1042930930</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>思茅蜂跑七队</t>
+          <t>思茅蜂跑六队</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2</t>
+          <t>下午茶2、晚高峰、夜宵1、夜宵2</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -6391,7 +6391,7 @@
         <v>20</v>
       </c>
       <c r="K116" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -6405,12 +6405,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>郭皓嘉</t>
+          <t>刘智颖</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1087266441</t>
+          <t>298652316</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -6446,7 +6446,7 @@
         <v>20</v>
       </c>
       <c r="K117" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -6460,12 +6460,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>李二</t>
+          <t>李建强</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>90000334955228</t>
+          <t>1108985115</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -6501,7 +6501,7 @@
         <v>20</v>
       </c>
       <c r="K118" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -6515,12 +6515,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>付美依</t>
+          <t>靳熙</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>1117870153</t>
+          <t>1090161529</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -6556,7 +6556,7 @@
         <v>20</v>
       </c>
       <c r="K119" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -6570,12 +6570,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>林光涛</t>
+          <t>罗成飞</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>1125257369</t>
+          <t>217491379</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -6611,7 +6611,7 @@
         <v>20</v>
       </c>
       <c r="K120" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L120" t="n">
         <v>0</v>
@@ -6625,17 +6625,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>胡飞</t>
+          <t>罗庭坤</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>1154325068</t>
+          <t>1019361639</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>思茅蜂跑十队</t>
+          <t>思茅蜂跑七队</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -6666,7 +6666,7 @@
         <v>20</v>
       </c>
       <c r="K121" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="L121" t="n">
         <v>0</v>
@@ -6680,17 +6680,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>李开平</t>
+          <t>李勇康</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>1042226798</t>
+          <t>1055750155</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>思茅蜂跑十队</t>
+          <t>思茅蜂跑七队</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -6721,7 +6721,7 @@
         <v>20</v>
       </c>
       <c r="K122" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
@@ -6735,17 +6735,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>彭跃超</t>
+          <t>郭皓嘉</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>147529594</t>
+          <t>1087266441</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>思茅蜂跑十队</t>
+          <t>思茅蜂跑七队</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -6790,17 +6790,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>陈柏宏</t>
+          <t>李二</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>1121020019</t>
+          <t>90000334955228</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>思茅蜂跑十队</t>
+          <t>思茅蜂跑七队</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -6831,7 +6831,7 @@
         <v>20</v>
       </c>
       <c r="K124" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
@@ -6845,17 +6845,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>白云春</t>
+          <t>付美依</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1040532465</t>
+          <t>1117870153</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>思茅蜂跑十队</t>
+          <t>思茅蜂跑七队</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6886,7 +6886,7 @@
         <v>20</v>
       </c>
       <c r="K125" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L125" t="n">
         <v>0</v>
@@ -6900,17 +6900,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>李荣祝</t>
+          <t>林光涛</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>293180284</t>
+          <t>1125257369</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>思茅蜂跑十队</t>
+          <t>思茅蜂跑七队</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6941,7 +6941,7 @@
         <v>20</v>
       </c>
       <c r="K126" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L126" t="n">
         <v>0</v>
@@ -6955,12 +6955,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>李嘎亮</t>
+          <t>胡飞</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>1147310101</t>
+          <t>1154325068</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -7010,12 +7010,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>田宗平</t>
+          <t>李开平</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1050830056</t>
+          <t>1042226798</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -7051,7 +7051,7 @@
         <v>20</v>
       </c>
       <c r="K128" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L128" t="n">
         <v>0</v>
@@ -7065,12 +7065,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>高梓菘</t>
+          <t>彭跃超</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1065535017</t>
+          <t>147529594</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -7106,7 +7106,7 @@
         <v>20</v>
       </c>
       <c r="K129" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="L129" t="n">
         <v>0</v>
@@ -7120,12 +7120,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>凤玉兴</t>
+          <t>陈柏宏</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1037531500</t>
+          <t>1121020019</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>下午茶2、晚高峰、夜宵2</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -7175,12 +7175,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>周忠宽</t>
+          <t>陈强</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>1154175029</t>
+          <t>1059893263</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>午高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -7230,17 +7230,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>刀俊平</t>
+          <t>白云春</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1019636183</t>
+          <t>1040532465</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>思茅蜂跑十一队</t>
+          <t>思茅蜂跑十队</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -7271,7 +7271,7 @@
         <v>20</v>
       </c>
       <c r="K132" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="L132" t="n">
         <v>0</v>
@@ -7285,17 +7285,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>罗诗洪</t>
+          <t>李荣祝</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1091335309</t>
+          <t>293180284</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>思茅蜂跑十一队</t>
+          <t>思茅蜂跑十队</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -7326,7 +7326,7 @@
         <v>20</v>
       </c>
       <c r="K133" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L133" t="n">
         <v>0</v>
@@ -7340,17 +7340,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>胡明发</t>
+          <t>李嘎亮</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>328151452</t>
+          <t>1147310101</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>思茅蜂跑十一队</t>
+          <t>思茅蜂跑十队</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>午高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -7381,7 +7381,7 @@
         <v>20</v>
       </c>
       <c r="K134" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="L134" t="n">
         <v>0</v>
@@ -7395,17 +7395,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>宗祖江</t>
+          <t>田宗平</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>1093490392</t>
+          <t>1050830056</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>思茅蜂跑十一队</t>
+          <t>思茅蜂跑十队</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -7436,7 +7436,7 @@
         <v>20</v>
       </c>
       <c r="K135" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L135" t="n">
         <v>0</v>
@@ -7450,17 +7450,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>罗开鑫</t>
+          <t>高梓菘</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>1149640115</t>
+          <t>1065535017</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>思茅蜂跑十一队</t>
+          <t>思茅蜂跑十队</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -7491,7 +7491,7 @@
         <v>20</v>
       </c>
       <c r="K136" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
@@ -7505,17 +7505,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>雷国松</t>
+          <t>凤玉兴</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>214339123</t>
+          <t>1037531500</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>思茅蜂跑十一队</t>
+          <t>思茅蜂跑十队</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -7560,17 +7560,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>李真</t>
+          <t>周忠宽</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>1059999192</t>
+          <t>1154175029</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>思茅蜂跑十一队</t>
+          <t>思茅蜂跑十队</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -7601,7 +7601,7 @@
         <v>20</v>
       </c>
       <c r="K138" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
@@ -7615,12 +7615,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>何忠文</t>
+          <t>刀俊平</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>1015977046</t>
+          <t>1019636183</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -7656,7 +7656,7 @@
         <v>20</v>
       </c>
       <c r="K139" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
@@ -7670,12 +7670,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>岩仁</t>
+          <t>罗诗洪</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>1156480048</t>
+          <t>1091335309</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -7711,7 +7711,7 @@
         <v>20</v>
       </c>
       <c r="K140" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -7725,12 +7725,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>王涛</t>
+          <t>宗祖江</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>1052831727</t>
+          <t>1093490392</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -7766,7 +7766,7 @@
         <v>20</v>
       </c>
       <c r="K141" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -7780,17 +7780,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>马恩杰</t>
+          <t>罗开鑫</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>290446620</t>
+          <t>1149640115</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>思茅蜂跑十三队</t>
+          <t>思茅蜂跑十一队</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -7835,17 +7835,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>魏魁</t>
+          <t>雷国松</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>1153735120</t>
+          <t>214339123</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>思茅蜂跑十三队</t>
+          <t>思茅蜂跑十一队</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -7876,7 +7876,7 @@
         <v>20</v>
       </c>
       <c r="K143" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L143" t="n">
         <v>0</v>
@@ -7890,17 +7890,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>徐红</t>
+          <t>李真</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>1067685015</t>
+          <t>1059999192</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>思茅蜂跑十三队</t>
+          <t>思茅蜂跑十一队</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -7931,7 +7931,7 @@
         <v>20</v>
       </c>
       <c r="K144" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -7945,17 +7945,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>罗金伟</t>
+          <t>何忠文</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>1019360308</t>
+          <t>1015977046</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>思茅蜂跑十三队</t>
+          <t>思茅蜂跑十一队</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -7986,7 +7986,7 @@
         <v>20</v>
       </c>
       <c r="K145" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -8000,17 +8000,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>李杰</t>
+          <t>岩仁</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>1035094629</t>
+          <t>1156480048</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>思茅蜂跑十三队</t>
+          <t>思茅蜂跑十一队</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -8041,7 +8041,7 @@
         <v>20</v>
       </c>
       <c r="K146" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L146" t="n">
         <v>0</v>
@@ -8055,17 +8055,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>许英宝</t>
+          <t>王涛</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>1153845086</t>
+          <t>1052831727</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>思茅蜂跑十三队</t>
+          <t>思茅蜂跑十一队</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -8096,7 +8096,7 @@
         <v>20</v>
       </c>
       <c r="K147" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L147" t="n">
         <v>0</v>
@@ -8110,12 +8110,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>贺定军</t>
+          <t>马恩杰</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>1051380786</t>
+          <t>290446620</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -8165,12 +8165,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>李续相</t>
+          <t>徐红</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>310243844</t>
+          <t>1067685015</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -8206,7 +8206,7 @@
         <v>20</v>
       </c>
       <c r="K149" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L149" t="n">
         <v>0</v>
@@ -8220,12 +8220,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>祝涛</t>
+          <t>罗金伟</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>1019304138</t>
+          <t>1019360308</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -8261,7 +8261,7 @@
         <v>20</v>
       </c>
       <c r="K150" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
@@ -8275,12 +8275,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>阿开园</t>
+          <t>李杰</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>1035449050</t>
+          <t>1035094629</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -8316,7 +8316,7 @@
         <v>20</v>
       </c>
       <c r="K151" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L151" t="n">
         <v>0</v>
@@ -8330,12 +8330,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>王俊</t>
+          <t>许英宝</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>303146764</t>
+          <t>1153845086</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>午高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -8371,7 +8371,7 @@
         <v>20</v>
       </c>
       <c r="K152" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -8385,12 +8385,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>黄聪</t>
+          <t>贺定军</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>1130305617</t>
+          <t>1051380786</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -8426,7 +8426,7 @@
         <v>20</v>
       </c>
       <c r="K153" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L153" t="n">
         <v>0</v>
@@ -8440,27 +8440,27 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>杨晓强</t>
+          <t>李续相</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>279931948</t>
+          <t>310243844</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>思茅优远一队</t>
+          <t>思茅蜂跑十三队</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>优远</t>
+          <t>蜂跑</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -8481,7 +8481,7 @@
         <v>20</v>
       </c>
       <c r="K154" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L154" t="n">
         <v>0</v>
@@ -8495,27 +8495,27 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>鲁明春</t>
+          <t>祝涛</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>1033936996</t>
+          <t>1019304138</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>思茅优远一队</t>
+          <t>思茅蜂跑十三队</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>优远</t>
+          <t>蜂跑</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -8536,7 +8536,7 @@
         <v>20</v>
       </c>
       <c r="K155" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="L155" t="n">
         <v>0</v>
@@ -8550,27 +8550,27 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>白文斌</t>
+          <t>阿开园</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>277601740</t>
+          <t>1035449050</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>思茅优远一队</t>
+          <t>思茅蜂跑十三队</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>优远</t>
+          <t>蜂跑</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -8591,7 +8591,7 @@
         <v>20</v>
       </c>
       <c r="K156" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L156" t="n">
         <v>0</v>
@@ -8605,27 +8605,27 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>彭思宸</t>
+          <t>王俊</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>316377628</t>
+          <t>303146764</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>思茅优远一队</t>
+          <t>思茅蜂跑十三队</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>优远</t>
+          <t>蜂跑</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -8646,7 +8646,7 @@
         <v>20</v>
       </c>
       <c r="K157" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L157" t="n">
         <v>0</v>
@@ -8660,27 +8660,27 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>李光升</t>
+          <t>黄聪</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>1112515464</t>
+          <t>1130305617</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>思茅优远一队</t>
+          <t>思茅蜂跑十三队</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>优远</t>
+          <t>蜂跑</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -8701,7 +8701,7 @@
         <v>20</v>
       </c>
       <c r="K158" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L158" t="n">
         <v>0</v>
@@ -8715,12 +8715,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>杨云海</t>
+          <t>鲁明春</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>265785436</t>
+          <t>1033936996</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -8770,12 +8770,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>李晓东</t>
+          <t>白文斌</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>312936500</t>
+          <t>277601740</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -8811,7 +8811,7 @@
         <v>20</v>
       </c>
       <c r="K160" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L160" t="n">
         <v>0</v>
@@ -8825,12 +8825,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>周杰宽</t>
+          <t>彭思宸</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>241046795</t>
+          <t>316377628</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -8866,7 +8866,7 @@
         <v>20</v>
       </c>
       <c r="K161" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L161" t="n">
         <v>0</v>
@@ -8880,12 +8880,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>雷仕华</t>
+          <t>李光升</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>277513820</t>
+          <t>1112515464</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -8921,7 +8921,7 @@
         <v>20</v>
       </c>
       <c r="K162" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L162" t="n">
         <v>0</v>
@@ -8935,12 +8935,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>周正余</t>
+          <t>杨云海</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>331435036</t>
+          <t>265785436</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -8990,12 +8990,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>邱龙涛</t>
+          <t>李晓东</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>328769468</t>
+          <t>312936500</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -9045,12 +9045,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>兰情芳</t>
+          <t>刘癸奇</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>90000338970244</t>
+          <t>294234972</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -9086,7 +9086,7 @@
         <v>20</v>
       </c>
       <c r="K165" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L165" t="n">
         <v>0</v>
@@ -9100,12 +9100,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>刀志鸿</t>
+          <t>周杰宽</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>308511236</t>
+          <t>241046795</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -9155,12 +9155,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>罗庆福</t>
+          <t>雷仕华</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>265204452</t>
+          <t>277513820</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -9175,7 +9175,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -9196,7 +9196,7 @@
         <v>20</v>
       </c>
       <c r="K167" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L167" t="n">
         <v>0</v>
@@ -9210,12 +9210,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>沈正阳</t>
+          <t>罗锦馥</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>1020850421</t>
+          <t>1056121129</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -9251,7 +9251,7 @@
         <v>20</v>
       </c>
       <c r="K168" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L168" t="n">
         <v>0</v>
@@ -9265,12 +9265,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>陈会岭</t>
+          <t>杨忠林</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>202706747</t>
+          <t>1016132235</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -9285,7 +9285,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -9306,7 +9306,7 @@
         <v>20</v>
       </c>
       <c r="K169" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L169" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>李祖顺</t>
+          <t>周正余</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>300606788</t>
+          <t>331435036</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -9361,7 +9361,7 @@
         <v>20</v>
       </c>
       <c r="K170" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L170" t="n">
         <v>0</v>
@@ -9375,12 +9375,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>吴发春</t>
+          <t>魏启东</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>1125257340</t>
+          <t>291727548</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -9416,7 +9416,7 @@
         <v>20</v>
       </c>
       <c r="K171" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L171" t="n">
         <v>0</v>
@@ -9430,12 +9430,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>黄显龙</t>
+          <t>邱龙涛</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>270399468</t>
+          <t>328769468</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -9450,7 +9450,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -9471,7 +9471,7 @@
         <v>20</v>
       </c>
       <c r="K172" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L172" t="n">
         <v>0</v>
@@ -9485,12 +9485,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>朱原庆</t>
+          <t>兰情芳</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>1090480333</t>
+          <t>90000338970244</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -9526,7 +9526,7 @@
         <v>20</v>
       </c>
       <c r="K173" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L173" t="n">
         <v>0</v>
@@ -9540,12 +9540,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>罗杰</t>
+          <t>刀志鸿</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>291486188</t>
+          <t>308511236</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -9560,7 +9560,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -9581,7 +9581,7 @@
         <v>20</v>
       </c>
       <c r="K174" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L174" t="n">
         <v>0</v>
@@ -9595,12 +9595,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>佟露</t>
+          <t>罗庆福</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>1016169126</t>
+          <t>265204452</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -9615,7 +9615,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -9636,7 +9636,7 @@
         <v>20</v>
       </c>
       <c r="K175" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L175" t="n">
         <v>0</v>
@@ -9650,12 +9650,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>李健海</t>
+          <t>李童焘</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>330770764</t>
+          <t>1040564072</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -9670,7 +9670,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>凌晨1、晚高峰</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -9691,7 +9691,7 @@
         <v>20</v>
       </c>
       <c r="K176" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L176" t="n">
         <v>0</v>
@@ -9705,12 +9705,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>周铅超</t>
+          <t>沈正阳</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>157611867</t>
+          <t>1020850421</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -9746,7 +9746,7 @@
         <v>20</v>
       </c>
       <c r="K177" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L177" t="n">
         <v>0</v>
@@ -9760,17 +9760,17 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>匡伊雕</t>
+          <t>祁杨</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>324847356</t>
+          <t>277527332</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -9801,7 +9801,7 @@
         <v>20</v>
       </c>
       <c r="K178" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L178" t="n">
         <v>0</v>
@@ -9815,17 +9815,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>李宏</t>
+          <t>陈会岭</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>293086524</t>
+          <t>202706747</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -9856,7 +9856,7 @@
         <v>20</v>
       </c>
       <c r="K179" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L179" t="n">
         <v>0</v>
@@ -9870,17 +9870,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>赵学初</t>
+          <t>李祖顺</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>290252548</t>
+          <t>300606788</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -9911,7 +9911,7 @@
         <v>20</v>
       </c>
       <c r="K180" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L180" t="n">
         <v>0</v>
@@ -9925,17 +9925,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>李笙福</t>
+          <t>吴发春</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>1115214416</t>
+          <t>1125257340</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -9945,7 +9945,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -9966,7 +9966,7 @@
         <v>20</v>
       </c>
       <c r="K181" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L181" t="n">
         <v>0</v>
@@ -9980,17 +9980,17 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>罗云照</t>
+          <t>李永福</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>297822572</t>
+          <t>313354908</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -10035,17 +10035,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>王俊</t>
+          <t>朱原庆</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>317570748</t>
+          <t>1090480333</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -10076,7 +10076,7 @@
         <v>20</v>
       </c>
       <c r="K183" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L183" t="n">
         <v>0</v>
@@ -10090,17 +10090,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>王兵</t>
+          <t>罗杰</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>330361220</t>
+          <t>291486188</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵2、夜宵1</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -10145,17 +10145,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>李正国</t>
+          <t>佟露</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>261808524</t>
+          <t>1016169126</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -10186,7 +10186,7 @@
         <v>20</v>
       </c>
       <c r="K185" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L185" t="n">
         <v>0</v>
@@ -10200,17 +10200,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>张云强</t>
+          <t>刀太勇</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>1016211018</t>
+          <t>1051720597</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -10220,7 +10220,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -10241,7 +10241,7 @@
         <v>20</v>
       </c>
       <c r="K186" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L186" t="n">
         <v>0</v>
@@ -10255,17 +10255,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>王政元</t>
+          <t>李健海</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>1034685238</t>
+          <t>330770764</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -10275,7 +10275,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -10296,7 +10296,7 @@
         <v>20</v>
       </c>
       <c r="K187" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L187" t="n">
         <v>0</v>
@@ -10310,17 +10310,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>罗师航</t>
+          <t>吴海斌</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>1092599780</t>
+          <t>1052004810</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -10330,7 +10330,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -10351,7 +10351,7 @@
         <v>20</v>
       </c>
       <c r="K188" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L188" t="n">
         <v>0</v>
@@ -10365,17 +10365,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>石福</t>
+          <t>周铅超</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>282612804</t>
+          <t>157611867</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -10406,7 +10406,7 @@
         <v>20</v>
       </c>
       <c r="K189" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L189" t="n">
         <v>0</v>
@@ -10420,17 +10420,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>张仲阳</t>
+          <t>黄显龙</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>273841420</t>
+          <t>270399468</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -10475,12 +10475,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>王世奎</t>
+          <t>匡伊雕</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>320004748</t>
+          <t>324847356</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -10495,7 +10495,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -10516,7 +10516,7 @@
         <v>20</v>
       </c>
       <c r="K191" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L191" t="n">
         <v>0</v>
@@ -10530,17 +10530,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>罗坤</t>
+          <t>李宏</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>1142045554</t>
+          <t>293086524</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -10571,7 +10571,7 @@
         <v>20</v>
       </c>
       <c r="K192" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L192" t="n">
         <v>0</v>
@@ -10585,17 +10585,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>查懿原</t>
+          <t>赵学初</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>276165364</t>
+          <t>290252548</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵2、夜宵1</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -10626,7 +10626,7 @@
         <v>20</v>
       </c>
       <c r="K193" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L193" t="n">
         <v>0</v>
@@ -10640,17 +10640,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>李星龙</t>
+          <t>李笙福</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>1090430076</t>
+          <t>1115214416</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -10660,7 +10660,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -10681,7 +10681,7 @@
         <v>20</v>
       </c>
       <c r="K194" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L194" t="n">
         <v>0</v>
@@ -10695,17 +10695,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>李海瑞</t>
+          <t>李德生</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>1129764787</t>
+          <t>1016030307</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -10715,7 +10715,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -10736,7 +10736,7 @@
         <v>20</v>
       </c>
       <c r="K195" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L195" t="n">
         <v>0</v>
@@ -10750,17 +10750,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>钱学林</t>
+          <t>罗云照</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>1130041012</t>
+          <t>297822572</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -10791,7 +10791,7 @@
         <v>20</v>
       </c>
       <c r="K196" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L196" t="n">
         <v>0</v>
@@ -10805,17 +10805,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>白顺荣</t>
+          <t>杨城鑫</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>1045718631</t>
+          <t>1159670127</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -10846,7 +10846,7 @@
         <v>20</v>
       </c>
       <c r="K197" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L197" t="n">
         <v>0</v>
@@ -10860,17 +10860,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>周明权</t>
+          <t>王俊</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>1158625019</t>
+          <t>317570748</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -10901,7 +10901,7 @@
         <v>20</v>
       </c>
       <c r="K198" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L198" t="n">
         <v>0</v>
@@ -10915,17 +10915,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>曾平</t>
+          <t>王兵</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>1143782010</t>
+          <t>330361220</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰、夜宵2</t>
+          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -10956,7 +10956,7 @@
         <v>20</v>
       </c>
       <c r="K199" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L199" t="n">
         <v>0</v>
@@ -10970,17 +10970,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>梁祖恩</t>
+          <t>李正国</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>1069696308</t>
+          <t>261808524</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -10990,7 +10990,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -11011,7 +11011,7 @@
         <v>20</v>
       </c>
       <c r="K200" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L200" t="n">
         <v>0</v>
@@ -11025,17 +11025,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>付林臣</t>
+          <t>张云强</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>1024206523</t>
+          <t>1016211018</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -11066,7 +11066,7 @@
         <v>20</v>
       </c>
       <c r="K201" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="L201" t="n">
         <v>0</v>
@@ -11080,17 +11080,17 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>罗杰</t>
+          <t>王政元</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>1142566401</t>
+          <t>1034685238</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -11135,17 +11135,17 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>邓迪社</t>
+          <t>罗师航</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>221905563</t>
+          <t>1092599780</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵2、夜宵1</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -11190,17 +11190,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>熊远发</t>
+          <t>石福</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>266314300</t>
+          <t>282612804</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -11210,7 +11210,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵2</t>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -11231,7 +11231,7 @@
         <v>20</v>
       </c>
       <c r="K204" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L204" t="n">
         <v>0</v>
@@ -11245,17 +11245,17 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>黄健翔</t>
+          <t>张仲阳</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>1071071679</t>
+          <t>273841420</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -11265,7 +11265,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -11286,7 +11286,7 @@
         <v>20</v>
       </c>
       <c r="K205" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L205" t="n">
         <v>0</v>
@@ -11300,17 +11300,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>张鹏</t>
+          <t>王世奎</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>1028523558</t>
+          <t>320004748</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -11355,17 +11355,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>杨双辉</t>
+          <t>罗坤</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>264798596</t>
+          <t>1142045554</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -11375,7 +11375,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -11396,7 +11396,7 @@
         <v>20</v>
       </c>
       <c r="K207" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L207" t="n">
         <v>0</v>
@@ -11410,17 +11410,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>肖滔滔</t>
+          <t>查懿原</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>270093300</t>
+          <t>276165364</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -11430,7 +11430,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -11451,7 +11451,7 @@
         <v>20</v>
       </c>
       <c r="K208" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L208" t="n">
         <v>0</v>
@@ -11465,17 +11465,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>匡一鸣</t>
+          <t>李星龙</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>90000340722076</t>
+          <t>1090430076</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -11485,7 +11485,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>晚高峰</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -11506,7 +11506,7 @@
         <v>20</v>
       </c>
       <c r="K209" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L209" t="n">
         <v>0</v>
@@ -11520,17 +11520,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>彭毅勇</t>
+          <t>唐涛</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>175204387</t>
+          <t>277946036</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -11540,7 +11540,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -11575,17 +11575,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>夏彪</t>
+          <t>李海瑞</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>278430252</t>
+          <t>1129764787</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -11595,7 +11595,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -11616,7 +11616,7 @@
         <v>20</v>
       </c>
       <c r="K211" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L211" t="n">
         <v>0</v>
@@ -11630,17 +11630,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>孙帅</t>
+          <t>钱学林</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>227759883</t>
+          <t>1130041012</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -11650,7 +11650,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -11671,7 +11671,7 @@
         <v>20</v>
       </c>
       <c r="K212" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="L212" t="n">
         <v>0</v>
@@ -11685,17 +11685,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>陈明源</t>
+          <t>白顺荣</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>277124636</t>
+          <t>1045718631</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -11705,7 +11705,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -11726,7 +11726,7 @@
         <v>20</v>
       </c>
       <c r="K213" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L213" t="n">
         <v>0</v>
@@ -11740,17 +11740,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>李清林</t>
+          <t>周明权</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>266695804</t>
+          <t>1158625019</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -11760,7 +11760,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -11781,7 +11781,7 @@
         <v>20</v>
       </c>
       <c r="K214" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L214" t="n">
         <v>0</v>
@@ -11795,17 +11795,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>自银号</t>
+          <t>曾平</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>1086868625</t>
+          <t>1143782010</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -11815,7 +11815,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵2、夜宵1</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -11836,7 +11836,7 @@
         <v>20</v>
       </c>
       <c r="K215" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L215" t="n">
         <v>0</v>
@@ -11850,17 +11850,17 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>杨静修</t>
+          <t>梁祖恩</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>281365980</t>
+          <t>1069696308</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -11891,7 +11891,7 @@
         <v>20</v>
       </c>
       <c r="K216" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="L216" t="n">
         <v>0</v>
@@ -11905,17 +11905,17 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>郭莉萍</t>
+          <t>付林臣</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>276709156</t>
+          <t>1024206523</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -11946,7 +11946,7 @@
         <v>20</v>
       </c>
       <c r="K217" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L217" t="n">
         <v>0</v>
@@ -11960,17 +11960,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>陈新文</t>
+          <t>罗杰</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>266350460</t>
+          <t>1142566401</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -11980,7 +11980,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵2、夜宵1</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -12001,7 +12001,7 @@
         <v>20</v>
       </c>
       <c r="K218" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L218" t="n">
         <v>0</v>
@@ -12015,17 +12015,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>罗文龙</t>
+          <t>罗文婷</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>173435307</t>
+          <t>280481452</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -12035,7 +12035,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -12070,53 +12070,1318 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
+          <t>袁翊博</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>1145707189</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>思茅优远四队</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" t="n">
+        <v>480</v>
+      </c>
+      <c r="I220" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" t="n">
+        <v>20</v>
+      </c>
+      <c r="K220" t="n">
+        <v>12</v>
+      </c>
+      <c r="L220" t="n">
+        <v>0</v>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>邓迪社</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>221905563</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="n">
+        <v>480</v>
+      </c>
+      <c r="I221" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" t="n">
+        <v>20</v>
+      </c>
+      <c r="K221" t="n">
+        <v>8</v>
+      </c>
+      <c r="L221" t="n">
+        <v>0</v>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>熊远发</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>266314300</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>午高峰、晚高峰、夜宵1</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G222" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" t="n">
+        <v>480</v>
+      </c>
+      <c r="I222" t="n">
+        <v>0</v>
+      </c>
+      <c r="J222" t="n">
+        <v>20</v>
+      </c>
+      <c r="K222" t="n">
+        <v>6</v>
+      </c>
+      <c r="L222" t="n">
+        <v>0</v>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>黄健翔</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>1071071679</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>早餐2、午高峰、晚高峰</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" t="n">
+        <v>480</v>
+      </c>
+      <c r="I223" t="n">
+        <v>0</v>
+      </c>
+      <c r="J223" t="n">
+        <v>20</v>
+      </c>
+      <c r="K223" t="n">
+        <v>11</v>
+      </c>
+      <c r="L223" t="n">
+        <v>0</v>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>张鹏</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>1028523558</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>午高峰、下午茶2、晚高峰</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G224" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" t="n">
+        <v>480</v>
+      </c>
+      <c r="I224" t="n">
+        <v>0</v>
+      </c>
+      <c r="J224" t="n">
+        <v>20</v>
+      </c>
+      <c r="K224" t="n">
+        <v>13</v>
+      </c>
+      <c r="L224" t="n">
+        <v>0</v>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>杨双辉</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>264798596</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>午高峰、下午茶1、晚高峰</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
+      <c r="H225" t="n">
+        <v>480</v>
+      </c>
+      <c r="I225" t="n">
+        <v>0</v>
+      </c>
+      <c r="J225" t="n">
+        <v>20</v>
+      </c>
+      <c r="K225" t="n">
+        <v>15</v>
+      </c>
+      <c r="L225" t="n">
+        <v>0</v>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>陈晓林</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>278941292</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>午高峰、下午茶1、晚高峰</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" t="n">
+        <v>480</v>
+      </c>
+      <c r="I226" t="n">
+        <v>0</v>
+      </c>
+      <c r="J226" t="n">
+        <v>20</v>
+      </c>
+      <c r="K226" t="n">
+        <v>15</v>
+      </c>
+      <c r="L226" t="n">
+        <v>0</v>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>肖滔滔</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>270093300</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>午高峰、下午茶2、晚高峰</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+      <c r="H227" t="n">
+        <v>480</v>
+      </c>
+      <c r="I227" t="n">
+        <v>0</v>
+      </c>
+      <c r="J227" t="n">
+        <v>20</v>
+      </c>
+      <c r="K227" t="n">
+        <v>8</v>
+      </c>
+      <c r="L227" t="n">
+        <v>0</v>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>普红兵</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>277529860</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>午高峰、下午茶1、晚高峰</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G228" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" t="n">
+        <v>480</v>
+      </c>
+      <c r="I228" t="n">
+        <v>0</v>
+      </c>
+      <c r="J228" t="n">
+        <v>20</v>
+      </c>
+      <c r="K228" t="n">
+        <v>1</v>
+      </c>
+      <c r="L228" t="n">
+        <v>0</v>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>罗俊杰</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>1096790672</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G229" t="n">
+        <v>0</v>
+      </c>
+      <c r="H229" t="n">
+        <v>480</v>
+      </c>
+      <c r="I229" t="n">
+        <v>0</v>
+      </c>
+      <c r="J229" t="n">
+        <v>20</v>
+      </c>
+      <c r="K229" t="n">
+        <v>1</v>
+      </c>
+      <c r="L229" t="n">
+        <v>0</v>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>匡一鸣</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>90000340722076</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" t="n">
+        <v>480</v>
+      </c>
+      <c r="I230" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" t="n">
+        <v>20</v>
+      </c>
+      <c r="K230" t="n">
+        <v>1</v>
+      </c>
+      <c r="L230" t="n">
+        <v>0</v>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>彭毅勇</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>175204387</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>午高峰、下午茶1、晚高峰</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G231" t="n">
+        <v>0</v>
+      </c>
+      <c r="H231" t="n">
+        <v>480</v>
+      </c>
+      <c r="I231" t="n">
+        <v>0</v>
+      </c>
+      <c r="J231" t="n">
+        <v>20</v>
+      </c>
+      <c r="K231" t="n">
+        <v>10</v>
+      </c>
+      <c r="L231" t="n">
+        <v>0</v>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>夏彪</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>278430252</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G232" t="n">
+        <v>0</v>
+      </c>
+      <c r="H232" t="n">
+        <v>480</v>
+      </c>
+      <c r="I232" t="n">
+        <v>0</v>
+      </c>
+      <c r="J232" t="n">
+        <v>20</v>
+      </c>
+      <c r="K232" t="n">
+        <v>12</v>
+      </c>
+      <c r="L232" t="n">
+        <v>0</v>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>孙帅</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>227759883</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
+      <c r="H233" t="n">
+        <v>480</v>
+      </c>
+      <c r="I233" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" t="n">
+        <v>20</v>
+      </c>
+      <c r="K233" t="n">
+        <v>8</v>
+      </c>
+      <c r="L233" t="n">
+        <v>0</v>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>陈明源</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>277124636</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G234" t="n">
+        <v>0</v>
+      </c>
+      <c r="H234" t="n">
+        <v>480</v>
+      </c>
+      <c r="I234" t="n">
+        <v>0</v>
+      </c>
+      <c r="J234" t="n">
+        <v>20</v>
+      </c>
+      <c r="K234" t="n">
+        <v>4</v>
+      </c>
+      <c r="L234" t="n">
+        <v>0</v>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>李清林</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>266695804</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G235" t="n">
+        <v>0</v>
+      </c>
+      <c r="H235" t="n">
+        <v>480</v>
+      </c>
+      <c r="I235" t="n">
+        <v>0</v>
+      </c>
+      <c r="J235" t="n">
+        <v>20</v>
+      </c>
+      <c r="K235" t="n">
+        <v>6</v>
+      </c>
+      <c r="L235" t="n">
+        <v>0</v>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>自银号</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>1086868625</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+      <c r="H236" t="n">
+        <v>480</v>
+      </c>
+      <c r="I236" t="n">
+        <v>0</v>
+      </c>
+      <c r="J236" t="n">
+        <v>20</v>
+      </c>
+      <c r="K236" t="n">
+        <v>13</v>
+      </c>
+      <c r="L236" t="n">
+        <v>0</v>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>杨静修</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>281365980</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G237" t="n">
+        <v>0</v>
+      </c>
+      <c r="H237" t="n">
+        <v>480</v>
+      </c>
+      <c r="I237" t="n">
+        <v>0</v>
+      </c>
+      <c r="J237" t="n">
+        <v>20</v>
+      </c>
+      <c r="K237" t="n">
+        <v>5</v>
+      </c>
+      <c r="L237" t="n">
+        <v>0</v>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>郭莉萍</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>276709156</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>早餐2、午高峰、晚高峰</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G238" t="n">
+        <v>0</v>
+      </c>
+      <c r="H238" t="n">
+        <v>480</v>
+      </c>
+      <c r="I238" t="n">
+        <v>0</v>
+      </c>
+      <c r="J238" t="n">
+        <v>20</v>
+      </c>
+      <c r="K238" t="n">
+        <v>15</v>
+      </c>
+      <c r="L238" t="n">
+        <v>0</v>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>陈新文</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>266350460</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G239" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" t="n">
+        <v>480</v>
+      </c>
+      <c r="I239" t="n">
+        <v>0</v>
+      </c>
+      <c r="J239" t="n">
+        <v>20</v>
+      </c>
+      <c r="K239" t="n">
+        <v>14</v>
+      </c>
+      <c r="L239" t="n">
+        <v>0</v>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>罗文龙</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>173435307</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>午高峰、下午茶2、晚高峰</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
+      <c r="H240" t="n">
+        <v>480</v>
+      </c>
+      <c r="I240" t="n">
+        <v>0</v>
+      </c>
+      <c r="J240" t="n">
+        <v>20</v>
+      </c>
+      <c r="K240" t="n">
+        <v>15</v>
+      </c>
+      <c r="L240" t="n">
+        <v>0</v>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>王仕臣</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>1043620937</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>午高峰、下午茶1、晚高峰</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G241" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" t="n">
+        <v>480</v>
+      </c>
+      <c r="I241" t="n">
+        <v>0</v>
+      </c>
+      <c r="J241" t="n">
+        <v>20</v>
+      </c>
+      <c r="K241" t="n">
+        <v>14</v>
+      </c>
+      <c r="L241" t="n">
+        <v>0</v>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>陶树良</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>278115308</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>午高峰、下午茶2、晚高峰</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G242" t="n">
+        <v>0</v>
+      </c>
+      <c r="H242" t="n">
+        <v>480</v>
+      </c>
+      <c r="I242" t="n">
+        <v>0</v>
+      </c>
+      <c r="J242" t="n">
+        <v>20</v>
+      </c>
+      <c r="K242" t="n">
+        <v>8</v>
+      </c>
+      <c r="L242" t="n">
+        <v>0</v>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
           <t>李杰彪</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
+      <c r="B243" t="inlineStr">
         <is>
           <t>279705460</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr">
+      <c r="C243" t="inlineStr">
         <is>
           <t>思茅优远五队</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
+      <c r="D243" t="inlineStr">
         <is>
           <t>优远</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr">
+      <c r="E243" t="inlineStr">
         <is>
           <t>午高峰</t>
         </is>
       </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>离线</t>
-        </is>
-      </c>
-      <c r="G220" t="n">
-        <v>0</v>
-      </c>
-      <c r="H220" t="n">
-        <v>480</v>
-      </c>
-      <c r="I220" t="n">
-        <v>0</v>
-      </c>
-      <c r="J220" t="n">
-        <v>20</v>
-      </c>
-      <c r="K220" t="n">
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>在线</t>
+        </is>
+      </c>
+      <c r="G243" t="n">
+        <v>0</v>
+      </c>
+      <c r="H243" t="n">
+        <v>480</v>
+      </c>
+      <c r="I243" t="n">
+        <v>0</v>
+      </c>
+      <c r="J243" t="n">
+        <v>20</v>
+      </c>
+      <c r="K243" t="n">
         <v>8</v>
       </c>
-      <c r="L220" t="n">
-        <v>0</v>
-      </c>
-      <c r="M220" t="inlineStr">
+      <c r="L243" t="n">
+        <v>0</v>
+      </c>
+      <c r="M243" t="inlineStr">
         <is>
           <t>预计达标</t>
         </is>

--- a/public/monitor_latest.xlsx
+++ b/public/monitor_latest.xlsx
@@ -245,17 +245,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>汪宗兵</t>
+          <t>鲍家伟</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1037848475</t>
+          <t>1069055452</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>思茅优选二队</t>
+          <t>思茅优选三队</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -265,12 +265,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>凌晨1、午高峰、下午茶1、晚高峰</t>
+          <t>凌晨1、凌晨2、凌晨3、夜宵2</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>在线</t>
+          <t>离线</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -375,7 +375,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>凌晨1、凌晨2、夜宵2</t>
+          <t>凌晨1、凌晨2、凌晨3、夜宵2</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -410,27 +410,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>李童焘</t>
+          <t>李俊杰</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1040564072</t>
+          <t>303569484</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>思茅优远一队</t>
+          <t>思茅优选一队</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>优远</t>
+          <t>优选</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>凌晨1、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -442,35 +442,35 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>有风险</t>
+          <t>预计达标</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>李俊杰</t>
+          <t>苏亚春</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>303569484</t>
+          <t>283451844</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -485,7 +485,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -506,7 +506,7 @@
         <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -520,12 +520,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>邓成毅</t>
+          <t>李翠伟</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1043170062</t>
+          <t>1049933839</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -575,12 +575,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>苏亚春</t>
+          <t>杨海轮</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>283451844</t>
+          <t>290558268</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -616,7 +616,7 @@
         <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -630,12 +630,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>李翠伟</t>
+          <t>胡关浚</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1049933839</t>
+          <t>261536156</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -671,7 +671,7 @@
         <v>20</v>
       </c>
       <c r="K12" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -685,12 +685,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>杨海轮</t>
+          <t>田新宾</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>290558268</t>
+          <t>279429852</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -726,7 +726,7 @@
         <v>20</v>
       </c>
       <c r="K13" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -740,12 +740,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>田新宾</t>
+          <t>陈维富</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>279429852</t>
+          <t>270698852</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>凌晨1、凌晨2</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -781,7 +781,7 @@
         <v>20</v>
       </c>
       <c r="K14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -795,12 +795,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>杨思杰</t>
+          <t>刀荣程</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1082260013</t>
+          <t>1044820977</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -836,7 +836,7 @@
         <v>20</v>
       </c>
       <c r="K15" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -850,12 +850,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>陈维富</t>
+          <t>沈红心</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>270698852</t>
+          <t>1151687559</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>凌晨1、凌晨2</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -891,7 +891,7 @@
         <v>20</v>
       </c>
       <c r="K16" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -905,12 +905,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>刀荣程</t>
+          <t>朱健明</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1044820977</t>
+          <t>1013523131</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>凌晨1、凌晨2、凌晨3、夜宵2</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -960,12 +960,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>沈红心</t>
+          <t>邓成毅</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1151687559</t>
+          <t>1043170062</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1001,7 +1001,7 @@
         <v>20</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1015,12 +1015,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>朱健明</t>
+          <t>杨思杰</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1013523131</t>
+          <t>1082260013</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1035,12 +1035,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>凌晨1、凌晨2、凌晨3、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1056,7 +1056,7 @@
         <v>20</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>早餐2</t>
+          <t>下午茶1</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、夜宵1</t>
+          <t>早餐2、午高峰、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1221,7 +1221,7 @@
         <v>20</v>
       </c>
       <c r="K22" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -1290,12 +1290,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>李金威</t>
+          <t>熊正存</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>281910660</t>
+          <t>1070938748</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1345,12 +1345,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>熊正存</t>
+          <t>马豪</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1070938748</t>
+          <t>1086929921</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1400,12 +1400,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>马豪</t>
+          <t>罗宗辉</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1086929921</t>
+          <t>90000338986940</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1455,12 +1455,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>罗宗辉</t>
+          <t>董宇</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>90000338986940</t>
+          <t>1040981176</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1620,12 +1620,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>尹江涛</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1042321509</t>
+          <t>1051146884</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>下午茶1、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1675,12 +1675,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>杨福云</t>
+          <t>李国斌</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1156896791</t>
+          <t>286239588</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1716,7 +1716,7 @@
         <v>20</v>
       </c>
       <c r="K31" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -1730,12 +1730,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>杨绍元</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>264801124</t>
+          <t>1042321509</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1771,7 +1771,7 @@
         <v>20</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -1785,12 +1785,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>鲍国明</t>
+          <t>杨福云</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1087319378</t>
+          <t>1156896791</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>凌晨1、凌晨2、凌晨3、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1840,12 +1840,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>鲍德斌</t>
+          <t>杨绍元</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>317794948</t>
+          <t>264801124</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1881,7 +1881,7 @@
         <v>20</v>
       </c>
       <c r="K34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -1895,12 +1895,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>王武斌</t>
+          <t>鲍国明</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>300824396</t>
+          <t>1087319378</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>凌晨1、凌晨2、凌晨3、夜宵2</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1936,7 +1936,7 @@
         <v>20</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -1950,12 +1950,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>施发龙</t>
+          <t>鲍德斌</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1060067605</t>
+          <t>317794948</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2005,12 +2005,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>尹江涛</t>
+          <t>王武斌</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1051146884</t>
+          <t>300824396</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2025,12 +2025,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>下午茶1、下午茶2、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>在线</t>
+          <t>离线</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2046,7 +2046,7 @@
         <v>20</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -2060,12 +2060,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>汪宗兵</t>
+          <t>施发龙</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1037848475</t>
+          <t>1060067605</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2080,12 +2080,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>凌晨1、午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>在线</t>
+          <t>离线</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2115,12 +2115,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>王朝顺</t>
+          <t>李金威</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>287127412</t>
+          <t>281910660</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2170,17 +2170,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>鲍家伟</t>
+          <t>王朝顺</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1069055452</t>
+          <t>287127412</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>思茅优选三队</t>
+          <t>思茅优选二队</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2214,7 +2214,7 @@
         <v>15</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -2225,12 +2225,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>杨建国</t>
+          <t>鲍家伟</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1138840186</t>
+          <t>1069055452</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2280,12 +2280,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>李海斌</t>
+          <t>杨建国</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>90000335390900</t>
+          <t>1138840186</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>凌晨1、凌晨2、凌晨3、夜宵2</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2321,7 +2321,7 @@
         <v>20</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -2335,12 +2335,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>王钱</t>
+          <t>李海斌</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>289243292</t>
+          <t>90000335390900</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2390,12 +2390,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>胡锦波</t>
+          <t>王钱</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>316835700</t>
+          <t>289243292</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>凌晨1、凌晨2、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2445,12 +2445,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>普李叶</t>
+          <t>胡锦波</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1019684446</t>
+          <t>316835700</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>凌晨1、凌晨2、凌晨3、夜宵2</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2486,7 +2486,7 @@
         <v>20</v>
       </c>
       <c r="K45" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -2500,12 +2500,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>佟奇</t>
+          <t>普李叶</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>90000336291956</t>
+          <t>1019684446</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2541,7 +2541,7 @@
         <v>20</v>
       </c>
       <c r="K46" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -2555,12 +2555,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>李健伟</t>
+          <t>佟奇</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>264431676</t>
+          <t>90000336291956</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>下午茶1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2596,7 +2596,7 @@
         <v>20</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -2610,12 +2610,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>农光应</t>
+          <t>李健伟</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1142610772</t>
+          <t>264431676</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>下午茶1</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2651,7 +2651,7 @@
         <v>20</v>
       </c>
       <c r="K48" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -2665,12 +2665,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>龙峰</t>
+          <t>农光应</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1087320804</t>
+          <t>1142610772</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2720,12 +2720,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>赵兴跃</t>
+          <t>龙峰</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1045086221</t>
+          <t>1087320804</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>午高峰</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2761,7 +2761,7 @@
         <v>20</v>
       </c>
       <c r="K50" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -2775,27 +2775,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>罗佳杨</t>
+          <t>赵兴跃</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>289157644</t>
+          <t>1045086221</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>思茅蜂跑一队</t>
+          <t>思茅优选三队</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>蜂跑</t>
+          <t>优选</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、夜宵1</t>
+          <t>午高峰</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2816,7 +2816,7 @@
         <v>20</v>
       </c>
       <c r="K51" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -2830,12 +2830,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>李新田</t>
+          <t>罗佳杨</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>320683868</t>
+          <t>289157644</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>下午茶1、下午茶2、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、夜宵1</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2885,12 +2885,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>赵文俊</t>
+          <t>李新田</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1019362134</t>
+          <t>320683868</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>下午茶1、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2926,7 +2926,7 @@
         <v>20</v>
       </c>
       <c r="K53" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -2940,12 +2940,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>袁洲</t>
+          <t>赵文俊</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>332120988</t>
+          <t>1019362134</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2995,12 +2995,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>车俊超</t>
+          <t>郑荣建</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>291997260</t>
+          <t>307784220</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>下午茶1、下午茶2、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3036,7 +3036,7 @@
         <v>20</v>
       </c>
       <c r="K55" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -3050,12 +3050,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>张忠海</t>
+          <t>袁洲</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1003950027</t>
+          <t>332120988</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>早餐2、午高峰</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3091,7 +3091,7 @@
         <v>20</v>
       </c>
       <c r="K56" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -3105,12 +3105,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>王浩</t>
+          <t>车俊超</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1046180007</t>
+          <t>291997260</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>下午茶1、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3146,7 +3146,7 @@
         <v>20</v>
       </c>
       <c r="K57" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -3160,12 +3160,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>李志义</t>
+          <t>张忠海</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1112358704</t>
+          <t>1003950027</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3215,12 +3215,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>王金林</t>
+          <t>王浩</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1125678007</t>
+          <t>1046180007</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
+          <t>早餐2、午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3256,7 +3256,7 @@
         <v>20</v>
       </c>
       <c r="K59" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -3270,12 +3270,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>者少军</t>
+          <t>王金林</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>261859444</t>
+          <t>1125678007</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3325,17 +3325,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>朱加林</t>
+          <t>者少军</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>186839747</t>
+          <t>261859444</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>思茅蜂跑三队</t>
+          <t>思茅蜂跑一队</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3366,7 +3366,7 @@
         <v>20</v>
       </c>
       <c r="K61" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -3380,12 +3380,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>张小华</t>
+          <t>罗晨龙</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>317756532</t>
+          <t>293959380</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3421,7 +3421,7 @@
         <v>20</v>
       </c>
       <c r="K62" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -3435,12 +3435,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>蓝琨</t>
+          <t>朱加林</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1070814423</t>
+          <t>186839747</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3476,7 +3476,7 @@
         <v>20</v>
       </c>
       <c r="K63" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -3490,12 +3490,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>王东奎</t>
+          <t>张小华</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1042700176</t>
+          <t>317756532</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>下午茶2、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3531,7 +3531,7 @@
         <v>20</v>
       </c>
       <c r="K64" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -3545,12 +3545,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>钱思安</t>
+          <t>蓝琨</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>289601204</t>
+          <t>1070814423</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3586,7 +3586,7 @@
         <v>20</v>
       </c>
       <c r="K65" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -3600,12 +3600,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>金富勤</t>
+          <t>王东奎</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>615466374</t>
+          <t>1042700176</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3641,7 +3641,7 @@
         <v>20</v>
       </c>
       <c r="K66" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -3655,12 +3655,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>陈少平</t>
+          <t>钱思安</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1015826982</t>
+          <t>289601204</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3696,7 +3696,7 @@
         <v>20</v>
       </c>
       <c r="K67" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -3710,12 +3710,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>李旺坤</t>
+          <t>金富勤</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1052121306</t>
+          <t>615466374</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3751,7 +3751,7 @@
         <v>20</v>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -3765,12 +3765,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>白凯勇</t>
+          <t>陈少平</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1092736925</t>
+          <t>1015826982</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>下午茶2、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3806,7 +3806,7 @@
         <v>20</v>
       </c>
       <c r="K69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -3820,12 +3820,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>金锐</t>
+          <t>白凯勇</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>292657164</t>
+          <t>1092736925</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3861,7 +3861,7 @@
         <v>20</v>
       </c>
       <c r="K70" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -3916,7 +3916,7 @@
         <v>20</v>
       </c>
       <c r="K71" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -3930,12 +3930,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>罗晨龙</t>
+          <t>金锐</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>293959380</t>
+          <t>292657164</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3971,7 +3971,7 @@
         <v>20</v>
       </c>
       <c r="K72" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -4026,7 +4026,7 @@
         <v>20</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>20</v>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -4260,12 +4260,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>段文斌</t>
+          <t>毕朝军</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>280124636</t>
+          <t>90000334561228</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4301,7 +4301,7 @@
         <v>20</v>
       </c>
       <c r="K78" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -4315,12 +4315,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>施圆章</t>
+          <t>段文斌</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>261823124</t>
+          <t>280124636</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4370,12 +4370,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>罗晓余</t>
+          <t>施圆章</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1150777253</t>
+          <t>261823124</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4411,7 +4411,7 @@
         <v>20</v>
       </c>
       <c r="K80" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -4425,12 +4425,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>李晓春</t>
+          <t>毛勇</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>286141340</t>
+          <t>1044060042</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4466,7 +4466,7 @@
         <v>20</v>
       </c>
       <c r="K81" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -4480,12 +4480,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>罗梦宇</t>
+          <t>罗晓余</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1075569997</t>
+          <t>1150777253</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4521,7 +4521,7 @@
         <v>20</v>
       </c>
       <c r="K82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -4535,12 +4535,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>白永斌</t>
+          <t>李晓春</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>256160060</t>
+          <t>286141340</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4576,7 +4576,7 @@
         <v>20</v>
       </c>
       <c r="K83" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -4590,12 +4590,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>谭欣海</t>
+          <t>罗梦宇</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>287795932</t>
+          <t>1075569997</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4631,7 +4631,7 @@
         <v>20</v>
       </c>
       <c r="K84" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -4645,12 +4645,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>张永生</t>
+          <t>姚天杰</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>308807828</t>
+          <t>1003026879</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4686,7 +4686,7 @@
         <v>20</v>
       </c>
       <c r="K85" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -4700,12 +4700,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>李冬杰</t>
+          <t>白永斌</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>328840900</t>
+          <t>256160060</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4741,7 +4741,7 @@
         <v>20</v>
       </c>
       <c r="K86" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -4755,12 +4755,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>毛勇</t>
+          <t>白启鹏</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1044060042</t>
+          <t>284683276</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>在线</t>
+          <t>离线</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -4796,7 +4796,7 @@
         <v>20</v>
       </c>
       <c r="K87" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -4810,17 +4810,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>郭朝坤</t>
+          <t>谭欣海</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>187384715</t>
+          <t>287795932</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>思茅蜂跑五队</t>
+          <t>思茅蜂跑四队</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4851,7 +4851,7 @@
         <v>20</v>
       </c>
       <c r="K88" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -4865,17 +4865,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>李子平</t>
+          <t>张永生</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>285715108</t>
+          <t>308807828</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>思茅蜂跑五队</t>
+          <t>思茅蜂跑四队</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4906,7 +4906,7 @@
         <v>20</v>
       </c>
       <c r="K89" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -4920,17 +4920,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>曾宏飞</t>
+          <t>郭成红</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1045088102</t>
+          <t>277421812</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>思茅蜂跑五队</t>
+          <t>思茅蜂跑四队</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4975,17 +4975,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>郭熙</t>
+          <t>李冬杰</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1079452442</t>
+          <t>328840900</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>思茅蜂跑五队</t>
+          <t>思茅蜂跑四队</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5016,7 +5016,7 @@
         <v>20</v>
       </c>
       <c r="K91" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -5030,12 +5030,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>郭栩</t>
+          <t>郭朝坤</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>265884340</t>
+          <t>187384715</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5071,7 +5071,7 @@
         <v>20</v>
       </c>
       <c r="K92" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -5085,12 +5085,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>殷啟成</t>
+          <t>李子平</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1110070085</t>
+          <t>285715108</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5140,12 +5140,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>罗江元</t>
+          <t>曾宏飞</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1049953338</t>
+          <t>1045088102</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5181,7 +5181,7 @@
         <v>20</v>
       </c>
       <c r="K94" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
@@ -5195,12 +5195,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>周春亮</t>
+          <t>郭熙</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1028562970</t>
+          <t>1079452442</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5236,7 +5236,7 @@
         <v>20</v>
       </c>
       <c r="K95" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
@@ -5250,12 +5250,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>徐俊杰</t>
+          <t>郭栩</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1019518033</t>
+          <t>265884340</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5291,7 +5291,7 @@
         <v>20</v>
       </c>
       <c r="K96" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
@@ -5305,12 +5305,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>李新龙</t>
+          <t>殷啟成</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1097517309</t>
+          <t>1110070085</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5346,7 +5346,7 @@
         <v>20</v>
       </c>
       <c r="K97" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
@@ -5360,12 +5360,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>蒋丛华</t>
+          <t>罗江元</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>276619204</t>
+          <t>1049953338</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5401,7 +5401,7 @@
         <v>20</v>
       </c>
       <c r="K98" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -5415,12 +5415,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>刀建华</t>
+          <t>周春亮</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>330888580</t>
+          <t>1028562970</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5456,7 +5456,7 @@
         <v>20</v>
       </c>
       <c r="K99" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -5470,12 +5470,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>郑云天</t>
+          <t>徐俊杰</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>309340812</t>
+          <t>1019518033</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5511,7 +5511,7 @@
         <v>20</v>
       </c>
       <c r="K100" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -5525,12 +5525,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>李西</t>
+          <t>李新龙</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1127440078</t>
+          <t>1097517309</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5566,7 +5566,7 @@
         <v>20</v>
       </c>
       <c r="K101" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
@@ -5580,17 +5580,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>王龙飞</t>
+          <t>刀建华</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>330359444</t>
+          <t>330888580</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>思茅蜂跑六队</t>
+          <t>思茅蜂跑五队</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5621,7 +5621,7 @@
         <v>20</v>
       </c>
       <c r="K102" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
@@ -5635,17 +5635,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>石改新</t>
+          <t>郑云天</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1035136982</t>
+          <t>309340812</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>思茅蜂跑六队</t>
+          <t>思茅蜂跑五队</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -5676,7 +5676,7 @@
         <v>20</v>
       </c>
       <c r="K103" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -5690,17 +5690,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>杨雄</t>
+          <t>李西</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>303350396</t>
+          <t>1127440078</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>思茅蜂跑六队</t>
+          <t>思茅蜂跑五队</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -5731,7 +5731,7 @@
         <v>20</v>
       </c>
       <c r="K104" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
@@ -5745,17 +5745,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>罗晓秋</t>
+          <t>刀思孟</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>277087084</t>
+          <t>1059874387</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>思茅蜂跑六队</t>
+          <t>思茅蜂跑五队</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5800,17 +5800,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>李光泽</t>
+          <t>蒋丛华</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1069710126</t>
+          <t>276619204</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>思茅蜂跑六队</t>
+          <t>思茅蜂跑五队</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -5841,7 +5841,7 @@
         <v>20</v>
       </c>
       <c r="K106" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -5855,12 +5855,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>张韩斌</t>
+          <t>王龙飞</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1123350074</t>
+          <t>330359444</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5896,7 +5896,7 @@
         <v>20</v>
       </c>
       <c r="K107" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
@@ -5910,12 +5910,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>郑恩琦</t>
+          <t>石改新</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1076905054</t>
+          <t>1035136982</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>下午茶1、下午茶2、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5951,7 +5951,7 @@
         <v>20</v>
       </c>
       <c r="K108" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -5965,12 +5965,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>紫龙标</t>
+          <t>杨雄</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1083595205</t>
+          <t>303350396</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6006,7 +6006,7 @@
         <v>20</v>
       </c>
       <c r="K109" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -6020,12 +6020,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>彭奇伟</t>
+          <t>罗晓秋</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1119321475</t>
+          <t>277087084</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6061,7 +6061,7 @@
         <v>20</v>
       </c>
       <c r="K110" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
@@ -6075,12 +6075,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>陈旺</t>
+          <t>李光泽</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1148705026</t>
+          <t>1069710126</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6116,7 +6116,7 @@
         <v>20</v>
       </c>
       <c r="K111" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
@@ -6130,12 +6130,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>李进明</t>
+          <t>张韩斌</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1123870054</t>
+          <t>1123350074</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>午高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -6171,7 +6171,7 @@
         <v>20</v>
       </c>
       <c r="K112" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -6185,12 +6185,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>兰龙</t>
+          <t>郑恩琦</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1150771562</t>
+          <t>1076905054</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>下午茶1、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -6226,7 +6226,7 @@
         <v>20</v>
       </c>
       <c r="K113" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -6240,12 +6240,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>董俊才</t>
+          <t>紫龙标</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1083956676</t>
+          <t>1083595205</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -6281,7 +6281,7 @@
         <v>20</v>
       </c>
       <c r="K114" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -6295,12 +6295,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>刀悦</t>
+          <t>彭奇伟</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1137910044</t>
+          <t>1119321475</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>晚高峰、夜宵1、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>在线</t>
+          <t>离线</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -6336,7 +6336,7 @@
         <v>20</v>
       </c>
       <c r="K115" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
@@ -6350,12 +6350,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>王志明</t>
+          <t>陈旺</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1042930930</t>
+          <t>1148705026</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>下午茶2、晚高峰、夜宵1、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>在线</t>
+          <t>离线</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -6405,17 +6405,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>刘智颖</t>
+          <t>李进明</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>298652316</t>
+          <t>1123870054</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>思茅蜂跑七队</t>
+          <t>思茅蜂跑六队</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -6446,7 +6446,7 @@
         <v>20</v>
       </c>
       <c r="K117" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -6460,17 +6460,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>李建强</t>
+          <t>王志明</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1108985115</t>
+          <t>1042930930</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>思茅蜂跑七队</t>
+          <t>思茅蜂跑六队</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>下午茶2、晚高峰、夜宵1、夜宵2</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -6501,7 +6501,7 @@
         <v>20</v>
       </c>
       <c r="K118" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -6515,17 +6515,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>靳熙</t>
+          <t>兰龙</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>1090161529</t>
+          <t>1150771562</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>思茅蜂跑七队</t>
+          <t>思茅蜂跑六队</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -6556,7 +6556,7 @@
         <v>20</v>
       </c>
       <c r="K119" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -6570,17 +6570,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>罗成飞</t>
+          <t>董俊才</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>217491379</t>
+          <t>1083956676</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>思茅蜂跑七队</t>
+          <t>思茅蜂跑六队</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -6611,7 +6611,7 @@
         <v>20</v>
       </c>
       <c r="K120" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L120" t="n">
         <v>0</v>
@@ -6625,12 +6625,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>罗庭坤</t>
+          <t>刘智颖</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>1019361639</t>
+          <t>298652316</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -6666,7 +6666,7 @@
         <v>20</v>
       </c>
       <c r="K121" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L121" t="n">
         <v>0</v>
@@ -6680,12 +6680,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>李勇康</t>
+          <t>李建强</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>1055750155</t>
+          <t>1108985115</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -6721,7 +6721,7 @@
         <v>20</v>
       </c>
       <c r="K122" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>郭皓嘉</t>
+          <t>靳熙</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>1087266441</t>
+          <t>1090161529</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -6776,7 +6776,7 @@
         <v>20</v>
       </c>
       <c r="K123" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
@@ -6790,12 +6790,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>李二</t>
+          <t>罗成飞</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>90000334955228</t>
+          <t>217491379</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -6831,7 +6831,7 @@
         <v>20</v>
       </c>
       <c r="K124" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
@@ -6845,12 +6845,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>付美依</t>
+          <t>李勇康</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1117870153</t>
+          <t>1055750155</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6886,7 +6886,7 @@
         <v>20</v>
       </c>
       <c r="K125" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="L125" t="n">
         <v>0</v>
@@ -6900,12 +6900,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>林光涛</t>
+          <t>郭皓嘉</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1125257369</t>
+          <t>1087266441</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6941,7 +6941,7 @@
         <v>20</v>
       </c>
       <c r="K126" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L126" t="n">
         <v>0</v>
@@ -6955,17 +6955,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>胡飞</t>
+          <t>李二</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>1154325068</t>
+          <t>90000334955228</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>思茅蜂跑十队</t>
+          <t>思茅蜂跑七队</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6996,7 +6996,7 @@
         <v>20</v>
       </c>
       <c r="K127" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L127" t="n">
         <v>0</v>
@@ -7010,17 +7010,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>李开平</t>
+          <t>付美依</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1042226798</t>
+          <t>1117870153</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>思茅蜂跑十队</t>
+          <t>思茅蜂跑七队</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -7065,12 +7065,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>彭跃超</t>
+          <t>胡飞</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>147529594</t>
+          <t>1154325068</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -7106,7 +7106,7 @@
         <v>20</v>
       </c>
       <c r="K129" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L129" t="n">
         <v>0</v>
@@ -7120,12 +7120,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>陈柏宏</t>
+          <t>李开平</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1121020019</t>
+          <t>1042226798</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -7175,12 +7175,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>陈强</t>
+          <t>彭跃超</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>1059893263</t>
+          <t>147529594</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -7216,7 +7216,7 @@
         <v>20</v>
       </c>
       <c r="K131" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="L131" t="n">
         <v>0</v>
@@ -7230,12 +7230,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>白云春</t>
+          <t>陈柏宏</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1040532465</t>
+          <t>1121020019</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -7271,7 +7271,7 @@
         <v>20</v>
       </c>
       <c r="K132" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L132" t="n">
         <v>0</v>
@@ -7285,12 +7285,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>李荣祝</t>
+          <t>陈强</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>293180284</t>
+          <t>1059893263</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -7340,12 +7340,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>李嘎亮</t>
+          <t>白云春</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1147310101</t>
+          <t>1040532465</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -7381,7 +7381,7 @@
         <v>20</v>
       </c>
       <c r="K134" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="L134" t="n">
         <v>0</v>
@@ -7395,12 +7395,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>田宗平</t>
+          <t>李荣祝</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>1050830056</t>
+          <t>293180284</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -7450,12 +7450,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>高梓菘</t>
+          <t>田宗平</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>1065535017</t>
+          <t>1050830056</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -7491,7 +7491,7 @@
         <v>20</v>
       </c>
       <c r="K136" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
@@ -7505,12 +7505,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>凤玉兴</t>
+          <t>高梓菘</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>1037531500</t>
+          <t>1065535017</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>下午茶2、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -7546,7 +7546,7 @@
         <v>20</v>
       </c>
       <c r="K137" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
@@ -7560,12 +7560,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>周忠宽</t>
+          <t>凤玉兴</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>1154175029</t>
+          <t>1037531500</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>午高峰</t>
+          <t>下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -7601,7 +7601,7 @@
         <v>20</v>
       </c>
       <c r="K138" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
@@ -7615,17 +7615,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>刀俊平</t>
+          <t>周忠宽</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>1019636183</t>
+          <t>1154175029</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>思茅蜂跑十一队</t>
+          <t>思茅蜂跑十队</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -7656,7 +7656,7 @@
         <v>20</v>
       </c>
       <c r="K139" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
@@ -7670,12 +7670,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>罗诗洪</t>
+          <t>刀俊平</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>1091335309</t>
+          <t>1019636183</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -7711,7 +7711,7 @@
         <v>20</v>
       </c>
       <c r="K140" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -7725,12 +7725,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>宗祖江</t>
+          <t>罗诗洪</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>1093490392</t>
+          <t>1091335309</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -7766,7 +7766,7 @@
         <v>20</v>
       </c>
       <c r="K141" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -7780,12 +7780,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>罗开鑫</t>
+          <t>胡明发</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>1149640115</t>
+          <t>328151452</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -7800,7 +7800,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -7821,7 +7821,7 @@
         <v>20</v>
       </c>
       <c r="K142" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
@@ -7835,12 +7835,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>雷国松</t>
+          <t>宗祖江</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>214339123</t>
+          <t>1093490392</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -7876,7 +7876,7 @@
         <v>20</v>
       </c>
       <c r="K143" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L143" t="n">
         <v>0</v>
@@ -7890,12 +7890,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>李真</t>
+          <t>罗开鑫</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>1059999192</t>
+          <t>1149640115</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -7931,7 +7931,7 @@
         <v>20</v>
       </c>
       <c r="K144" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -7945,12 +7945,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>何忠文</t>
+          <t>雷国松</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>1015977046</t>
+          <t>214339123</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -7986,7 +7986,7 @@
         <v>20</v>
       </c>
       <c r="K145" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -8000,12 +8000,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>岩仁</t>
+          <t>李真</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>1156480048</t>
+          <t>1059999192</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -8041,7 +8041,7 @@
         <v>20</v>
       </c>
       <c r="K146" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L146" t="n">
         <v>0</v>
@@ -8055,12 +8055,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>王涛</t>
+          <t>何忠文</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>1052831727</t>
+          <t>1015977046</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -8096,7 +8096,7 @@
         <v>20</v>
       </c>
       <c r="K147" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="L147" t="n">
         <v>0</v>
@@ -8110,17 +8110,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>马恩杰</t>
+          <t>岩仁</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>290446620</t>
+          <t>1156480048</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>思茅蜂跑十三队</t>
+          <t>思茅蜂跑十一队</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -8151,7 +8151,7 @@
         <v>20</v>
       </c>
       <c r="K148" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L148" t="n">
         <v>0</v>
@@ -8165,17 +8165,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>徐红</t>
+          <t>王涛</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>1067685015</t>
+          <t>1052831727</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>思茅蜂跑十三队</t>
+          <t>思茅蜂跑十一队</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -8206,7 +8206,7 @@
         <v>20</v>
       </c>
       <c r="K149" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L149" t="n">
         <v>0</v>
@@ -8220,12 +8220,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>罗金伟</t>
+          <t>马恩杰</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>1019360308</t>
+          <t>290446620</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -8261,7 +8261,7 @@
         <v>20</v>
       </c>
       <c r="K150" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
@@ -8275,12 +8275,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>李杰</t>
+          <t>魏魁</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>1035094629</t>
+          <t>1153735120</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -8316,7 +8316,7 @@
         <v>20</v>
       </c>
       <c r="K151" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L151" t="n">
         <v>0</v>
@@ -8330,12 +8330,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>许英宝</t>
+          <t>徐红</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>1153845086</t>
+          <t>1067685015</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -8371,7 +8371,7 @@
         <v>20</v>
       </c>
       <c r="K152" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -8385,12 +8385,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>贺定军</t>
+          <t>罗金伟</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>1051380786</t>
+          <t>1019360308</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -8426,7 +8426,7 @@
         <v>20</v>
       </c>
       <c r="K153" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L153" t="n">
         <v>0</v>
@@ -8440,12 +8440,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>李续相</t>
+          <t>李杰</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>310243844</t>
+          <t>1035094629</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -8460,7 +8460,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -8495,12 +8495,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>祝涛</t>
+          <t>许英宝</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>1019304138</t>
+          <t>1153845086</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -8536,7 +8536,7 @@
         <v>20</v>
       </c>
       <c r="K155" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L155" t="n">
         <v>0</v>
@@ -8550,12 +8550,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>阿开园</t>
+          <t>贺定军</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>1035449050</t>
+          <t>1051380786</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -8591,7 +8591,7 @@
         <v>20</v>
       </c>
       <c r="K156" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L156" t="n">
         <v>0</v>
@@ -8605,12 +8605,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>王俊</t>
+          <t>李续相</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>303146764</t>
+          <t>310243844</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>午高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -8660,12 +8660,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>黄聪</t>
+          <t>祝涛</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>1130305617</t>
+          <t>1019304138</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -8715,27 +8715,27 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>鲁明春</t>
+          <t>阿开园</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>1033936996</t>
+          <t>1035449050</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>思茅优远一队</t>
+          <t>思茅蜂跑十三队</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>优远</t>
+          <t>蜂跑</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -8756,7 +8756,7 @@
         <v>20</v>
       </c>
       <c r="K159" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="L159" t="n">
         <v>0</v>
@@ -8770,27 +8770,27 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>白文斌</t>
+          <t>王俊</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>277601740</t>
+          <t>303146764</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>思茅优远一队</t>
+          <t>思茅蜂跑十三队</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>优远</t>
+          <t>蜂跑</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -8811,7 +8811,7 @@
         <v>20</v>
       </c>
       <c r="K160" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L160" t="n">
         <v>0</v>
@@ -8825,27 +8825,27 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>彭思宸</t>
+          <t>黄聪</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>316377628</t>
+          <t>1130305617</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>思茅优远一队</t>
+          <t>思茅蜂跑十三队</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>优远</t>
+          <t>蜂跑</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -8866,7 +8866,7 @@
         <v>20</v>
       </c>
       <c r="K161" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="L161" t="n">
         <v>0</v>
@@ -8880,12 +8880,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>李光升</t>
+          <t>杨晓强</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>1112515464</t>
+          <t>279931948</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -8921,7 +8921,7 @@
         <v>20</v>
       </c>
       <c r="K162" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L162" t="n">
         <v>0</v>
@@ -8935,12 +8935,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>杨云海</t>
+          <t>鲁明春</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>265785436</t>
+          <t>1033936996</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -8990,12 +8990,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>李晓东</t>
+          <t>白文斌</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>312936500</t>
+          <t>277601740</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -9031,7 +9031,7 @@
         <v>20</v>
       </c>
       <c r="K164" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L164" t="n">
         <v>0</v>
@@ -9045,12 +9045,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>刘癸奇</t>
+          <t>彭思宸</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>294234972</t>
+          <t>316377628</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -9086,7 +9086,7 @@
         <v>20</v>
       </c>
       <c r="K165" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L165" t="n">
         <v>0</v>
@@ -9100,12 +9100,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>周杰宽</t>
+          <t>李光升</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>241046795</t>
+          <t>1112515464</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -9141,7 +9141,7 @@
         <v>20</v>
       </c>
       <c r="K166" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L166" t="n">
         <v>0</v>
@@ -9155,12 +9155,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>雷仕华</t>
+          <t>杨云海</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>277513820</t>
+          <t>265785436</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -9196,7 +9196,7 @@
         <v>20</v>
       </c>
       <c r="K167" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L167" t="n">
         <v>0</v>
@@ -9210,12 +9210,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>罗锦馥</t>
+          <t>李晓东</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>1056121129</t>
+          <t>312936500</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -9251,7 +9251,7 @@
         <v>20</v>
       </c>
       <c r="K168" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L168" t="n">
         <v>0</v>
@@ -9265,12 +9265,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>杨忠林</t>
+          <t>刘癸奇</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>1016132235</t>
+          <t>294234972</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -9285,7 +9285,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -9306,7 +9306,7 @@
         <v>20</v>
       </c>
       <c r="K169" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L169" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>周正余</t>
+          <t>周杰宽</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>331435036</t>
+          <t>241046795</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -9361,7 +9361,7 @@
         <v>20</v>
       </c>
       <c r="K170" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L170" t="n">
         <v>0</v>
@@ -9375,12 +9375,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>魏启东</t>
+          <t>雷仕华</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>291727548</t>
+          <t>277513820</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -9416,7 +9416,7 @@
         <v>20</v>
       </c>
       <c r="K171" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L171" t="n">
         <v>0</v>
@@ -9430,12 +9430,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>邱龙涛</t>
+          <t>罗锦馥</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>328769468</t>
+          <t>1056121129</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -9471,7 +9471,7 @@
         <v>20</v>
       </c>
       <c r="K172" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L172" t="n">
         <v>0</v>
@@ -9485,12 +9485,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>兰情芳</t>
+          <t>杨忠林</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>90000338970244</t>
+          <t>1016132235</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -9505,7 +9505,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -9526,7 +9526,7 @@
         <v>20</v>
       </c>
       <c r="K173" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L173" t="n">
         <v>0</v>
@@ -9540,12 +9540,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>刀志鸿</t>
+          <t>周正余</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>308511236</t>
+          <t>331435036</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -9560,7 +9560,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -9581,7 +9581,7 @@
         <v>20</v>
       </c>
       <c r="K174" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L174" t="n">
         <v>0</v>
@@ -9595,12 +9595,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>罗庆福</t>
+          <t>魏启东</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>265204452</t>
+          <t>291727548</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -9615,7 +9615,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -9636,7 +9636,7 @@
         <v>20</v>
       </c>
       <c r="K175" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L175" t="n">
         <v>0</v>
@@ -9650,12 +9650,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>李童焘</t>
+          <t>邱龙涛</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>1040564072</t>
+          <t>328769468</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -9670,7 +9670,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>凌晨1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -9691,7 +9691,7 @@
         <v>20</v>
       </c>
       <c r="K176" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L176" t="n">
         <v>0</v>
@@ -9705,12 +9705,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>沈正阳</t>
+          <t>兰情芳</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>1020850421</t>
+          <t>90000338970244</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -9746,7 +9746,7 @@
         <v>20</v>
       </c>
       <c r="K177" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L177" t="n">
         <v>0</v>
@@ -9760,12 +9760,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>祁杨</t>
+          <t>刀志鸿</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>277527332</t>
+          <t>308511236</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -9801,7 +9801,7 @@
         <v>20</v>
       </c>
       <c r="K178" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L178" t="n">
         <v>0</v>
@@ -9815,12 +9815,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>陈会岭</t>
+          <t>罗庆福</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>202706747</t>
+          <t>265204452</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -9856,7 +9856,7 @@
         <v>20</v>
       </c>
       <c r="K179" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L179" t="n">
         <v>0</v>
@@ -9870,12 +9870,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>李祖顺</t>
+          <t>李童焘</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>300606788</t>
+          <t>1040564072</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>晚高峰</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -9911,7 +9911,7 @@
         <v>20</v>
       </c>
       <c r="K180" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L180" t="n">
         <v>0</v>
@@ -9925,12 +9925,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>吴发春</t>
+          <t>沈正阳</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>1125257340</t>
+          <t>1020850421</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -9945,7 +9945,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -9966,7 +9966,7 @@
         <v>20</v>
       </c>
       <c r="K181" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L181" t="n">
         <v>0</v>
@@ -9980,12 +9980,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>李永福</t>
+          <t>祁杨</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>313354908</t>
+          <t>277527332</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -10021,7 +10021,7 @@
         <v>20</v>
       </c>
       <c r="K182" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="L182" t="n">
         <v>0</v>
@@ -10035,12 +10035,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>朱原庆</t>
+          <t>陈会岭</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>1090480333</t>
+          <t>202706747</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -10076,7 +10076,7 @@
         <v>20</v>
       </c>
       <c r="K183" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L183" t="n">
         <v>0</v>
@@ -10090,12 +10090,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>罗杰</t>
+          <t>李祖顺</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>291486188</t>
+          <t>300606788</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -10131,7 +10131,7 @@
         <v>20</v>
       </c>
       <c r="K184" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L184" t="n">
         <v>0</v>
@@ -10145,12 +10145,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>佟露</t>
+          <t>吴发春</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>1016169126</t>
+          <t>1125257340</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -10186,7 +10186,7 @@
         <v>20</v>
       </c>
       <c r="K185" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L185" t="n">
         <v>0</v>
@@ -10200,12 +10200,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>刀太勇</t>
+          <t>李永福</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>1051720597</t>
+          <t>313354908</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -10220,7 +10220,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -10241,7 +10241,7 @@
         <v>20</v>
       </c>
       <c r="K186" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L186" t="n">
         <v>0</v>
@@ -10255,12 +10255,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>李健海</t>
+          <t>黄显龙</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>330770764</t>
+          <t>270399468</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -10275,7 +10275,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -10296,7 +10296,7 @@
         <v>20</v>
       </c>
       <c r="K187" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L187" t="n">
         <v>0</v>
@@ -10310,12 +10310,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>吴海斌</t>
+          <t>罗杰</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>1052004810</t>
+          <t>291486188</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -10365,12 +10365,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>周铅超</t>
+          <t>佟露</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>157611867</t>
+          <t>1016169126</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
+          <t>午高峰、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -10406,7 +10406,7 @@
         <v>20</v>
       </c>
       <c r="K189" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L189" t="n">
         <v>0</v>
@@ -10420,12 +10420,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>黄显龙</t>
+          <t>刀太勇</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>270399468</t>
+          <t>1051720597</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>在线</t>
+          <t>离线</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -10461,7 +10461,7 @@
         <v>20</v>
       </c>
       <c r="K190" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L190" t="n">
         <v>0</v>
@@ -10475,17 +10475,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>匡伊雕</t>
+          <t>李健海</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>324847356</t>
+          <t>330770764</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -10495,7 +10495,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -10516,7 +10516,7 @@
         <v>20</v>
       </c>
       <c r="K191" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L191" t="n">
         <v>0</v>
@@ -10530,17 +10530,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>李宏</t>
+          <t>吴海斌</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>293086524</t>
+          <t>1052004810</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -10550,7 +10550,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -10571,7 +10571,7 @@
         <v>20</v>
       </c>
       <c r="K192" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L192" t="n">
         <v>0</v>
@@ -10585,17 +10585,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>赵学初</t>
+          <t>周铅超</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>290252548</t>
+          <t>157611867</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -10626,7 +10626,7 @@
         <v>20</v>
       </c>
       <c r="K193" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L193" t="n">
         <v>0</v>
@@ -10640,17 +10640,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>李笙福</t>
+          <t>朱原庆</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>1115214416</t>
+          <t>1090480333</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -10660,12 +10660,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -10681,7 +10681,7 @@
         <v>20</v>
       </c>
       <c r="K194" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L194" t="n">
         <v>0</v>
@@ -10695,12 +10695,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>李德生</t>
+          <t>匡伊雕</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>1016030307</t>
+          <t>324847356</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -10715,7 +10715,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>午高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -10736,7 +10736,7 @@
         <v>20</v>
       </c>
       <c r="K195" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L195" t="n">
         <v>0</v>
@@ -10750,12 +10750,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>罗云照</t>
+          <t>李宏</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>297822572</t>
+          <t>293086524</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -10791,7 +10791,7 @@
         <v>20</v>
       </c>
       <c r="K196" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L196" t="n">
         <v>0</v>
@@ -10805,12 +10805,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>杨城鑫</t>
+          <t>赵学初</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>1159670127</t>
+          <t>290252548</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -10846,7 +10846,7 @@
         <v>20</v>
       </c>
       <c r="K197" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L197" t="n">
         <v>0</v>
@@ -10860,12 +10860,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>王俊</t>
+          <t>李笙福</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>317570748</t>
+          <t>1115214416</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -10901,7 +10901,7 @@
         <v>20</v>
       </c>
       <c r="K198" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L198" t="n">
         <v>0</v>
@@ -10915,12 +10915,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>王兵</t>
+          <t>李德生</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>330361220</t>
+          <t>1016030307</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
+          <t>午高峰</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -10970,12 +10970,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>李正国</t>
+          <t>罗云照</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>261808524</t>
+          <t>297822572</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -11011,7 +11011,7 @@
         <v>20</v>
       </c>
       <c r="K200" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="L200" t="n">
         <v>0</v>
@@ -11025,12 +11025,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>张云强</t>
+          <t>杨城鑫</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>1016211018</t>
+          <t>1159670127</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -11066,7 +11066,7 @@
         <v>20</v>
       </c>
       <c r="K201" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L201" t="n">
         <v>0</v>
@@ -11080,12 +11080,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>王政元</t>
+          <t>王俊</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>1034685238</t>
+          <t>317570748</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -11121,7 +11121,7 @@
         <v>20</v>
       </c>
       <c r="K202" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L202" t="n">
         <v>0</v>
@@ -11135,12 +11135,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>罗师航</t>
+          <t>王兵</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>1092599780</t>
+          <t>330361220</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -11176,7 +11176,7 @@
         <v>20</v>
       </c>
       <c r="K203" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L203" t="n">
         <v>0</v>
@@ -11190,12 +11190,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>石福</t>
+          <t>李正国</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>282612804</t>
+          <t>261808524</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -11210,7 +11210,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -11231,7 +11231,7 @@
         <v>20</v>
       </c>
       <c r="K204" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L204" t="n">
         <v>0</v>
@@ -11245,12 +11245,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>张仲阳</t>
+          <t>张云强</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>273841420</t>
+          <t>1016211018</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -11265,7 +11265,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -11286,7 +11286,7 @@
         <v>20</v>
       </c>
       <c r="K205" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L205" t="n">
         <v>0</v>
@@ -11300,12 +11300,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>王世奎</t>
+          <t>王政元</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>320004748</t>
+          <t>1034685238</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -11341,7 +11341,7 @@
         <v>20</v>
       </c>
       <c r="K206" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L206" t="n">
         <v>0</v>
@@ -11355,17 +11355,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>罗坤</t>
+          <t>罗师航</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>1142045554</t>
+          <t>1092599780</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -11375,7 +11375,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -11396,7 +11396,7 @@
         <v>20</v>
       </c>
       <c r="K207" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L207" t="n">
         <v>0</v>
@@ -11410,17 +11410,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>查懿原</t>
+          <t>石福</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>276165364</t>
+          <t>282612804</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -11430,7 +11430,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -11451,7 +11451,7 @@
         <v>20</v>
       </c>
       <c r="K208" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L208" t="n">
         <v>0</v>
@@ -11465,17 +11465,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>李星龙</t>
+          <t>张仲阳</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>1090430076</t>
+          <t>273841420</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -11485,7 +11485,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -11506,7 +11506,7 @@
         <v>20</v>
       </c>
       <c r="K209" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L209" t="n">
         <v>0</v>
@@ -11520,17 +11520,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>唐涛</t>
+          <t>王世奎</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>277946036</t>
+          <t>320004748</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -11540,7 +11540,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -11561,7 +11561,7 @@
         <v>20</v>
       </c>
       <c r="K210" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L210" t="n">
         <v>0</v>
@@ -11575,12 +11575,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>李海瑞</t>
+          <t>罗坤</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>1129764787</t>
+          <t>1142045554</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -11595,7 +11595,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -11616,7 +11616,7 @@
         <v>20</v>
       </c>
       <c r="K211" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L211" t="n">
         <v>0</v>
@@ -11630,12 +11630,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>钱学林</t>
+          <t>查懿原</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>1130041012</t>
+          <t>276165364</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -11650,7 +11650,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -11671,7 +11671,7 @@
         <v>20</v>
       </c>
       <c r="K212" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L212" t="n">
         <v>0</v>
@@ -11685,12 +11685,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>白顺荣</t>
+          <t>李星龙</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>1045718631</t>
+          <t>1090430076</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -11705,7 +11705,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>晚高峰</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -11726,7 +11726,7 @@
         <v>20</v>
       </c>
       <c r="K213" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L213" t="n">
         <v>0</v>
@@ -11740,12 +11740,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>周明权</t>
+          <t>唐涛</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>1158625019</t>
+          <t>277946036</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -11760,7 +11760,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -11781,7 +11781,7 @@
         <v>20</v>
       </c>
       <c r="K214" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L214" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>曾平</t>
+          <t>李海瑞</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>1143782010</t>
+          <t>1129764787</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -11815,7 +11815,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -11836,7 +11836,7 @@
         <v>20</v>
       </c>
       <c r="K215" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L215" t="n">
         <v>0</v>
@@ -11850,12 +11850,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>梁祖恩</t>
+          <t>钱学林</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>1069696308</t>
+          <t>1130041012</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -11891,7 +11891,7 @@
         <v>20</v>
       </c>
       <c r="K216" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L216" t="n">
         <v>0</v>
@@ -11905,12 +11905,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>付林臣</t>
+          <t>白顺荣</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>1024206523</t>
+          <t>1045718631</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -11946,7 +11946,7 @@
         <v>20</v>
       </c>
       <c r="K217" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L217" t="n">
         <v>0</v>
@@ -11960,12 +11960,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>罗杰</t>
+          <t>周明权</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>1142566401</t>
+          <t>1158625019</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -12001,7 +12001,7 @@
         <v>20</v>
       </c>
       <c r="K218" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L218" t="n">
         <v>0</v>
@@ -12015,12 +12015,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>罗文婷</t>
+          <t>曾平</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>280481452</t>
+          <t>1143782010</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -12035,7 +12035,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -12056,7 +12056,7 @@
         <v>20</v>
       </c>
       <c r="K219" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L219" t="n">
         <v>0</v>
@@ -12070,12 +12070,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>袁翊博</t>
+          <t>梁祖恩</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>1145707189</t>
+          <t>1069696308</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -12111,7 +12111,7 @@
         <v>20</v>
       </c>
       <c r="K220" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L220" t="n">
         <v>0</v>
@@ -12125,17 +12125,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>邓迪社</t>
+          <t>付林臣</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>221905563</t>
+          <t>1024206523</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -12145,7 +12145,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -12166,7 +12166,7 @@
         <v>20</v>
       </c>
       <c r="K221" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L221" t="n">
         <v>0</v>
@@ -12180,17 +12180,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>熊远发</t>
+          <t>罗杰</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>266314300</t>
+          <t>1142566401</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -12221,7 +12221,7 @@
         <v>20</v>
       </c>
       <c r="K222" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L222" t="n">
         <v>0</v>
@@ -12235,17 +12235,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>黄健翔</t>
+          <t>罗文婷</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>1071071679</t>
+          <t>280481452</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -12255,7 +12255,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -12276,7 +12276,7 @@
         <v>20</v>
       </c>
       <c r="K223" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L223" t="n">
         <v>0</v>
@@ -12290,17 +12290,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>张鹏</t>
+          <t>袁翊博</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>1028523558</t>
+          <t>1145707189</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>思茅优远五队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -12310,7 +12310,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -12331,7 +12331,7 @@
         <v>20</v>
       </c>
       <c r="K224" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L224" t="n">
         <v>0</v>
@@ -12345,12 +12345,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>杨双辉</t>
+          <t>邓迪社</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>264798596</t>
+          <t>221905563</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -12365,7 +12365,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -12386,7 +12386,7 @@
         <v>20</v>
       </c>
       <c r="K225" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L225" t="n">
         <v>0</v>
@@ -12400,12 +12400,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>陈晓林</t>
+          <t>熊远发</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>278941292</t>
+          <t>266314300</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -12420,7 +12420,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -12441,7 +12441,7 @@
         <v>20</v>
       </c>
       <c r="K226" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L226" t="n">
         <v>0</v>
@@ -12455,12 +12455,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>肖滔滔</t>
+          <t>黄健翔</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>270093300</t>
+          <t>1071071679</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -12475,7 +12475,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -12496,7 +12496,7 @@
         <v>20</v>
       </c>
       <c r="K227" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L227" t="n">
         <v>0</v>
@@ -12510,12 +12510,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>普红兵</t>
+          <t>杨双辉</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>277529860</t>
+          <t>264798596</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -12565,12 +12565,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>罗俊杰</t>
+          <t>陈晓林</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>1096790672</t>
+          <t>278941292</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -12606,7 +12606,7 @@
         <v>20</v>
       </c>
       <c r="K229" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L229" t="n">
         <v>0</v>
@@ -12620,12 +12620,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>匡一鸣</t>
+          <t>肖滔滔</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>90000340722076</t>
+          <t>270093300</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -12640,7 +12640,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -12661,7 +12661,7 @@
         <v>20</v>
       </c>
       <c r="K230" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L230" t="n">
         <v>0</v>
@@ -12675,12 +12675,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>彭毅勇</t>
+          <t>普红兵</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>175204387</t>
+          <t>277529860</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -12730,12 +12730,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>夏彪</t>
+          <t>罗俊杰</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>278430252</t>
+          <t>1096790672</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -12750,7 +12750,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -12771,7 +12771,7 @@
         <v>20</v>
       </c>
       <c r="K232" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L232" t="n">
         <v>0</v>
@@ -12785,12 +12785,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>孙帅</t>
+          <t>匡一鸣</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>227759883</t>
+          <t>90000340722076</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -12826,7 +12826,7 @@
         <v>20</v>
       </c>
       <c r="K233" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L233" t="n">
         <v>0</v>
@@ -12840,12 +12840,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>陈明源</t>
+          <t>彭毅勇</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>277124636</t>
+          <t>175204387</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -12860,7 +12860,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -12881,7 +12881,7 @@
         <v>20</v>
       </c>
       <c r="K234" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="L234" t="n">
         <v>0</v>
@@ -12895,12 +12895,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>李清林</t>
+          <t>夏彪</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>266695804</t>
+          <t>278430252</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -12915,7 +12915,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -12936,7 +12936,7 @@
         <v>20</v>
       </c>
       <c r="K235" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L235" t="n">
         <v>0</v>
@@ -12950,12 +12950,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>自银号</t>
+          <t>孙帅</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>1086868625</t>
+          <t>227759883</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -12970,7 +12970,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -12991,7 +12991,7 @@
         <v>20</v>
       </c>
       <c r="K236" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L236" t="n">
         <v>0</v>
@@ -13005,12 +13005,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>杨静修</t>
+          <t>陈明源</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>281365980</t>
+          <t>277124636</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -13025,7 +13025,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -13046,7 +13046,7 @@
         <v>20</v>
       </c>
       <c r="K237" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L237" t="n">
         <v>0</v>
@@ -13060,12 +13060,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>郭莉萍</t>
+          <t>李清林</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>276709156</t>
+          <t>266695804</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -13080,7 +13080,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -13101,7 +13101,7 @@
         <v>20</v>
       </c>
       <c r="K238" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L238" t="n">
         <v>0</v>
@@ -13115,12 +13115,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>陈新文</t>
+          <t>自银号</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>266350460</t>
+          <t>1086868625</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -13156,7 +13156,7 @@
         <v>20</v>
       </c>
       <c r="K239" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L239" t="n">
         <v>0</v>
@@ -13170,12 +13170,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>罗文龙</t>
+          <t>杨静修</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>173435307</t>
+          <t>281365980</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -13190,7 +13190,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -13211,7 +13211,7 @@
         <v>20</v>
       </c>
       <c r="K240" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="L240" t="n">
         <v>0</v>
@@ -13225,12 +13225,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>王仕臣</t>
+          <t>郭莉萍</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>1043620937</t>
+          <t>276709156</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -13245,7 +13245,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -13266,7 +13266,7 @@
         <v>20</v>
       </c>
       <c r="K241" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L241" t="n">
         <v>0</v>
@@ -13280,12 +13280,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>陶树良</t>
+          <t>陈新文</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>278115308</t>
+          <t>266350460</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -13300,7 +13300,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -13321,7 +13321,7 @@
         <v>20</v>
       </c>
       <c r="K242" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L242" t="n">
         <v>0</v>
@@ -13335,53 +13335,218 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
+          <t>罗文龙</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>173435307</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>午高峰、下午茶2、晚高峰</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G243" t="n">
+        <v>0</v>
+      </c>
+      <c r="H243" t="n">
+        <v>480</v>
+      </c>
+      <c r="I243" t="n">
+        <v>0</v>
+      </c>
+      <c r="J243" t="n">
+        <v>20</v>
+      </c>
+      <c r="K243" t="n">
+        <v>15</v>
+      </c>
+      <c r="L243" t="n">
+        <v>0</v>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>王仕臣</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>1043620937</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>午高峰、下午茶1、晚高峰</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G244" t="n">
+        <v>0</v>
+      </c>
+      <c r="H244" t="n">
+        <v>480</v>
+      </c>
+      <c r="I244" t="n">
+        <v>0</v>
+      </c>
+      <c r="J244" t="n">
+        <v>20</v>
+      </c>
+      <c r="K244" t="n">
+        <v>14</v>
+      </c>
+      <c r="L244" t="n">
+        <v>0</v>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
           <t>李杰彪</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
+      <c r="B245" t="inlineStr">
         <is>
           <t>279705460</t>
         </is>
       </c>
-      <c r="C243" t="inlineStr">
+      <c r="C245" t="inlineStr">
         <is>
           <t>思茅优远五队</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr">
+      <c r="D245" t="inlineStr">
         <is>
           <t>优远</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr">
+      <c r="E245" t="inlineStr">
         <is>
           <t>午高峰</t>
         </is>
       </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>在线</t>
-        </is>
-      </c>
-      <c r="G243" t="n">
-        <v>0</v>
-      </c>
-      <c r="H243" t="n">
-        <v>480</v>
-      </c>
-      <c r="I243" t="n">
-        <v>0</v>
-      </c>
-      <c r="J243" t="n">
-        <v>20</v>
-      </c>
-      <c r="K243" t="n">
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G245" t="n">
+        <v>0</v>
+      </c>
+      <c r="H245" t="n">
+        <v>480</v>
+      </c>
+      <c r="I245" t="n">
+        <v>0</v>
+      </c>
+      <c r="J245" t="n">
+        <v>20</v>
+      </c>
+      <c r="K245" t="n">
         <v>8</v>
       </c>
-      <c r="L243" t="n">
-        <v>0</v>
-      </c>
-      <c r="M243" t="inlineStr">
+      <c r="L245" t="n">
+        <v>0</v>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>预计达标</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>陶树良</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>278115308</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>思茅优远五队</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>优远</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>午高峰、下午茶2、晚高峰</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>离线</t>
+        </is>
+      </c>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" t="n">
+        <v>480</v>
+      </c>
+      <c r="I246" t="n">
+        <v>0</v>
+      </c>
+      <c r="J246" t="n">
+        <v>20</v>
+      </c>
+      <c r="K246" t="n">
+        <v>8</v>
+      </c>
+      <c r="L246" t="n">
+        <v>0</v>
+      </c>
+      <c r="M246" t="inlineStr">
         <is>
           <t>预计达标</t>
         </is>

--- a/public/monitor_latest.xlsx
+++ b/public/monitor_latest.xlsx
@@ -176,7 +176,7 @@
         <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -430,7 +430,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -451,7 +451,7 @@
         <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -465,12 +465,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>苏亚春</t>
+          <t>邓成毅</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>283451844</t>
+          <t>1043170062</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -506,7 +506,7 @@
         <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -520,12 +520,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>李翠伟</t>
+          <t>苏亚春</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1049933839</t>
+          <t>283451844</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -561,7 +561,7 @@
         <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -575,12 +575,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>杨海轮</t>
+          <t>李翠伟</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>290558268</t>
+          <t>1049933839</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -616,7 +616,7 @@
         <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -630,12 +630,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>胡关浚</t>
+          <t>杨海轮</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>261536156</t>
+          <t>290558268</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -671,7 +671,7 @@
         <v>20</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -740,12 +740,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>陈维富</t>
+          <t>杨思杰</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>270698852</t>
+          <t>1082260013</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>凌晨1、凌晨2</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -781,7 +781,7 @@
         <v>20</v>
       </c>
       <c r="K14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -795,12 +795,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>刀荣程</t>
+          <t>陈维富</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1044820977</t>
+          <t>270698852</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>凌晨1、凌晨2</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -836,7 +836,7 @@
         <v>20</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -850,12 +850,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>沈红心</t>
+          <t>刀荣程</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1151687559</t>
+          <t>1044820977</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -905,12 +905,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>朱健明</t>
+          <t>沈红心</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1013523131</t>
+          <t>1151687559</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>凌晨1、凌晨2、凌晨3、夜宵2</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -946,7 +946,7 @@
         <v>20</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>邓成毅</t>
+          <t>朱健明</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1043170062</t>
+          <t>1013523131</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>凌晨1、凌晨2、凌晨3、夜宵2</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>在线</t>
+          <t>离线</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1015,12 +1015,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>杨思杰</t>
+          <t>胡关浚</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1082260013</t>
+          <t>261536156</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1056,7 +1056,7 @@
         <v>20</v>
       </c>
       <c r="K19" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>下午茶1</t>
+          <t>早餐2</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1290,12 +1290,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>熊正存</t>
+          <t>李金威</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1070938748</t>
+          <t>281910660</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1345,12 +1345,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>马豪</t>
+          <t>熊正存</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1086929921</t>
+          <t>1070938748</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1400,12 +1400,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>罗宗辉</t>
+          <t>马豪</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>90000338986940</t>
+          <t>1086929921</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1455,12 +1455,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>董宇</t>
+          <t>罗宗辉</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1040981176</t>
+          <t>90000338986940</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1510,12 +1510,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>陶伊翔</t>
+          <t>董宇</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1110435691</t>
+          <t>1040981176</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1565,12 +1565,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>鲁炫</t>
+          <t>陶伊翔</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>90000339224588</t>
+          <t>1110435691</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1606,7 +1606,7 @@
         <v>20</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -1620,12 +1620,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>尹江涛</t>
+          <t>鲁炫</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1051146884</t>
+          <t>90000339224588</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>下午茶1、下午茶2、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1661,7 +1661,7 @@
         <v>20</v>
       </c>
       <c r="K30" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>李国斌</t>
+          <t>尹江涛</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>286239588</t>
+          <t>1051146884</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>下午茶1、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1716,7 +1716,7 @@
         <v>20</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -1730,12 +1730,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>李国斌</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1042321509</t>
+          <t>286239588</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1771,7 +1771,7 @@
         <v>20</v>
       </c>
       <c r="K32" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -1785,12 +1785,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>杨福云</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1156896791</t>
+          <t>1042321509</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1840,12 +1840,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>杨绍元</t>
+          <t>杨福云</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>264801124</t>
+          <t>1156896791</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1881,7 +1881,7 @@
         <v>20</v>
       </c>
       <c r="K34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -1895,12 +1895,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>鲍国明</t>
+          <t>杨绍元</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1087319378</t>
+          <t>264801124</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>凌晨1、凌晨2、凌晨3、夜宵2</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1936,7 +1936,7 @@
         <v>20</v>
       </c>
       <c r="K35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -1950,12 +1950,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>鲍德斌</t>
+          <t>汪宗兵</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>317794948</t>
+          <t>1037848475</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2005,12 +2005,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>王武斌</t>
+          <t>王朝顺</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>300824396</t>
+          <t>287127412</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2046,7 +2046,7 @@
         <v>20</v>
       </c>
       <c r="K37" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -2060,12 +2060,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>施发龙</t>
+          <t>鲍国明</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1060067605</t>
+          <t>1087319378</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
+          <t>凌晨1、凌晨2、凌晨3、夜宵2</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2115,12 +2115,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>李金威</t>
+          <t>鲍德斌</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>281910660</t>
+          <t>317794948</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>在线</t>
+          <t>离线</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -2170,12 +2170,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>王朝顺</t>
+          <t>施发龙</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>287127412</t>
+          <t>1060067605</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>在线</t>
+          <t>离线</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2214,7 +2214,7 @@
         <v>15</v>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>20</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -2596,7 +2596,7 @@
         <v>20</v>
       </c>
       <c r="K47" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -2706,7 +2706,7 @@
         <v>20</v>
       </c>
       <c r="K49" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -2720,12 +2720,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>龙峰</t>
+          <t>赵兴跃</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1087320804</t>
+          <t>1045086221</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
+          <t>午高峰</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2761,7 +2761,7 @@
         <v>20</v>
       </c>
       <c r="K50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>赵兴跃</t>
+          <t>龙峰</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1045086221</t>
+          <t>1087320804</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>午高峰</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -2816,7 +2816,7 @@
         <v>20</v>
       </c>
       <c r="K51" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -2871,7 +2871,7 @@
         <v>20</v>
       </c>
       <c r="K52" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -2981,7 +2981,7 @@
         <v>20</v>
       </c>
       <c r="K54" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>20</v>
       </c>
       <c r="K56" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -3201,7 +3201,7 @@
         <v>20</v>
       </c>
       <c r="K58" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -3270,12 +3270,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>王金林</t>
+          <t>李志义</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1125678007</t>
+          <t>1112358704</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3311,7 +3311,7 @@
         <v>20</v>
       </c>
       <c r="K60" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -3325,12 +3325,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>者少军</t>
+          <t>王金林</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>261859444</t>
+          <t>1125678007</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3380,17 +3380,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>罗晨龙</t>
+          <t>者少军</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>293959380</t>
+          <t>261859444</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>思茅蜂跑三队</t>
+          <t>思茅蜂跑一队</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>下午茶2、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3421,7 +3421,7 @@
         <v>20</v>
       </c>
       <c r="K62" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -3435,12 +3435,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>朱加林</t>
+          <t>罗晨龙</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>186839747</t>
+          <t>293959380</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3476,7 +3476,7 @@
         <v>20</v>
       </c>
       <c r="K63" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -3545,12 +3545,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>蓝琨</t>
+          <t>王东奎</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1070814423</t>
+          <t>1042700176</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3586,7 +3586,7 @@
         <v>20</v>
       </c>
       <c r="K65" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -3600,12 +3600,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>王东奎</t>
+          <t>钱思安</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1042700176</t>
+          <t>289601204</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>下午茶2、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3641,7 +3641,7 @@
         <v>20</v>
       </c>
       <c r="K66" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -3655,12 +3655,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>钱思安</t>
+          <t>金富勤</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>289601204</t>
+          <t>615466374</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3710,12 +3710,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>金富勤</t>
+          <t>陈少平</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>615466374</t>
+          <t>1015826982</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3751,7 +3751,7 @@
         <v>20</v>
       </c>
       <c r="K68" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -3765,12 +3765,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>陈少平</t>
+          <t>李旺坤</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1015826982</t>
+          <t>1052121306</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、夜宵1</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3806,7 +3806,7 @@
         <v>20</v>
       </c>
       <c r="K69" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -3820,12 +3820,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>白凯勇</t>
+          <t>金锐</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1092736925</t>
+          <t>292657164</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3861,7 +3861,7 @@
         <v>20</v>
       </c>
       <c r="K70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -3875,12 +3875,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>刘钦臣</t>
+          <t>蓝琨</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>332133620</t>
+          <t>1070814423</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、夜宵1</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -3930,17 +3930,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>金锐</t>
+          <t>何彪</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>292657164</t>
+          <t>511001013</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>思茅蜂跑三队</t>
+          <t>思茅蜂跑四队</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>下午茶2、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>在线</t>
+          <t>离线</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -3971,7 +3971,7 @@
         <v>20</v>
       </c>
       <c r="K72" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -3985,12 +3985,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>何彪</t>
+          <t>毕航</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>511001013</t>
+          <t>325067300</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4026,7 +4026,7 @@
         <v>20</v>
       </c>
       <c r="K73" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -4040,12 +4040,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>毕航</t>
+          <t>苏志国</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>325067300</t>
+          <t>1011062500</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4081,7 +4081,7 @@
         <v>20</v>
       </c>
       <c r="K74" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -4095,12 +4095,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>苏志国</t>
+          <t>李院辉</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1011062500</t>
+          <t>1140485075</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4136,7 +4136,7 @@
         <v>20</v>
       </c>
       <c r="K75" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -4150,12 +4150,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>李院辉</t>
+          <t>陶改荣</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1140485075</t>
+          <t>1102455067</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4191,7 +4191,7 @@
         <v>20</v>
       </c>
       <c r="K76" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -4205,12 +4205,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>陶改荣</t>
+          <t>段文斌</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1102455067</t>
+          <t>280124636</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4246,7 +4246,7 @@
         <v>20</v>
       </c>
       <c r="K77" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -4260,12 +4260,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>毕朝军</t>
+          <t>施圆章</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>90000334561228</t>
+          <t>261823124</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>午高峰</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4301,7 +4301,7 @@
         <v>20</v>
       </c>
       <c r="K78" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -4315,12 +4315,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>段文斌</t>
+          <t>毛勇</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>280124636</t>
+          <t>1044060042</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4356,7 +4356,7 @@
         <v>20</v>
       </c>
       <c r="K79" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -4370,12 +4370,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>施圆章</t>
+          <t>罗晓余</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>261823124</t>
+          <t>1150777253</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4411,7 +4411,7 @@
         <v>20</v>
       </c>
       <c r="K80" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -4425,12 +4425,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>毛勇</t>
+          <t>李晓春</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1044060042</t>
+          <t>286141340</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4466,7 +4466,7 @@
         <v>20</v>
       </c>
       <c r="K81" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -4480,12 +4480,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>罗晓余</t>
+          <t>罗梦宇</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1150777253</t>
+          <t>1075569997</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4521,7 +4521,7 @@
         <v>20</v>
       </c>
       <c r="K82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -4535,12 +4535,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>李晓春</t>
+          <t>姚天杰</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>286141340</t>
+          <t>1003026879</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4576,7 +4576,7 @@
         <v>20</v>
       </c>
       <c r="K83" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -4590,12 +4590,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>罗梦宇</t>
+          <t>白永斌</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1075569997</t>
+          <t>256160060</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4631,7 +4631,7 @@
         <v>20</v>
       </c>
       <c r="K84" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -4645,12 +4645,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>姚天杰</t>
+          <t>白启鹏</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1003026879</t>
+          <t>284683276</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4686,7 +4686,7 @@
         <v>20</v>
       </c>
       <c r="K85" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -4700,12 +4700,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>白永斌</t>
+          <t>谭欣海</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>256160060</t>
+          <t>287795932</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4741,7 +4741,7 @@
         <v>20</v>
       </c>
       <c r="K86" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -4755,12 +4755,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>白启鹏</t>
+          <t>张永生</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>284683276</t>
+          <t>308807828</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4796,7 +4796,7 @@
         <v>20</v>
       </c>
       <c r="K87" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -4810,12 +4810,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>谭欣海</t>
+          <t>郭成红</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>287795932</t>
+          <t>277421812</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4865,12 +4865,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>张永生</t>
+          <t>李冬杰</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>308807828</t>
+          <t>328840900</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4906,7 +4906,7 @@
         <v>20</v>
       </c>
       <c r="K89" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -4920,17 +4920,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>郭成红</t>
+          <t>郭朝坤</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>277421812</t>
+          <t>187384715</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>思茅蜂跑四队</t>
+          <t>思茅蜂跑五队</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4961,7 +4961,7 @@
         <v>20</v>
       </c>
       <c r="K90" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -4975,17 +4975,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>李冬杰</t>
+          <t>李子平</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>328840900</t>
+          <t>285715108</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>思茅蜂跑四队</t>
+          <t>思茅蜂跑五队</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5030,12 +5030,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>郭朝坤</t>
+          <t>郭熙</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>187384715</t>
+          <t>1079452442</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5071,7 +5071,7 @@
         <v>20</v>
       </c>
       <c r="K92" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -5085,12 +5085,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>李子平</t>
+          <t>郭栩</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>285715108</t>
+          <t>265884340</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5126,7 +5126,7 @@
         <v>20</v>
       </c>
       <c r="K93" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -5140,12 +5140,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>曾宏飞</t>
+          <t>殷啟成</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1045088102</t>
+          <t>1110070085</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5195,12 +5195,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>郭熙</t>
+          <t>周春亮</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1079452442</t>
+          <t>1028562970</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5236,7 +5236,7 @@
         <v>20</v>
       </c>
       <c r="K95" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
@@ -5250,12 +5250,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>郭栩</t>
+          <t>徐俊杰</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>265884340</t>
+          <t>1019518033</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5291,7 +5291,7 @@
         <v>20</v>
       </c>
       <c r="K96" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
@@ -5305,12 +5305,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>殷啟成</t>
+          <t>李新龙</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1110070085</t>
+          <t>1097517309</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5346,7 +5346,7 @@
         <v>20</v>
       </c>
       <c r="K97" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
@@ -5360,12 +5360,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>罗江元</t>
+          <t>蒋丛华</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1049953338</t>
+          <t>276619204</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5401,7 +5401,7 @@
         <v>20</v>
       </c>
       <c r="K98" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -5415,12 +5415,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>周春亮</t>
+          <t>刀建华</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1028562970</t>
+          <t>330888580</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5456,7 +5456,7 @@
         <v>20</v>
       </c>
       <c r="K99" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -5470,12 +5470,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>徐俊杰</t>
+          <t>李西</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1019518033</t>
+          <t>1127440078</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5511,7 +5511,7 @@
         <v>20</v>
       </c>
       <c r="K100" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -5525,12 +5525,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>李新龙</t>
+          <t>刀思孟</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1097517309</t>
+          <t>1059874387</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5566,7 +5566,7 @@
         <v>20</v>
       </c>
       <c r="K101" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
@@ -5580,17 +5580,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>刀建华</t>
+          <t>王龙飞</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>330888580</t>
+          <t>330359444</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>思茅蜂跑五队</t>
+          <t>思茅蜂跑六队</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5635,17 +5635,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>郑云天</t>
+          <t>石改新</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>309340812</t>
+          <t>1035136982</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>思茅蜂跑五队</t>
+          <t>思茅蜂跑六队</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -5676,7 +5676,7 @@
         <v>20</v>
       </c>
       <c r="K103" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -5690,17 +5690,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>李西</t>
+          <t>杨雄</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1127440078</t>
+          <t>303350396</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>思茅蜂跑五队</t>
+          <t>思茅蜂跑六队</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -5731,7 +5731,7 @@
         <v>20</v>
       </c>
       <c r="K104" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
@@ -5745,17 +5745,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>刀思孟</t>
+          <t>罗晓秋</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1059874387</t>
+          <t>277087084</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>思茅蜂跑五队</t>
+          <t>思茅蜂跑六队</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5786,7 +5786,7 @@
         <v>20</v>
       </c>
       <c r="K105" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="L105" t="n">
         <v>0</v>
@@ -5800,17 +5800,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>蒋丛华</t>
+          <t>李光泽</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>276619204</t>
+          <t>1069710126</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>思茅蜂跑五队</t>
+          <t>思茅蜂跑六队</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>在线</t>
+          <t>离线</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -5841,7 +5841,7 @@
         <v>20</v>
       </c>
       <c r="K106" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -5855,12 +5855,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>王龙飞</t>
+          <t>张韩斌</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>330359444</t>
+          <t>1123350074</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5896,7 +5896,7 @@
         <v>20</v>
       </c>
       <c r="K107" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
@@ -5910,12 +5910,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>石改新</t>
+          <t>郑恩琦</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1035136982</t>
+          <t>1076905054</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>下午茶1、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5951,7 +5951,7 @@
         <v>20</v>
       </c>
       <c r="K108" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -5965,12 +5965,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>杨雄</t>
+          <t>刀悦</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>303350396</t>
+          <t>1137910044</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -5985,7 +5985,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>晚高峰、夜宵1、夜宵2</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -6006,7 +6006,7 @@
         <v>20</v>
       </c>
       <c r="K109" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -6020,12 +6020,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>罗晓秋</t>
+          <t>紫龙标</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>277087084</t>
+          <t>1083595205</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -6061,7 +6061,7 @@
         <v>20</v>
       </c>
       <c r="K110" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
@@ -6075,12 +6075,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>李光泽</t>
+          <t>彭奇伟</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1069710126</t>
+          <t>1119321475</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6116,7 +6116,7 @@
         <v>20</v>
       </c>
       <c r="K111" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
@@ -6130,12 +6130,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>张韩斌</t>
+          <t>陈旺</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1123350074</t>
+          <t>1148705026</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -6185,12 +6185,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>郑恩琦</t>
+          <t>李进明</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1076905054</t>
+          <t>1123870054</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>下午茶1、下午茶2、晚高峰、夜宵1</t>
+          <t>午高峰</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -6226,7 +6226,7 @@
         <v>20</v>
       </c>
       <c r="K113" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -6240,12 +6240,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>紫龙标</t>
+          <t>兰龙</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1083595205</t>
+          <t>1150771562</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6281,7 +6281,7 @@
         <v>20</v>
       </c>
       <c r="K114" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -6295,12 +6295,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>彭奇伟</t>
+          <t>董俊才</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1119321475</t>
+          <t>1083956676</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -6336,7 +6336,7 @@
         <v>20</v>
       </c>
       <c r="K115" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
@@ -6350,12 +6350,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>陈旺</t>
+          <t>王志明</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1148705026</t>
+          <t>1042930930</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>下午茶2、晚高峰、夜宵1、夜宵2</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -6391,7 +6391,7 @@
         <v>20</v>
       </c>
       <c r="K116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -6405,17 +6405,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>李进明</t>
+          <t>刘智颖</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1123870054</t>
+          <t>298652316</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>思茅蜂跑六队</t>
+          <t>思茅蜂跑七队</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>午高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -6446,7 +6446,7 @@
         <v>20</v>
       </c>
       <c r="K117" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -6460,17 +6460,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>王志明</t>
+          <t>李建强</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1042930930</t>
+          <t>1108985115</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>思茅蜂跑六队</t>
+          <t>思茅蜂跑七队</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>下午茶2、晚高峰、夜宵1、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -6501,7 +6501,7 @@
         <v>20</v>
       </c>
       <c r="K118" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -6515,17 +6515,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>兰龙</t>
+          <t>靳熙</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>1150771562</t>
+          <t>1090161529</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>思茅蜂跑六队</t>
+          <t>思茅蜂跑七队</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -6556,7 +6556,7 @@
         <v>20</v>
       </c>
       <c r="K119" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -6570,17 +6570,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>董俊才</t>
+          <t>罗成飞</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>1083956676</t>
+          <t>217491379</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>思茅蜂跑六队</t>
+          <t>思茅蜂跑七队</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -6611,7 +6611,7 @@
         <v>20</v>
       </c>
       <c r="K120" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L120" t="n">
         <v>0</v>
@@ -6625,12 +6625,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>刘智颖</t>
+          <t>罗庭坤</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>298652316</t>
+          <t>1019361639</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -6666,7 +6666,7 @@
         <v>20</v>
       </c>
       <c r="K121" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L121" t="n">
         <v>0</v>
@@ -6680,12 +6680,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>李建强</t>
+          <t>李勇康</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>1108985115</t>
+          <t>1055750155</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -6721,7 +6721,7 @@
         <v>20</v>
       </c>
       <c r="K122" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>靳熙</t>
+          <t>郭皓嘉</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>1090161529</t>
+          <t>1087266441</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -6776,7 +6776,7 @@
         <v>20</v>
       </c>
       <c r="K123" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
@@ -6790,12 +6790,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>罗成飞</t>
+          <t>李二</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>217491379</t>
+          <t>90000334955228</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -6831,7 +6831,7 @@
         <v>20</v>
       </c>
       <c r="K124" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
@@ -6845,12 +6845,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>李勇康</t>
+          <t>付美依</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1055750155</t>
+          <t>1117870153</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2</t>
+          <t>午高峰、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6886,7 +6886,7 @@
         <v>20</v>
       </c>
       <c r="K125" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="L125" t="n">
         <v>0</v>
@@ -6900,12 +6900,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>郭皓嘉</t>
+          <t>林光涛</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1087266441</t>
+          <t>1125257369</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6941,7 +6941,7 @@
         <v>20</v>
       </c>
       <c r="K126" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L126" t="n">
         <v>0</v>
@@ -6955,17 +6955,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>李二</t>
+          <t>胡飞</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>90000334955228</t>
+          <t>1154325068</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>思茅蜂跑七队</t>
+          <t>思茅蜂跑十队</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6996,7 +6996,7 @@
         <v>20</v>
       </c>
       <c r="K127" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L127" t="n">
         <v>0</v>
@@ -7010,17 +7010,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>付美依</t>
+          <t>李开平</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>1117870153</t>
+          <t>1042226798</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>思茅蜂跑七队</t>
+          <t>思茅蜂跑十队</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -7065,12 +7065,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>胡飞</t>
+          <t>彭跃超</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>1154325068</t>
+          <t>147529594</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -7106,7 +7106,7 @@
         <v>20</v>
       </c>
       <c r="K129" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="L129" t="n">
         <v>0</v>
@@ -7120,12 +7120,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>李开平</t>
+          <t>陈柏宏</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1042226798</t>
+          <t>1121020019</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -7175,12 +7175,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>彭跃超</t>
+          <t>陈强</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>147529594</t>
+          <t>1059893263</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -7216,7 +7216,7 @@
         <v>20</v>
       </c>
       <c r="K131" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="L131" t="n">
         <v>0</v>
@@ -7230,12 +7230,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>陈柏宏</t>
+          <t>白云春</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1121020019</t>
+          <t>1040532465</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -7271,7 +7271,7 @@
         <v>20</v>
       </c>
       <c r="K132" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L132" t="n">
         <v>0</v>
@@ -7285,12 +7285,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>陈强</t>
+          <t>李荣祝</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>1059893263</t>
+          <t>293180284</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -7340,12 +7340,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>白云春</t>
+          <t>李嘎亮</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1040532465</t>
+          <t>1147310101</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -7381,7 +7381,7 @@
         <v>20</v>
       </c>
       <c r="K134" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="L134" t="n">
         <v>0</v>
@@ -7395,12 +7395,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>李荣祝</t>
+          <t>田宗平</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>293180284</t>
+          <t>1050830056</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -7450,12 +7450,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>田宗平</t>
+          <t>高梓菘</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>1050830056</t>
+          <t>1065535017</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -7491,7 +7491,7 @@
         <v>20</v>
       </c>
       <c r="K136" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
@@ -7505,12 +7505,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>高梓菘</t>
+          <t>凤玉兴</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>1065535017</t>
+          <t>1037531500</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -7546,7 +7546,7 @@
         <v>20</v>
       </c>
       <c r="K137" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
@@ -7560,12 +7560,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>凤玉兴</t>
+          <t>周忠宽</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>1037531500</t>
+          <t>1154175029</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>下午茶2、晚高峰、夜宵1</t>
+          <t>午高峰</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -7615,17 +7615,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>周忠宽</t>
+          <t>刀俊平</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>1154175029</t>
+          <t>1019636183</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>思茅蜂跑十队</t>
+          <t>思茅蜂跑十一队</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>午高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -7656,7 +7656,7 @@
         <v>20</v>
       </c>
       <c r="K139" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
@@ -7670,12 +7670,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>刀俊平</t>
+          <t>罗诗洪</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>1019636183</t>
+          <t>1091335309</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -7711,7 +7711,7 @@
         <v>20</v>
       </c>
       <c r="K140" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -7725,12 +7725,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>罗诗洪</t>
+          <t>胡明发</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>1091335309</t>
+          <t>328151452</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -7766,7 +7766,7 @@
         <v>20</v>
       </c>
       <c r="K141" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -7780,12 +7780,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>胡明发</t>
+          <t>宗祖江</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>328151452</t>
+          <t>1093490392</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -7800,7 +7800,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>午高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -7821,7 +7821,7 @@
         <v>20</v>
       </c>
       <c r="K142" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
@@ -7835,12 +7835,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>宗祖江</t>
+          <t>罗开鑫</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>1093490392</t>
+          <t>1149640115</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -7890,12 +7890,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>罗开鑫</t>
+          <t>雷国松</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>1149640115</t>
+          <t>214339123</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -7931,7 +7931,7 @@
         <v>20</v>
       </c>
       <c r="K144" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -7945,12 +7945,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>雷国松</t>
+          <t>李真</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>214339123</t>
+          <t>1059999192</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -7986,7 +7986,7 @@
         <v>20</v>
       </c>
       <c r="K145" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -8000,12 +8000,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>李真</t>
+          <t>何忠文</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>1059999192</t>
+          <t>1015977046</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -8041,7 +8041,7 @@
         <v>20</v>
       </c>
       <c r="K146" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="L146" t="n">
         <v>0</v>
@@ -8055,12 +8055,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>何忠文</t>
+          <t>岩仁</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>1015977046</t>
+          <t>1156480048</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -8096,7 +8096,7 @@
         <v>20</v>
       </c>
       <c r="K147" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="L147" t="n">
         <v>0</v>
@@ -8110,12 +8110,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>岩仁</t>
+          <t>王涛</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>1156480048</t>
+          <t>1052831727</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -8151,7 +8151,7 @@
         <v>20</v>
       </c>
       <c r="K148" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L148" t="n">
         <v>0</v>
@@ -8165,17 +8165,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>王涛</t>
+          <t>马恩杰</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>1052831727</t>
+          <t>290446620</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>思茅蜂跑十一队</t>
+          <t>思茅蜂跑十三队</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -8206,7 +8206,7 @@
         <v>20</v>
       </c>
       <c r="K149" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L149" t="n">
         <v>0</v>
@@ -8220,12 +8220,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>马恩杰</t>
+          <t>魏魁</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>290446620</t>
+          <t>1153735120</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -8261,7 +8261,7 @@
         <v>20</v>
       </c>
       <c r="K150" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
@@ -8275,12 +8275,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>魏魁</t>
+          <t>徐红</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>1153735120</t>
+          <t>1067685015</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -8316,7 +8316,7 @@
         <v>20</v>
       </c>
       <c r="K151" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L151" t="n">
         <v>0</v>
@@ -8330,12 +8330,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>徐红</t>
+          <t>罗金伟</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>1067685015</t>
+          <t>1019360308</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -8371,7 +8371,7 @@
         <v>20</v>
       </c>
       <c r="K152" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -8385,12 +8385,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>罗金伟</t>
+          <t>李杰</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>1019360308</t>
+          <t>1035094629</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -8426,7 +8426,7 @@
         <v>20</v>
       </c>
       <c r="K153" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="L153" t="n">
         <v>0</v>
@@ -8440,12 +8440,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>李杰</t>
+          <t>许英宝</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>1035094629</t>
+          <t>1153845086</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -8460,7 +8460,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -8481,7 +8481,7 @@
         <v>20</v>
       </c>
       <c r="K154" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L154" t="n">
         <v>0</v>
@@ -8495,12 +8495,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>许英宝</t>
+          <t>贺定军</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>1153845086</t>
+          <t>1051380786</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -8536,7 +8536,7 @@
         <v>20</v>
       </c>
       <c r="K155" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L155" t="n">
         <v>0</v>
@@ -8550,12 +8550,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>贺定军</t>
+          <t>李续相</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>1051380786</t>
+          <t>310243844</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -8591,7 +8591,7 @@
         <v>20</v>
       </c>
       <c r="K156" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L156" t="n">
         <v>0</v>
@@ -8605,12 +8605,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>李续相</t>
+          <t>祝涛</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>310243844</t>
+          <t>1019304138</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -8660,12 +8660,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>祝涛</t>
+          <t>阿开园</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>1019304138</t>
+          <t>1035449050</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -8715,12 +8715,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>阿开园</t>
+          <t>王俊</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>1035449050</t>
+          <t>303146764</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -8770,12 +8770,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>王俊</t>
+          <t>黄聪</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>303146764</t>
+          <t>1130305617</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>午高峰</t>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -8825,27 +8825,27 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>黄聪</t>
+          <t>杨晓强</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>1130305617</t>
+          <t>279931948</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>思茅蜂跑十三队</t>
+          <t>思茅优远一队</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>蜂跑</t>
+          <t>优远</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -8866,7 +8866,7 @@
         <v>20</v>
       </c>
       <c r="K161" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L161" t="n">
         <v>0</v>
@@ -8880,12 +8880,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>杨晓强</t>
+          <t>鲁明春</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>279931948</t>
+          <t>1033936996</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -8921,7 +8921,7 @@
         <v>20</v>
       </c>
       <c r="K162" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="L162" t="n">
         <v>0</v>
@@ -8935,12 +8935,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>鲁明春</t>
+          <t>白文斌</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>1033936996</t>
+          <t>277601740</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -8976,7 +8976,7 @@
         <v>20</v>
       </c>
       <c r="K163" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L163" t="n">
         <v>0</v>
@@ -8990,12 +8990,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>白文斌</t>
+          <t>彭思宸</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>277601740</t>
+          <t>316377628</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -9031,7 +9031,7 @@
         <v>20</v>
       </c>
       <c r="K164" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L164" t="n">
         <v>0</v>
@@ -9045,12 +9045,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>彭思宸</t>
+          <t>李光升</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>316377628</t>
+          <t>1112515464</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -9086,7 +9086,7 @@
         <v>20</v>
       </c>
       <c r="K165" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L165" t="n">
         <v>0</v>
@@ -9100,12 +9100,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>李光升</t>
+          <t>杨云海</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>1112515464</t>
+          <t>265785436</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -9141,7 +9141,7 @@
         <v>20</v>
       </c>
       <c r="K166" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L166" t="n">
         <v>0</v>
@@ -9155,12 +9155,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>杨云海</t>
+          <t>李晓东</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>265785436</t>
+          <t>312936500</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -9196,7 +9196,7 @@
         <v>20</v>
       </c>
       <c r="K167" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L167" t="n">
         <v>0</v>
@@ -9210,12 +9210,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>李晓东</t>
+          <t>刘癸奇</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>312936500</t>
+          <t>294234972</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -9265,12 +9265,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>刘癸奇</t>
+          <t>周杰宽</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>294234972</t>
+          <t>241046795</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -9285,7 +9285,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -9306,7 +9306,7 @@
         <v>20</v>
       </c>
       <c r="K169" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L169" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>周杰宽</t>
+          <t>雷仕华</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>241046795</t>
+          <t>277513820</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -9361,7 +9361,7 @@
         <v>20</v>
       </c>
       <c r="K170" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L170" t="n">
         <v>0</v>
@@ -9375,12 +9375,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>雷仕华</t>
+          <t>罗锦馥</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>277513820</t>
+          <t>1056121129</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -9430,12 +9430,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>罗锦馥</t>
+          <t>杨忠林</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>1056121129</t>
+          <t>1016132235</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -9450,7 +9450,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -9485,12 +9485,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>杨忠林</t>
+          <t>周正余</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>1016132235</t>
+          <t>331435036</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -9505,7 +9505,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -9526,7 +9526,7 @@
         <v>20</v>
       </c>
       <c r="K173" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L173" t="n">
         <v>0</v>
@@ -9540,12 +9540,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>周正余</t>
+          <t>魏启东</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>331435036</t>
+          <t>291727548</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -9560,7 +9560,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -9581,7 +9581,7 @@
         <v>20</v>
       </c>
       <c r="K174" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L174" t="n">
         <v>0</v>
@@ -9595,12 +9595,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>魏启东</t>
+          <t>邱龙涛</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>291727548</t>
+          <t>328769468</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -9615,7 +9615,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -9636,7 +9636,7 @@
         <v>20</v>
       </c>
       <c r="K175" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L175" t="n">
         <v>0</v>
@@ -9650,12 +9650,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>邱龙涛</t>
+          <t>兰情芳</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>328769468</t>
+          <t>90000338970244</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -9705,12 +9705,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>兰情芳</t>
+          <t>刀志鸿</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>90000338970244</t>
+          <t>308511236</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -9760,12 +9760,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>刀志鸿</t>
+          <t>罗庆福</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>308511236</t>
+          <t>265204452</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -9801,7 +9801,7 @@
         <v>20</v>
       </c>
       <c r="K178" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L178" t="n">
         <v>0</v>
@@ -9815,12 +9815,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>罗庆福</t>
+          <t>李童焘</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>265204452</t>
+          <t>1040564072</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>晚高峰</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -9856,7 +9856,7 @@
         <v>20</v>
       </c>
       <c r="K179" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L179" t="n">
         <v>0</v>
@@ -9870,12 +9870,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>李童焘</t>
+          <t>沈正阳</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>1040564072</t>
+          <t>1020850421</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -9911,7 +9911,7 @@
         <v>20</v>
       </c>
       <c r="K180" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L180" t="n">
         <v>0</v>
@@ -9925,12 +9925,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>沈正阳</t>
+          <t>祁杨</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>1020850421</t>
+          <t>277527332</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -9945,7 +9945,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -9966,7 +9966,7 @@
         <v>20</v>
       </c>
       <c r="K181" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L181" t="n">
         <v>0</v>
@@ -9980,12 +9980,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>祁杨</t>
+          <t>陈会岭</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>277527332</t>
+          <t>202706747</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -10021,7 +10021,7 @@
         <v>20</v>
       </c>
       <c r="K182" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L182" t="n">
         <v>0</v>
@@ -10035,12 +10035,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>陈会岭</t>
+          <t>李祖顺</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>202706747</t>
+          <t>300606788</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -10076,7 +10076,7 @@
         <v>20</v>
       </c>
       <c r="K183" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L183" t="n">
         <v>0</v>
@@ -10090,12 +10090,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>李祖顺</t>
+          <t>吴发春</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>300606788</t>
+          <t>1125257340</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -10131,7 +10131,7 @@
         <v>20</v>
       </c>
       <c r="K184" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L184" t="n">
         <v>0</v>
@@ -10145,12 +10145,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>吴发春</t>
+          <t>李永福</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>1125257340</t>
+          <t>313354908</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -10186,7 +10186,7 @@
         <v>20</v>
       </c>
       <c r="K185" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L185" t="n">
         <v>0</v>
@@ -10200,12 +10200,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>李永福</t>
+          <t>黄显龙</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>313354908</t>
+          <t>270399468</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -10220,7 +10220,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵2</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -10241,7 +10241,7 @@
         <v>20</v>
       </c>
       <c r="K186" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L186" t="n">
         <v>0</v>
@@ -10255,12 +10255,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>黄显龙</t>
+          <t>朱原庆</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>270399468</t>
+          <t>1090480333</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -10275,7 +10275,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰、夜宵2</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -10296,7 +10296,7 @@
         <v>20</v>
       </c>
       <c r="K187" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L187" t="n">
         <v>0</v>
@@ -10351,7 +10351,7 @@
         <v>20</v>
       </c>
       <c r="K188" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L188" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
         <v>20</v>
       </c>
       <c r="K189" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L189" t="n">
         <v>0</v>
@@ -10640,17 +10640,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>朱原庆</t>
+          <t>匡伊雕</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>1090480333</t>
+          <t>324847356</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>思茅优远一队</t>
+          <t>思茅优远二队</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -10660,12 +10660,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>在线</t>
+          <t>离线</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -10681,7 +10681,7 @@
         <v>20</v>
       </c>
       <c r="K194" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L194" t="n">
         <v>0</v>
@@ -10695,12 +10695,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>匡伊雕</t>
+          <t>李宏</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>324847356</t>
+          <t>293086524</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -10715,7 +10715,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -10736,7 +10736,7 @@
         <v>20</v>
       </c>
       <c r="K195" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L195" t="n">
         <v>0</v>
@@ -10750,12 +10750,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>李宏</t>
+          <t>赵学初</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>293086524</t>
+          <t>290252548</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -10791,7 +10791,7 @@
         <v>20</v>
       </c>
       <c r="K196" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L196" t="n">
         <v>0</v>
@@ -10805,12 +10805,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>赵学初</t>
+          <t>李笙福</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>290252548</t>
+          <t>1115214416</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -10846,7 +10846,7 @@
         <v>20</v>
       </c>
       <c r="K197" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L197" t="n">
         <v>0</v>
@@ -10860,12 +10860,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>李笙福</t>
+          <t>李德生</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>1115214416</t>
+          <t>1016030307</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -10901,7 +10901,7 @@
         <v>20</v>
       </c>
       <c r="K198" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L198" t="n">
         <v>0</v>
@@ -10915,12 +10915,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>李德生</t>
+          <t>罗云照</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>1016030307</t>
+          <t>297822572</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>午高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -10956,7 +10956,7 @@
         <v>20</v>
       </c>
       <c r="K199" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L199" t="n">
         <v>0</v>
@@ -10970,12 +10970,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>罗云照</t>
+          <t>杨城鑫</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>297822572</t>
+          <t>1159670127</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -10990,7 +10990,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -11011,7 +11011,7 @@
         <v>20</v>
       </c>
       <c r="K200" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L200" t="n">
         <v>0</v>
@@ -11025,12 +11025,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>杨城鑫</t>
+          <t>王俊</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>1159670127</t>
+          <t>317570748</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -11066,7 +11066,7 @@
         <v>20</v>
       </c>
       <c r="K201" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L201" t="n">
         <v>0</v>
@@ -11080,12 +11080,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>王俊</t>
+          <t>王兵</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>317570748</t>
+          <t>330361220</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -11121,7 +11121,7 @@
         <v>20</v>
       </c>
       <c r="K202" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L202" t="n">
         <v>0</v>
@@ -11135,12 +11135,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>王兵</t>
+          <t>李正国</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>330361220</t>
+          <t>261808524</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -11176,7 +11176,7 @@
         <v>20</v>
       </c>
       <c r="K203" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L203" t="n">
         <v>0</v>
@@ -11190,12 +11190,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>李正国</t>
+          <t>张云强</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>261808524</t>
+          <t>1016211018</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -11210,7 +11210,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -11231,7 +11231,7 @@
         <v>20</v>
       </c>
       <c r="K204" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L204" t="n">
         <v>0</v>
@@ -11245,12 +11245,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>张云强</t>
+          <t>王政元</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>1016211018</t>
+          <t>1034685238</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -11265,7 +11265,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -11286,7 +11286,7 @@
         <v>20</v>
       </c>
       <c r="K205" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L205" t="n">
         <v>0</v>
@@ -11300,12 +11300,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>王政元</t>
+          <t>罗师航</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>1034685238</t>
+          <t>1092599780</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -11341,7 +11341,7 @@
         <v>20</v>
       </c>
       <c r="K206" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L206" t="n">
         <v>0</v>
@@ -11355,12 +11355,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>罗师航</t>
+          <t>石福</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>1092599780</t>
+          <t>282612804</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -11375,7 +11375,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>早餐2、午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -11410,12 +11410,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>石福</t>
+          <t>张仲阳</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>282612804</t>
+          <t>273841420</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -11430,7 +11430,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -11451,7 +11451,7 @@
         <v>20</v>
       </c>
       <c r="K208" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L208" t="n">
         <v>0</v>
@@ -11465,12 +11465,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>张仲阳</t>
+          <t>王世奎</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>273841420</t>
+          <t>320004748</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -11485,7 +11485,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -11506,7 +11506,7 @@
         <v>20</v>
       </c>
       <c r="K209" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L209" t="n">
         <v>0</v>
@@ -11520,17 +11520,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>王世奎</t>
+          <t>罗坤</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>320004748</t>
+          <t>1142045554</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>思茅优远二队</t>
+          <t>思茅优远四队</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -11540,7 +11540,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -11561,7 +11561,7 @@
         <v>20</v>
       </c>
       <c r="K210" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L210" t="n">
         <v>0</v>
@@ -11575,12 +11575,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>罗坤</t>
+          <t>唐涛</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>1142045554</t>
+          <t>277946036</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -11595,7 +11595,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -11616,7 +11616,7 @@
         <v>20</v>
       </c>
       <c r="K211" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L211" t="n">
         <v>0</v>
@@ -11630,12 +11630,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>查懿原</t>
+          <t>李海瑞</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>276165364</t>
+          <t>1129764787</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -11650,7 +11650,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -11671,7 +11671,7 @@
         <v>20</v>
       </c>
       <c r="K212" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L212" t="n">
         <v>0</v>
@@ -11685,12 +11685,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>李星龙</t>
+          <t>钱学林</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>1090430076</t>
+          <t>1130041012</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -11705,7 +11705,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -11726,7 +11726,7 @@
         <v>20</v>
       </c>
       <c r="K213" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L213" t="n">
         <v>0</v>
@@ -11740,12 +11740,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>唐涛</t>
+          <t>白顺荣</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>277946036</t>
+          <t>1045718631</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -11760,7 +11760,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -11781,7 +11781,7 @@
         <v>20</v>
       </c>
       <c r="K214" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L214" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>李海瑞</t>
+          <t>周明权</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>1129764787</t>
+          <t>1158625019</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -11836,7 +11836,7 @@
         <v>20</v>
       </c>
       <c r="K215" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L215" t="n">
         <v>0</v>
@@ -11850,12 +11850,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>钱学林</t>
+          <t>曾平</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>1130041012</t>
+          <t>1143782010</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -11891,7 +11891,7 @@
         <v>20</v>
       </c>
       <c r="K216" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L216" t="n">
         <v>0</v>
@@ -11905,12 +11905,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>白顺荣</t>
+          <t>梁祖恩</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>1045718631</t>
+          <t>1069696308</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -11946,7 +11946,7 @@
         <v>20</v>
       </c>
       <c r="K217" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L217" t="n">
         <v>0</v>
@@ -11960,12 +11960,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>周明权</t>
+          <t>付林臣</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>1158625019</t>
+          <t>1024206523</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -12001,7 +12001,7 @@
         <v>20</v>
       </c>
       <c r="K218" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L218" t="n">
         <v>0</v>
@@ -12015,12 +12015,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>曾平</t>
+          <t>罗杰</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>1143782010</t>
+          <t>1142566401</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -12035,7 +12035,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -12056,7 +12056,7 @@
         <v>20</v>
       </c>
       <c r="K219" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L219" t="n">
         <v>0</v>
@@ -12070,12 +12070,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>梁祖恩</t>
+          <t>罗文婷</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>1069696308</t>
+          <t>280481452</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -12111,7 +12111,7 @@
         <v>20</v>
       </c>
       <c r="K220" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L220" t="n">
         <v>0</v>
@@ -12125,12 +12125,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>付林臣</t>
+          <t>袁翊博</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>1024206523</t>
+          <t>1145707189</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -12166,7 +12166,7 @@
         <v>20</v>
       </c>
       <c r="K221" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L221" t="n">
         <v>0</v>
@@ -12180,12 +12180,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>罗杰</t>
+          <t>查懿原</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>1142566401</t>
+          <t>276165364</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -12200,12 +12200,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -12221,7 +12221,7 @@
         <v>20</v>
       </c>
       <c r="K222" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L222" t="n">
         <v>0</v>
@@ -12235,12 +12235,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>罗文婷</t>
+          <t>李星龙</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>280481452</t>
+          <t>1090430076</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -12255,12 +12255,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>晚高峰</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -12276,7 +12276,7 @@
         <v>20</v>
       </c>
       <c r="K223" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L223" t="n">
         <v>0</v>
@@ -12290,17 +12290,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>袁翊博</t>
+          <t>邓迪社</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>1145707189</t>
+          <t>221905563</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>思茅优远四队</t>
+          <t>思茅优远五队</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -12310,7 +12310,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -12331,7 +12331,7 @@
         <v>20</v>
       </c>
       <c r="K224" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L224" t="n">
         <v>0</v>
@@ -12345,12 +12345,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>邓迪社</t>
+          <t>熊远发</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>221905563</t>
+          <t>266314300</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -12365,7 +12365,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
+          <t>午高峰、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -12400,12 +12400,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>熊远发</t>
+          <t>黄健翔</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>266314300</t>
+          <t>1071071679</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -12420,7 +12420,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵1</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -12441,7 +12441,7 @@
         <v>20</v>
       </c>
       <c r="K226" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L226" t="n">
         <v>0</v>
@@ -12455,12 +12455,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>黄健翔</t>
+          <t>张鹏</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>1071071679</t>
+          <t>1028523558</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -12475,7 +12475,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -12496,7 +12496,7 @@
         <v>20</v>
       </c>
       <c r="K227" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L227" t="n">
         <v>0</v>
@@ -12510,12 +12510,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>杨双辉</t>
+          <t>陈晓林</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>264798596</t>
+          <t>278941292</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -12565,12 +12565,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>陈晓林</t>
+          <t>肖滔滔</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>278941292</t>
+          <t>270093300</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -12606,7 +12606,7 @@
         <v>20</v>
       </c>
       <c r="K229" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L229" t="n">
         <v>0</v>
@@ -12620,12 +12620,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>肖滔滔</t>
+          <t>普红兵</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>270093300</t>
+          <t>277529860</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -12640,7 +12640,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -12661,7 +12661,7 @@
         <v>20</v>
       </c>
       <c r="K230" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L230" t="n">
         <v>0</v>
@@ -12675,12 +12675,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>普红兵</t>
+          <t>罗俊杰</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>277529860</t>
+          <t>1096790672</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -12695,7 +12695,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -12716,7 +12716,7 @@
         <v>20</v>
       </c>
       <c r="K231" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L231" t="n">
         <v>0</v>
@@ -12730,12 +12730,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>罗俊杰</t>
+          <t>匡一鸣</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>1096790672</t>
+          <t>90000340722076</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -12750,7 +12750,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -12771,7 +12771,7 @@
         <v>20</v>
       </c>
       <c r="K232" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="L232" t="n">
         <v>0</v>
@@ -12785,12 +12785,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>匡一鸣</t>
+          <t>彭毅勇</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>90000340722076</t>
+          <t>175204387</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -12805,7 +12805,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -12840,12 +12840,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>彭毅勇</t>
+          <t>夏彪</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>175204387</t>
+          <t>278430252</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -12860,7 +12860,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -12881,7 +12881,7 @@
         <v>20</v>
       </c>
       <c r="K234" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L234" t="n">
         <v>0</v>
@@ -12895,12 +12895,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>夏彪</t>
+          <t>孙帅</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>278430252</t>
+          <t>227759883</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -12915,7 +12915,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -12936,7 +12936,7 @@
         <v>20</v>
       </c>
       <c r="K235" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L235" t="n">
         <v>0</v>
@@ -12950,12 +12950,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>孙帅</t>
+          <t>陈明源</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>227759883</t>
+          <t>277124636</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -12970,7 +12970,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰、夜宵1</t>
+          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -12991,7 +12991,7 @@
         <v>20</v>
       </c>
       <c r="K236" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L236" t="n">
         <v>0</v>
@@ -13005,12 +13005,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>陈明源</t>
+          <t>李清林</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>277124636</t>
+          <t>266695804</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -13025,7 +13025,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、下午茶2、晚高峰</t>
+          <t>早餐2、午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -13046,7 +13046,7 @@
         <v>20</v>
       </c>
       <c r="K237" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L237" t="n">
         <v>0</v>
@@ -13060,12 +13060,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>李清林</t>
+          <t>杨静修</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>266695804</t>
+          <t>281365980</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -13101,7 +13101,7 @@
         <v>20</v>
       </c>
       <c r="K238" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L238" t="n">
         <v>0</v>
@@ -13115,12 +13115,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>自银号</t>
+          <t>郭莉萍</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>1086868625</t>
+          <t>276709156</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -13135,7 +13135,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
+          <t>早餐2、午高峰、晚高峰</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -13156,7 +13156,7 @@
         <v>20</v>
       </c>
       <c r="K239" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L239" t="n">
         <v>0</v>
@@ -13170,12 +13170,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>杨静修</t>
+          <t>陈新文</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>281365980</t>
+          <t>266350460</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -13190,7 +13190,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -13211,7 +13211,7 @@
         <v>20</v>
       </c>
       <c r="K240" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L240" t="n">
         <v>0</v>
@@ -13225,12 +13225,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>郭莉萍</t>
+          <t>罗文龙</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>276709156</t>
+          <t>173435307</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -13245,7 +13245,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>早餐2、午高峰、晚高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -13266,7 +13266,7 @@
         <v>20</v>
       </c>
       <c r="K241" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L241" t="n">
         <v>0</v>
@@ -13280,12 +13280,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>陈新文</t>
+          <t>王仕臣</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>266350460</t>
+          <t>1043620937</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -13300,7 +13300,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
+          <t>午高峰、下午茶1、晚高峰</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -13335,12 +13335,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>罗文龙</t>
+          <t>自银号</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>173435307</t>
+          <t>1086868625</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -13355,12 +13355,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>午高峰、下午茶2、晚高峰</t>
+          <t>午高峰、晚高峰、夜宵1、夜宵2</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -13376,7 +13376,7 @@
         <v>20</v>
       </c>
       <c r="K243" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L243" t="n">
         <v>0</v>
@@ -13390,12 +13390,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>王仕臣</t>
+          <t>李杰彪</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>1043620937</t>
+          <t>279705460</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -13410,12 +13410,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>午高峰、下午茶1、晚高峰</t>
+          <t>午高峰</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -13431,7 +13431,7 @@
         <v>20</v>
       </c>
       <c r="K244" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L244" t="n">
         <v>0</v>
@@ -13445,12 +13445,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>李杰彪</t>
+          <t>陶树良</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>279705460</t>
+          <t>278115308</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -13465,12 +13465,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>午高峰</t>
+          <t>午高峰、下午茶2、晚高峰</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>离线</t>
+          <t>在线</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -13492,61 +13492,6 @@
         <v>0</v>
       </c>
       <c r="M245" t="inlineStr">
-        <is>
-          <t>预计达标</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>陶树良</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>278115308</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>思茅优远五队</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>优远</t>
-        </is>
-      </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>午高峰、下午茶2、晚高峰</t>
-        </is>
-      </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>离线</t>
-        </is>
-      </c>
-      <c r="G246" t="n">
-        <v>0</v>
-      </c>
-      <c r="H246" t="n">
-        <v>480</v>
-      </c>
-      <c r="I246" t="n">
-        <v>0</v>
-      </c>
-      <c r="J246" t="n">
-        <v>20</v>
-      </c>
-      <c r="K246" t="n">
-        <v>8</v>
-      </c>
-      <c r="L246" t="n">
-        <v>0</v>
-      </c>
-      <c r="M246" t="inlineStr">
         <is>
           <t>预计达标</t>
         </is>
